--- a/MSAMtoExcel_Sample.xlsx
+++ b/MSAMtoExcel_Sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\(F) Spectrum Engineering and Analysis Division\FNajmy\ExcelMSAM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/700f8b47762a8359/Documents/Fred/Temp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA659CC0-416D-4BA7-9861-FEA2709725C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{82E1E936-CF85-4E33-BC44-2D54D544A112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2363B8C3-0311-475E-84F4-9313FE91B908}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Propagation" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,9 @@
     <sheet name="Antenna" sheetId="4" r:id="rId3"/>
     <sheet name="Conversion Functions" sheetId="2" r:id="rId4"/>
     <sheet name="Geographic" sheetId="3" r:id="rId5"/>
-    <sheet name="Intermod" sheetId="6" r:id="rId6"/>
-    <sheet name="Sample Locations" sheetId="7" r:id="rId7"/>
+    <sheet name="Intermod (2)" sheetId="8" r:id="rId6"/>
+    <sheet name="Intermod" sheetId="6" r:id="rId7"/>
+    <sheet name="Sample Locations" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="TerDirectory">Propagation!$Z$8</definedName>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="246">
   <si>
     <t>TxLat</t>
   </si>
@@ -346,9 +347,6 @@
     <t>Line-Of-Sight</t>
   </si>
   <si>
-    <t>P.528</t>
-  </si>
-  <si>
     <t>Delta Bearing</t>
   </si>
   <si>
@@ -437,9 +435,6 @@
   </si>
   <si>
     <t>P.676</t>
-  </si>
-  <si>
-    <t>Terrain Ht(m)</t>
   </si>
   <si>
     <t>Tx</t>
@@ -722,9 +717,6 @@
     <t>Terrain Directory:</t>
   </si>
   <si>
-    <t>C:\USGS</t>
-  </si>
-  <si>
     <t>RxBW (KHz)</t>
   </si>
   <si>
@@ -846,6 +838,9 @@
   </si>
   <si>
     <t>Kitoro</t>
+  </si>
+  <si>
+    <t>F:\USGS</t>
   </si>
 </sst>
 </file>
@@ -855,7 +850,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -892,12 +887,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF040C28"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1042,7 +1031,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1093,7 +1082,10 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1127,8 +1119,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1804,52 +1794,52 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>135.42766979138744</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>135.95371367721219</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>136.44968437376377</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>136.91883544733909</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>137.36391944334778</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>137.78728575442187</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>138.1909557003485</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>138.57668090486609</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>138.94598923918485</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>139.30022138052666</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>139.64056019618354</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>139.96805457904148</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>140.2836389462158</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>140.58814931456496</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>140.88233664983366</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>141.16687802613515</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4625,6 +4615,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4890,18 +4884,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A2:AI38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.85546875" customWidth="1"/>
-    <col min="17" max="17" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6640625" customWidth="1"/>
+    <col min="16" max="16" width="9.88671875" customWidth="1"/>
+    <col min="17" max="17" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:35" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -4960,13 +4954,13 @@
         <v>16</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="V2" s="10" t="s">
         <v>119</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>120</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>18</v>
@@ -4975,7 +4969,7 @@
         <v>20</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>23</v>
@@ -4984,13 +4978,10 @@
         <v>22</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="29">
         <v>8000</v>
       </c>
@@ -5039,56 +5030,52 @@
       <c r="P3" s="29">
         <v>0</v>
       </c>
-      <c r="Q3" s="30">
+      <c r="Q3" s="29">
         <v>0.5</v>
       </c>
-      <c r="R3" s="30">
+      <c r="R3" s="29">
         <v>0.5</v>
       </c>
-      <c r="S3" s="30">
+      <c r="S3" s="29">
         <v>0.5</v>
       </c>
-      <c r="T3" s="23">
-        <f>_xll.Celsius_to_Kelvin(15)</f>
+      <c r="T3" s="23" cm="1">
+        <f t="array" ref="T3">_xll.MSAM.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
-      <c r="U3" s="23">
-        <f>_xll.gpm3_to_hPa(7.5,T3)</f>
+      <c r="U3" s="23" cm="1">
+        <f t="array" ref="U3">_xll.MSAM.gpm3_to_hPa(7.5,T3)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V3" s="29">
         <v>1013.25</v>
       </c>
-      <c r="W3" s="23">
-        <f>_xll.DistKm(B3,C3,E3,F3)</f>
-        <v>17.76476411326108</v>
-      </c>
-      <c r="X3" s="23" t="b">
-        <f>_xll.IsLOS(B3,C3,E3,F3,D3,G3,1,TerDirectory)</f>
-        <v>1</v>
-      </c>
-      <c r="Y3" s="23">
-        <f>_xll.FreeSpace(W3,A3)</f>
-        <v>135.50298864283701</v>
-      </c>
-      <c r="Z3" s="23">
-        <f>_xll.ITMPointToPoint(D3,G3,B3,C3,E3,F3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100,TerHandler,TerDirectory)</f>
-        <v>135.42766979138744</v>
-      </c>
-      <c r="AA3" s="23">
-        <f>_xll.ITMArea(D3,G3,N3,O3,W3,L3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100)</f>
-        <v>137.74535973059781</v>
-      </c>
-      <c r="AB3" s="23">
-        <f>_xll.P528_5(W3,MIN(D3,G3),MAX(D3,G3),A3,H3,Q3*100)</f>
-        <v>135.61004247905726</v>
-      </c>
-      <c r="AC3" s="23">
-        <f>_xll.P676_SpecificAttenuation_dB(A3/1000,T3,U3,V3,W3)</f>
-        <v>0.20280107795331906</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="W3" s="23" cm="1">
+        <f t="array" ref="W3">_xll.MSAM.DistKm(B3,C3,E3,F3)</f>
+        <v>17.76476411326168</v>
+      </c>
+      <c r="X3" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="X3" ca="1">_xll.MSAM.IsLOS(B3,C3,E3,F3,D3,G3,1,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y3" s="23" cm="1">
+        <f t="array" ref="Y3">_xll.MSAM.FreeSpace(W3,A3)</f>
+        <v>135.50298864283729</v>
+      </c>
+      <c r="Z3" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="Z3" ca="1">_xll.MSAM.ITMPointToPoint(D3,G3,B3,C3,E3,F3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA3" s="23" cm="1">
+        <f t="array" ref="AA3">_xll.MSAM.ITMArea(D3,G3,N3,O3,W3,L3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100)</f>
+        <v>137.74535973059869</v>
+      </c>
+      <c r="AB3" s="23" cm="1">
+        <f t="array" ref="AB3">_xll.MSAM.P676_SpecificAttenuation_dB(A3/1000,T3,U3,V3,W3)</f>
+        <v>0.20280107795332591</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>7400</v>
       </c>
@@ -5137,56 +5124,52 @@
       <c r="P4" s="2">
         <v>0</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="2">
         <v>0.5</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="2">
         <v>0.5</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="2">
         <v>0.5</v>
       </c>
-      <c r="T4" s="23">
-        <f>_xll.Celsius_to_Kelvin(15)</f>
+      <c r="T4" s="23" cm="1">
+        <f t="array" ref="T4">_xll.MSAM.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
-      <c r="U4" s="23">
-        <f>_xll.gpm3_to_hPa(7.5,T4)</f>
+      <c r="U4" s="23" cm="1">
+        <f t="array" ref="U4">_xll.MSAM.gpm3_to_hPa(7.5,T4)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V4" s="2">
         <v>1013.25</v>
       </c>
-      <c r="W4" s="23">
-        <f>_xll.DistKm(B4,C4,E4,F4)</f>
-        <v>104.89071248171258</v>
-      </c>
-      <c r="X4" s="23" t="b">
-        <f>_xll.IsLOS(B4,C4,E4,F4,D4,G4,1,TerDirectory)</f>
-        <v>0</v>
-      </c>
-      <c r="Y4" s="23">
-        <f>_xll.FreeSpace(W4,A4)</f>
+      <c r="W4" s="23" cm="1">
+        <f t="array" ref="W4">_xll.MSAM.DistKm(B4,C4,E4,F4)</f>
+        <v>104.89071248171265</v>
+      </c>
+      <c r="X4" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="X4" ca="1">_xll.MSAM.IsLOS(B4,C4,E4,F4,D4,G4,1,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y4" s="23" cm="1">
+        <f t="array" ref="Y4">_xll.MSAM.FreeSpace(W4,A4)</f>
         <v>150.24937510291187</v>
       </c>
-      <c r="Z4" s="23">
-        <f>_xll.ITMPointToPoint(D4,G4,B4,C4,E4,F4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100,TerHandler,TerDirectory)</f>
-        <v>247.81390859953319</v>
-      </c>
-      <c r="AA4" s="23">
-        <f>_xll.ITMArea(D4,G4,N4,O4,W4,L4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100)</f>
+      <c r="Z4" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="Z4" ca="1">_xll.MSAM.ITMPointToPoint(D4,G4,B4,C4,E4,F4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA4" s="23" cm="1">
+        <f t="array" ref="AA4">_xll.MSAM.ITMArea(D4,G4,N4,O4,W4,L4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100)</f>
         <v>210.22674503575132</v>
       </c>
-      <c r="AB4" s="23">
-        <f>_xll.P528_5(W4,MIN(D4,G4),MAX(D4,G4),A4,H4,Q4*100)</f>
-        <v>201.74436882882611</v>
-      </c>
-      <c r="AC4" s="23">
-        <f>_xll.P676_SpecificAttenuation_dB(A4/1000,T4,U4,V4,W4)</f>
-        <v>1.1280677803367003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AB4" s="23" cm="1">
+        <f t="array" ref="AB4">_xll.MSAM.P676_SpecificAttenuation_dB(A4/1000,T4,U4,V4,W4)</f>
+        <v>1.1280677803367012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>7600</v>
       </c>
@@ -5235,56 +5218,52 @@
       <c r="P5" s="2">
         <v>0</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>0.5</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <v>0.5</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <v>0.5</v>
       </c>
-      <c r="T5" s="23">
-        <f>_xll.Celsius_to_Kelvin(15)</f>
+      <c r="T5" s="23" cm="1">
+        <f t="array" ref="T5">_xll.MSAM.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
-      <c r="U5" s="23">
-        <f>_xll.gpm3_to_hPa(7.5,T5)</f>
+      <c r="U5" s="23" cm="1">
+        <f t="array" ref="U5">_xll.MSAM.gpm3_to_hPa(7.5,T5)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V5" s="2">
         <v>1013.25</v>
       </c>
-      <c r="W5" s="23">
-        <f>_xll.DistKm(B5,C5,E5,F5)</f>
-        <v>104.89071248171258</v>
-      </c>
-      <c r="X5" s="23" t="b">
-        <f>_xll.IsLOS(B5,C5,E5,F5,D5,G5,1,TerDirectory)</f>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="23">
-        <f>_xll.FreeSpace(W5,A5)</f>
+      <c r="W5" s="23" cm="1">
+        <f t="array" ref="W5">_xll.MSAM.DistKm(B5,C5,E5,F5)</f>
+        <v>104.89071248171265</v>
+      </c>
+      <c r="X5" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="X5" ca="1">_xll.MSAM.IsLOS(B5,C5,E5,F5,D5,G5,1,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y5" s="23" cm="1">
+        <f t="array" ref="Y5">_xll.MSAM.FreeSpace(W5,A5)</f>
         <v>150.48101255390816</v>
       </c>
-      <c r="Z5" s="23">
-        <f>_xll.ITMPointToPoint(D5,G5,B5,C5,E5,F5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100,TerHandler,TerDirectory)</f>
-        <v>248.46459419519601</v>
-      </c>
-      <c r="AA5" s="23">
-        <f>_xll.ITMArea(D5,G5,N5,O5,W5,L5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100)</f>
+      <c r="Z5" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="Z5" ca="1">_xll.MSAM.ITMPointToPoint(D5,G5,B5,C5,E5,F5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA5" s="23" cm="1">
+        <f t="array" ref="AA5">_xll.MSAM.ITMArea(D5,G5,N5,O5,W5,L5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100)</f>
         <v>210.56824850094489</v>
       </c>
-      <c r="AB5" s="23">
-        <f>_xll.P528_5(W5,MIN(D5,G5),MAX(D5,G5),A5,H5,Q5*100)</f>
-        <v>202.09473080295425</v>
-      </c>
-      <c r="AC5" s="23">
-        <f>_xll.P676_SpecificAttenuation_dB(A5/1000,T5,U5,V5,W5)</f>
-        <v>1.1503823038844661</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AB5" s="23" cm="1">
+        <f t="array" ref="AB5">_xll.MSAM.P676_SpecificAttenuation_dB(A5/1000,T5,U5,V5,W5)</f>
+        <v>1.1503823038844667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>6725</v>
       </c>
@@ -5333,167 +5312,163 @@
       <c r="P6" s="2">
         <v>0</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="2">
         <v>0.5</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="2">
         <v>0.5</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="2">
         <v>0.5</v>
       </c>
-      <c r="T6" s="23">
-        <f>_xll.Celsius_to_Kelvin(15)</f>
+      <c r="T6" s="23" cm="1">
+        <f t="array" ref="T6">_xll.MSAM.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
-      <c r="U6" s="23">
-        <f>_xll.gpm3_to_hPa(7.5,T6)</f>
+      <c r="U6" s="23" cm="1">
+        <f t="array" ref="U6">_xll.MSAM.gpm3_to_hPa(7.5,T6)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V6" s="2">
         <v>1013.25</v>
       </c>
-      <c r="W6" s="23">
-        <f>_xll.DistKm(B6,C6,E6,F6)</f>
+      <c r="W6" s="23" cm="1">
+        <f t="array" ref="W6">_xll.MSAM.DistKm(B6,C6,E6,F6)</f>
         <v>35.791078240559798</v>
       </c>
-      <c r="X6" s="23" t="b">
-        <f>_xll.IsLOS(B6,C6,E6,F6,D6,G6,1,TerDirectory)</f>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="23">
-        <f>_xll.FreeSpace(W6,A6)</f>
+      <c r="X6" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="X6" ca="1">_xll.MSAM.IsLOS(B6,C6,E6,F6,D6,G6,1,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="Y6" s="23" cm="1">
+        <f t="array" ref="Y6">_xll.MSAM.FreeSpace(W6,A6)</f>
         <v>140.07934141598673</v>
       </c>
-      <c r="Z6" s="23">
-        <f>_xll.ITMPointToPoint(D6,G6,B6,C6,E6,F6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100,TerHandler,TerDirectory)</f>
-        <v>229.3596488564566</v>
-      </c>
-      <c r="AA6" s="23">
-        <f>_xll.ITMArea(D6,G6,N6,O6,W6,L6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100)</f>
+      <c r="Z6" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="Z6" ca="1">_xll.MSAM.ITMPointToPoint(D6,G6,B6,C6,E6,F6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="AA6" s="23" cm="1">
+        <f t="array" ref="AA6">_xll.MSAM.ITMArea(D6,G6,N6,O6,W6,L6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100)</f>
         <v>166.90495037329015</v>
       </c>
-      <c r="AB6" s="23">
-        <f>_xll.P528_5(W6,MIN(D6,G6),MAX(D6,G6),A6,H6,Q6*100)</f>
-        <v>169.25679822631758</v>
-      </c>
-      <c r="AC6" s="23">
-        <f>_xll.P676_SpecificAttenuation_dB(A6/1000,T6,U6,V6,W6)</f>
+      <c r="AB6" s="23" cm="1">
+        <f t="array" ref="AB6">_xll.MSAM.P676_SpecificAttenuation_dB(A6/1000,T6,U6,V6,W6)</f>
         <v>0.36111607479468177</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="X7" s="17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Z7" s="28">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
       <c r="S8" s="8"/>
       <c r="X8" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="Z8" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="AA8" s="31"/>
-      <c r="AB8" s="31"/>
-      <c r="AC8" s="31"/>
-      <c r="AD8" s="31"/>
-      <c r="AE8" s="31"/>
-      <c r="AF8" s="31"/>
-      <c r="AG8" s="31"/>
-      <c r="AH8" s="31"/>
-      <c r="AI8" s="31"/>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+      <c r="Z8" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA8" s="32"/>
+      <c r="AB8" s="32"/>
+      <c r="AC8" s="32"/>
+      <c r="AD8" s="32"/>
+      <c r="AE8" s="32"/>
+      <c r="AF8" s="32"/>
+      <c r="AG8" s="32"/>
+      <c r="AH8" s="32"/>
+      <c r="AI8" s="32"/>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="8"/>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
       <c r="S10" s="8"/>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
       <c r="S11" s="8"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A12" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="M12" s="33" t="s">
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="M12" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
-      <c r="V12" s="34"/>
-      <c r="W12" s="34"/>
-    </row>
-    <row r="13" spans="1:35" ht="45" x14ac:dyDescent="0.25">
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+    </row>
+    <row r="13" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>96</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>97</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="I13" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="J13" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="J13" s="9" t="s">
-        <v>97</v>
-      </c>
       <c r="K13" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>81</v>
@@ -5508,28 +5483,28 @@
         <v>82</v>
       </c>
       <c r="Q13" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="R13" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="R13" s="11" t="s">
+      <c r="S13" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="S13" s="11" t="s">
+      <c r="T13" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="T13" s="11" t="s">
+      <c r="U13" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="U13" s="11" t="s">
+      <c r="V13" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="V13" s="11" t="s">
-        <v>108</v>
-      </c>
       <c r="W13" s="11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>7125</v>
       </c>
@@ -5560,8 +5535,8 @@
       <c r="J14" s="2">
         <v>3</v>
       </c>
-      <c r="K14" s="23">
-        <f>_xll.FDR_Stairs_3_20_40_60_dB(B14,C14,D14,E14,G14,H14,I14,J14,A14,F14)</f>
+      <c r="K14" s="23" cm="1">
+        <f t="array" ref="K14">_xll.MSAM.FDR_Stairs_3_20_40_60_dB(B14,C14,D14,E14,G14,H14,I14,J14,A14,F14)</f>
         <v>6.6280214362000329</v>
       </c>
       <c r="M14" s="2">
@@ -5579,62 +5554,62 @@
       <c r="Q14" s="2">
         <v>35887</v>
       </c>
-      <c r="R14" s="23">
-        <f>_xll.SatAz(M14,N14,O14,P14,Q14,0)</f>
+      <c r="R14" s="23" cm="1">
+        <f t="array" ref="R14">_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,0)</f>
         <v>8.679000600046443</v>
       </c>
-      <c r="S14" s="23">
-        <f>_xll.SatAz(M14,N14,O14,P14,Q14,1)</f>
+      <c r="S14" s="23" cm="1">
+        <f t="array" ref="S14">_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,1)</f>
         <v>41689.597238153408</v>
       </c>
-      <c r="T14" s="23">
-        <f>_xll.SatAz(M14,N14,O14,P14,Q14,2)</f>
-        <v>97.359615358931151</v>
-      </c>
-      <c r="U14" s="23">
-        <f>_xll.SatAz(M14,N14,O14,P14,Q14,3)</f>
+      <c r="T14" s="23" cm="1">
+        <f t="array" ref="T14">_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,2)</f>
+        <v>97.359615358931137</v>
+      </c>
+      <c r="U14" s="23" cm="1">
+        <f t="array" ref="U14">_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,3)</f>
         <v>0.82543716113656984</v>
       </c>
-      <c r="V14" s="23">
-        <f>_xll.SatAz(M14,N14,O14,P14,Q14,4)</f>
+      <c r="V14" s="23" cm="1">
+        <f t="array" ref="V14">_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,4)</f>
         <v>13.318849480844628</v>
       </c>
-      <c r="W14" s="23" t="b">
-        <f>IF(_xll.SatAz(M14,N14,O14,P14,Q14,5)=0,TRUE,FALSE)</f>
+      <c r="W14" s="23" t="b" cm="1">
+        <f t="array" ref="W14">IF(_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,5)=0,TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
       <c r="S17" s="8"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
       <c r="S18" s="8"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
       <c r="S19" s="8"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
       <c r="S20" s="8"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
@@ -5648,276 +5623,276 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>50</v>
       </c>
-      <c r="B23" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A23,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B23" s="23" cm="1">
+        <f t="array" ref="B23">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A23,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>176.35416608939531</v>
       </c>
       <c r="M23" s="2">
         <f>A3</f>
         <v>8000</v>
       </c>
-      <c r="N23" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M23,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>135.42766979138744</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N23" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N23" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M23,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>60</v>
       </c>
-      <c r="B24" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A24,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B24" s="23" cm="1">
+        <f t="array" ref="B24">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A24,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>186.87976908830476</v>
       </c>
       <c r="M24" s="2">
         <f>M23+500</f>
         <v>8500</v>
       </c>
-      <c r="N24" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M24,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>135.95371367721219</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N24" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N24" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M24,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>70</v>
       </c>
-      <c r="B25" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A25,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B25" s="23" cm="1">
+        <f t="array" ref="B25">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A25,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>197.24551913339644</v>
       </c>
       <c r="M25" s="2">
         <f t="shared" ref="M25:M38" si="0">M24+500</f>
         <v>9000</v>
       </c>
-      <c r="N25" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M25,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>136.44968437376377</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N25" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N25" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M25,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>80</v>
       </c>
-      <c r="B26" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A26,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B26" s="23" cm="1">
+        <f t="array" ref="B26">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A26,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>207.52789850239242</v>
       </c>
       <c r="M26" s="2">
         <f t="shared" si="0"/>
         <v>9500</v>
       </c>
-      <c r="N26" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M26,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>136.91883544733909</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N26" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N26" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M26,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>90</v>
       </c>
-      <c r="B27" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A27,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B27" s="23" cm="1">
+        <f t="array" ref="B27">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A27,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>209.4443793957183</v>
       </c>
       <c r="M27" s="2">
         <f t="shared" si="0"/>
         <v>10000</v>
       </c>
-      <c r="N27" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M27,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>137.36391944334778</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N27" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N27" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M27,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>100</v>
       </c>
-      <c r="B28" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A28,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B28" s="23" cm="1">
+        <f t="array" ref="B28">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A28,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>210.66103070828476</v>
       </c>
       <c r="M28" s="2">
         <f t="shared" si="0"/>
         <v>10500</v>
       </c>
-      <c r="N28" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M28,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>137.78728575442187</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N28" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N28" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M28,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>110</v>
       </c>
-      <c r="B29" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A29,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B29" s="23" cm="1">
+        <f t="array" ref="B29">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A29,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>211.79807317762641</v>
       </c>
       <c r="M29" s="2">
         <f t="shared" si="0"/>
         <v>11000</v>
       </c>
-      <c r="N29" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M29,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>138.1909557003485</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N29" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N29" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M29,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>120</v>
       </c>
-      <c r="B30" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A30,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B30" s="23" cm="1">
+        <f t="array" ref="B30">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A30,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>212.88192518947073</v>
       </c>
       <c r="M30" s="2">
         <f t="shared" si="0"/>
         <v>11500</v>
       </c>
-      <c r="N30" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M30,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>138.57668090486609</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N30" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N30" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M30,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>130</v>
       </c>
-      <c r="B31" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A31,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B31" s="23" cm="1">
+        <f t="array" ref="B31">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A31,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>213.93526701187233</v>
       </c>
       <c r="M31" s="2">
         <f t="shared" si="0"/>
         <v>12000</v>
       </c>
-      <c r="N31" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M31,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>138.94598923918485</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N31" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N31" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M31,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>140</v>
       </c>
-      <c r="B32" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A32,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B32" s="23" cm="1">
+        <f t="array" ref="B32">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A32,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>214.9770617162292</v>
       </c>
       <c r="M32" s="2">
         <f t="shared" si="0"/>
         <v>12500</v>
       </c>
-      <c r="N32" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M32,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>139.30022138052666</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N32" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N32" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M32,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>150</v>
       </c>
-      <c r="B33" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A33,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B33" s="23" cm="1">
+        <f t="array" ref="B33">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A33,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>216.02224872255118</v>
       </c>
       <c r="M33" s="2">
         <f t="shared" si="0"/>
         <v>13000</v>
       </c>
-      <c r="N33" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M33,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>139.64056019618354</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N33" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N33" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M33,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>160</v>
       </c>
-      <c r="B34" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A34,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B34" s="23" cm="1">
+        <f t="array" ref="B34">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A34,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>217.08146223455873</v>
       </c>
       <c r="M34" s="2">
         <f t="shared" si="0"/>
         <v>13500</v>
       </c>
-      <c r="N34" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M34,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>139.96805457904148</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N34" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N34" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M34,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>170</v>
       </c>
-      <c r="B35" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A35,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B35" s="23" cm="1">
+        <f t="array" ref="B35">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A35,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>218.16101303187853</v>
       </c>
       <c r="M35" s="2">
         <f t="shared" si="0"/>
         <v>14000</v>
       </c>
-      <c r="N35" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M35,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>140.2836389462158</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N35" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N35" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M35,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>180</v>
       </c>
-      <c r="B36" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A36,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B36" s="23" cm="1">
+        <f t="array" ref="B36">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A36,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>219.26323500631244</v>
       </c>
       <c r="M36" s="2">
         <f t="shared" si="0"/>
         <v>14500</v>
       </c>
-      <c r="N36" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M36,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>140.58814931456496</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N36" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N36" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M36,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>190</v>
       </c>
-      <c r="B37" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A37,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B37" s="23" cm="1">
+        <f t="array" ref="B37">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A37,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>220.3871640114109</v>
       </c>
       <c r="M37" s="2">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
-      <c r="N37" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M37,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>140.88233664983366</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N37" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N37" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M37,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>200</v>
       </c>
-      <c r="B38" s="23">
-        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A38,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B38" s="23" cm="1">
+        <f t="array" ref="B38">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A38,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>221.52942277502015</v>
       </c>
       <c r="M38" s="2">
         <f t="shared" si="0"/>
         <v>15500</v>
       </c>
-      <c r="N38" s="23">
-        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M38,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>141.16687802613515</v>
+      <c r="N38" s="23" t="e" cm="1">
+        <f t="array" aca="1" ref="N38" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M38,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>#NAME?</v>
       </c>
     </row>
   </sheetData>
@@ -5939,33 +5914,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:AC37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" customWidth="1"/>
-    <col min="13" max="13" width="11.5703125" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" customWidth="1"/>
+    <col min="2" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="10" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="13.109375" customWidth="1"/>
+    <col min="12" max="12" width="10.5546875" customWidth="1"/>
+    <col min="13" max="13" width="11.5546875" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="16.28515625" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" customWidth="1"/>
+    <col min="17" max="17" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="B1" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-    </row>
-    <row r="2" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="B1" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B2" s="13" t="s">
         <v>81</v>
       </c>
@@ -5973,7 +5948,7 @@
         <v>82</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>81</v>
@@ -5982,40 +5957,40 @@
         <v>82</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H2" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="I2" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="K2" s="13" t="s">
+      <c r="M2" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="N2" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="O2" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="M2" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="P2" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="R2" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>6</v>
@@ -6051,27 +6026,27 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B3" s="24">
-        <f>_xll.GetLatitude(E3,F3,20,80)</f>
+        <v>136</v>
+      </c>
+      <c r="B3" s="24" cm="1">
+        <f t="array" ref="B3">_xll.GetLatitude(E3,F3,20,80)</f>
         <v>39.430778738197418</v>
       </c>
-      <c r="C3" s="24">
-        <f>_xll.GetLongitude(E3,F3,20,80)</f>
+      <c r="C3" s="24" cm="1">
+        <f t="array" ref="C3">_xll.GetLongitude(E3,F3,20,80)</f>
         <v>-77.408737187096492</v>
       </c>
       <c r="D3" s="14">
         <v>45.72</v>
       </c>
-      <c r="E3" s="2">
-        <f>_xll.DMS2DecDeg("392359N")</f>
+      <c r="E3" s="2" cm="1">
+        <f t="array" ref="E3">_xll.DMS2DecDeg("392359N")</f>
         <v>39.399722222222223</v>
       </c>
-      <c r="F3" s="2">
-        <f>_xll.DMS2DecDeg("0773815W")</f>
+      <c r="F3" s="2" cm="1">
+        <f t="array" ref="F3">_xll.DMS2DecDeg("0773815W")</f>
         <v>-77.637500000000003</v>
       </c>
       <c r="G3" s="2">
@@ -6096,17 +6071,17 @@
         <v>3.5</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O3" s="2">
         <v>4</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q3" s="23">
-        <f>_xll.Bearing(E3,F3,B3,C3)</f>
-        <v>79.999999999996078</v>
+        <v>142</v>
+      </c>
+      <c r="Q3" s="23" cm="1">
+        <f t="array" ref="Q3">_xll.Bearing(E3,F3,B3,C3)</f>
+        <v>80.000000000000057</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="20">
@@ -6143,27 +6118,27 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="23">
-        <f>_xll.DMS2DecDeg("392400N")</f>
+        <v>137</v>
+      </c>
+      <c r="B4" s="23" cm="1">
+        <f t="array" ref="B4">_xll.DMS2DecDeg("392400N")</f>
         <v>39.4</v>
       </c>
-      <c r="C4" s="23">
-        <f>_xll.DMS2DecDeg("0772400W")</f>
+      <c r="C4" s="23" cm="1">
+        <f t="array" ref="C4">_xll.DMS2DecDeg("0772400W")</f>
         <v>-77.400000000000006</v>
       </c>
       <c r="D4" s="2">
         <v>45.72</v>
       </c>
-      <c r="E4" s="24">
-        <f>_xll.GetLatitude(B4,C4,20,275)</f>
+      <c r="E4" s="24" cm="1">
+        <f t="array" ref="E4">_xll.GetLatitude(B4,C4,20,275)</f>
         <v>39.415470445255202</v>
       </c>
-      <c r="F4" s="24">
-        <f>_xll.GetLongitude(B4,C4,20,275)</f>
+      <c r="F4" s="24" cm="1">
+        <f t="array" ref="F4">_xll.GetLongitude(B4,C4,20,275)</f>
         <v>-77.631357303040929</v>
       </c>
       <c r="G4" s="14">
@@ -6188,195 +6163,195 @@
         <v>3.5</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O4" s="2">
         <v>3</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q4" s="23">
-        <f>_xll.Bearing(B4,C4,E4,F4)</f>
-        <v>274.9999999999921</v>
-      </c>
-      <c r="R4" s="23">
-        <f>_xll.Delta_Bearing(Q4,Q3)</f>
-        <v>165.00000000000398</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="Q4" s="23" cm="1">
+        <f t="array" ref="Q4">_xll.Bearing(B4,C4,E4,F4)</f>
+        <v>274.99999999999312</v>
+      </c>
+      <c r="R4" s="23" cm="1">
+        <f t="array" ref="R4">_xll.Delta_Bearing(Q4,Q3)</f>
+        <v>165.00000000000693</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="L6" s="17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E7">
         <f>_xll.Bearing(B4,C4,E3,F3)</f>
-        <v>269.98900055432671</v>
+        <v>269.98900055432966</v>
       </c>
       <c r="F7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G7">
         <f>_xll.DistKm(E3,F3,B4,C4)</f>
         <v>20.457487034523673</v>
       </c>
       <c r="L7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E8">
         <f>_xll.Bearing(E3,F3,B4,C4)</f>
-        <v>89.838252372907164</v>
+        <v>89.838252372911114</v>
       </c>
       <c r="L8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="N9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="K10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="K11">
         <v>-29.5</v>
       </c>
       <c r="L11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="K12">
         <v>33.5</v>
       </c>
       <c r="L12" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="K13">
         <v>16</v>
       </c>
       <c r="L13" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="L14" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="K15">
         <v>8</v>
       </c>
       <c r="L15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="L16" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="11:22" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="11:22" x14ac:dyDescent="0.3">
       <c r="L17" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="18" spans="11:22" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="11:22" x14ac:dyDescent="0.3">
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="19" spans="11:22" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="11:22" x14ac:dyDescent="0.3">
       <c r="K19">
         <v>3</v>
       </c>
       <c r="L19" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="20" spans="11:22" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="11:22" x14ac:dyDescent="0.3">
       <c r="K20">
         <v>4</v>
       </c>
       <c r="L20" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="21" spans="11:22" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="11:22" x14ac:dyDescent="0.3">
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="11:22" x14ac:dyDescent="0.3">
+      <c r="K24" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="M24" s="18" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="24" spans="11:22" x14ac:dyDescent="0.25">
-      <c r="K24" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="L24" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="M24" s="18" t="s">
+      <c r="N24" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="O24" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="N24" s="18" t="s">
+      <c r="P24" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="O24" s="18" t="s">
+      <c r="Q24" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="P24" s="18" t="s">
+      <c r="R24" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="Q24" s="18" t="s">
+      <c r="S24" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="T24" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="R24" s="18" t="s">
+      <c r="U24" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="V24" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="S24" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="T24" s="18" t="s">
+    </row>
+    <row r="25" spans="11:22" x14ac:dyDescent="0.3">
+      <c r="K25" s="16" t="s">
         <v>165</v>
-      </c>
-      <c r="U24" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="V24" s="18" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="25" spans="11:22" x14ac:dyDescent="0.25">
-      <c r="K25" s="16" t="s">
-        <v>167</v>
       </c>
       <c r="L25" s="2">
         <f>N25-O25-P25-Q25+R25+S25+T25+U25+V25</f>
@@ -6395,8 +6370,8 @@
       <c r="Q25" s="2">
         <v>8</v>
       </c>
-      <c r="R25" s="23">
-        <f>_xll.ITMArea(D4,G3,X3,Y3,_xll.DistKm(B4,C4,E3,F3),V3,W3,S3,H3,IF(N3="V",1,0),U3,T3,Z3,AA3*100,AB3*100,AC3*100)</f>
+      <c r="R25" s="23" cm="1">
+        <f t="array" ref="R25">_xll.ITMArea(D4,G3,X3,Y3,_xll.DistKm(B4,C4,E3,F3),V3,W3,S3,H3,IF(N3="V",1,0),U3,T3,Z3,AA3*100,AB3*100,AC3*100)</f>
         <v>136.65456853650161</v>
       </c>
       <c r="S25" s="2">
@@ -6412,13 +6387,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="11:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="11:22" x14ac:dyDescent="0.3">
       <c r="K26" s="16" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="2">
         <f>N26-O26-P26-Q26+R26+S26+T26+U26+V26</f>
-        <v>114.26920385903014</v>
+        <v>114.26920385902991</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2">
@@ -6433,9 +6408,9 @@
       <c r="Q26" s="2">
         <v>8</v>
       </c>
-      <c r="R26" s="23">
-        <f>_xll.ITMPointToPointCR(D4,G3,B4,C4,E3,F3,W3,S3,H3,IF(N3="V",1,0),U3,T3,Z3,AA3*100,AB3*100,0,TerDirectory)</f>
-        <v>194.26920385903014</v>
+      <c r="R26" s="23" cm="1">
+        <f t="array" ref="R26">_xll.ITMPointToPointCR(D4,G3,B4,C4,E3,F3,W3,S3,H3,IF(N3="V",1,0),U3,T3,Z3,AA3*100,AB3*100,0,TerDirectory)</f>
+        <v>194.26920385902991</v>
       </c>
       <c r="S26" s="2">
         <v>0</v>
@@ -6450,9 +6425,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="11:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="11:22" x14ac:dyDescent="0.3">
       <c r="K28" s="17" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L28">
         <f>-29.5-(-102.5)</f>
@@ -6463,67 +6438,67 @@
         <v>=</v>
       </c>
       <c r="N28" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="29" spans="11:22" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="11:22" x14ac:dyDescent="0.3">
       <c r="O29" t="s">
-        <v>182</v>
-      </c>
-      <c r="P29" s="27">
-        <f xml:space="preserve"> _xll.Delta_Bearing(_xll.Bearing(B4,C4,E4,F4),_xll.Bearing(B4,C4,E3,F3))</f>
-        <v>5.0109994456653908</v>
+        <v>180</v>
+      </c>
+      <c r="P29" s="27" cm="1">
+        <f t="array" ref="P29">_xll.Delta_Bearing(_xll.Bearing(B4,C4,E4,F4),_xll.Bearing(B4,C4,E3,F3))</f>
+        <v>5.0109994456634581</v>
       </c>
       <c r="Q29" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" spans="11:22" x14ac:dyDescent="0.3">
+      <c r="O30" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="30" spans="11:22" x14ac:dyDescent="0.25">
-      <c r="O30" t="s">
-        <v>183</v>
-      </c>
-      <c r="P30" s="27">
-        <f xml:space="preserve"> _xll.Delta_Bearing(_xll.Bearing(E4,F4,B4,C4),_xll.Bearing(E4,F4,B3,C3))</f>
+      <c r="P30" s="27" cm="1">
+        <f t="array" ref="P30">_xll.Delta_Bearing(_xll.Bearing(E4,F4,B4,C4),_xll.Bearing(E4,F4,B3,C3))</f>
         <v>9.9904702043319702</v>
       </c>
       <c r="Q30" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="31" spans="11:22" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="11:22" x14ac:dyDescent="0.3">
       <c r="L31" s="17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="32" spans="11:22" ht="17.25" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="11:22" ht="16.2" x14ac:dyDescent="0.3">
       <c r="L32" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33" spans="12:13" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="12:13" x14ac:dyDescent="0.3">
       <c r="M33" t="str">
         <f>"- Telecommunications Industry Association Bulletin 10F specifies an I/N of -6 dB for digital systems"</f>
         <v>- Telecommunications Industry Association Bulletin 10F specifies an I/N of -6 dB for digital systems</v>
       </c>
     </row>
-    <row r="34" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="M35" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="M35" t="s">
+    <row r="37" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="M37" t="s">
         <v>174</v>
-      </c>
-    </row>
-    <row r="36" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L36" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="37" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="M37" t="s">
-        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -6541,35 +6516,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:G23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="6" width="9.85546875" customWidth="1"/>
+    <col min="4" max="6" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>43</v>
       </c>
@@ -6582,20 +6557,20 @@
       <c r="D3" s="12">
         <v>0.75</v>
       </c>
-      <c r="E3" s="25">
-        <f>_xll.BmWToGain_dB(C3,D3)</f>
+      <c r="E3" s="25" cm="1">
+        <f t="array" ref="E3">_xll.BmWToGain_dB(C3,D3)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F3" s="25">
-        <f>_xll.StatGainWolfGain(B3,A3)</f>
+      <c r="F3" s="25" cm="1">
+        <f t="array" ref="F3">_xll.StatGainWolfGain(B3,A3)</f>
         <v>43</v>
       </c>
-      <c r="G3" s="25">
-        <f>_xll.StatGain(B3,A3)</f>
+      <c r="G3" s="25" cm="1">
+        <f t="array" ref="G3">_xll.StatGain(B3,A3)</f>
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>43</v>
       </c>
@@ -6608,20 +6583,20 @@
       <c r="D4" s="12">
         <v>0.75</v>
       </c>
-      <c r="E4" s="25">
-        <f>_xll.BmWToGain_dB(C4,D4)</f>
+      <c r="E4" s="25" cm="1">
+        <f t="array" ref="E4">_xll.BmWToGain_dB(C4,D4)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F4" s="25">
-        <f>_xll.StatGainWolfGain(B4,A4)</f>
+      <c r="F4" s="25" cm="1">
+        <f t="array" ref="F4">_xll.StatGainWolfGain(B4,A4)</f>
         <v>41.004737685031124</v>
       </c>
-      <c r="G4" s="25">
-        <f>_xll.StatGain(B4,A4)</f>
+      <c r="G4" s="25" cm="1">
+        <f t="array" ref="G4">_xll.StatGain(B4,A4)</f>
         <v>41.004737685031124</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>43</v>
       </c>
@@ -6634,20 +6609,20 @@
       <c r="D5" s="12">
         <v>0.75</v>
       </c>
-      <c r="E5" s="25">
-        <f>_xll.BmWToGain_dB(C5,D5)</f>
+      <c r="E5" s="25" cm="1">
+        <f t="array" ref="E5">_xll.BmWToGain_dB(C5,D5)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F5" s="25">
-        <f>_xll.StatGainWolfGain(B5,A5)</f>
+      <c r="F5" s="25" cm="1">
+        <f t="array" ref="F5">_xll.StatGainWolfGain(B5,A5)</f>
         <v>35.018950740124481</v>
       </c>
-      <c r="G5" s="25">
-        <f>_xll.StatGain(B5,A5)</f>
+      <c r="G5" s="25" cm="1">
+        <f t="array" ref="G5">_xll.StatGain(B5,A5)</f>
         <v>35.018950740124481</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>43</v>
       </c>
@@ -6660,20 +6635,20 @@
       <c r="D6" s="12">
         <v>0.75</v>
       </c>
-      <c r="E6" s="25">
-        <f>_xll.BmWToGain_dB(C6,D6)</f>
+      <c r="E6" s="25" cm="1">
+        <f t="array" ref="E6">_xll.BmWToGain_dB(C6,D6)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F6" s="25">
-        <f>_xll.StatGainWolfGain(B6,A6)</f>
+      <c r="F6" s="25" cm="1">
+        <f t="array" ref="F6">_xll.StatGainWolfGain(B6,A6)</f>
         <v>25.25</v>
       </c>
-      <c r="G6" s="25">
-        <f>_xll.StatGain(B6,A6)</f>
+      <c r="G6" s="25" cm="1">
+        <f t="array" ref="G6">_xll.StatGain(B6,A6)</f>
         <v>25.25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>43</v>
       </c>
@@ -6686,20 +6661,20 @@
       <c r="D7" s="12">
         <v>0.75</v>
       </c>
-      <c r="E7" s="25">
-        <f>_xll.BmWToGain_dB(C7,D7)</f>
+      <c r="E7" s="25" cm="1">
+        <f t="array" ref="E7">_xll.BmWToGain_dB(C7,D7)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F7" s="25">
-        <f>_xll.StatGainWolfGain(B7,A7)</f>
+      <c r="F7" s="25" cm="1">
+        <f t="array" ref="F7">_xll.StatGainWolfGain(B7,A7)</f>
         <v>23.974250108400469</v>
       </c>
-      <c r="G7" s="25">
-        <f>_xll.StatGain(B7,A7)</f>
+      <c r="G7" s="25" cm="1">
+        <f t="array" ref="G7">_xll.StatGain(B7,A7)</f>
         <v>23.974250108400469</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>43</v>
       </c>
@@ -6712,20 +6687,20 @@
       <c r="D8" s="12">
         <v>0.75</v>
       </c>
-      <c r="E8" s="25">
-        <f>_xll.BmWToGain_dB(C8,D8)</f>
+      <c r="E8" s="25" cm="1">
+        <f t="array" ref="E8">_xll.BmWToGain_dB(C8,D8)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F8" s="25">
-        <f>_xll.StatGainWolfGain(B8,A8)</f>
+      <c r="F8" s="25" cm="1">
+        <f t="array" ref="F8">_xll.StatGainWolfGain(B8,A8)</f>
         <v>21.551499783199059</v>
       </c>
-      <c r="G8" s="25">
-        <f>_xll.StatGain(B8,A8)</f>
+      <c r="G8" s="25" cm="1">
+        <f t="array" ref="G8">_xll.StatGain(B8,A8)</f>
         <v>21.551499783199059</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>43</v>
       </c>
@@ -6738,20 +6713,20 @@
       <c r="D9" s="12">
         <v>0.75</v>
       </c>
-      <c r="E9" s="25">
-        <f>_xll.BmWToGain_dB(C9,D9)</f>
+      <c r="E9" s="25" cm="1">
+        <f t="array" ref="E9">_xll.BmWToGain_dB(C9,D9)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F9" s="25">
-        <f>_xll.StatGainWolfGain(B9,A9)</f>
+      <c r="F9" s="25" cm="1">
+        <f t="array" ref="F9">_xll.StatGainWolfGain(B9,A9)</f>
         <v>19.571968632008439</v>
       </c>
-      <c r="G9" s="25">
-        <f>_xll.StatGain(B9,A9)</f>
+      <c r="G9" s="25" cm="1">
+        <f t="array" ref="G9">_xll.StatGain(B9,A9)</f>
         <v>19.571968632008439</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>43</v>
       </c>
@@ -6764,20 +6739,20 @@
       <c r="D10" s="12">
         <v>0.75</v>
       </c>
-      <c r="E10" s="25">
-        <f>_xll.BmWToGain_dB(C10,D10)</f>
+      <c r="E10" s="25" cm="1">
+        <f t="array" ref="E10">_xll.BmWToGain_dB(C10,D10)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F10" s="25">
-        <f>_xll.StatGainWolfGain(B10,A10)</f>
+      <c r="F10" s="25" cm="1">
+        <f t="array" ref="F10">_xll.StatGainWolfGain(B10,A10)</f>
         <v>17.898298891243108</v>
       </c>
-      <c r="G10" s="25">
-        <f>_xll.StatGain(B10,A10)</f>
+      <c r="G10" s="25" cm="1">
+        <f t="array" ref="G10">_xll.StatGain(B10,A10)</f>
         <v>17.898298891243108</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>43</v>
       </c>
@@ -6790,20 +6765,20 @@
       <c r="D11" s="12">
         <v>0.75</v>
       </c>
-      <c r="E11" s="25">
-        <f>_xll.BmWToGain_dB(C11,D11)</f>
+      <c r="E11" s="25" cm="1">
+        <f t="array" ref="E11">_xll.BmWToGain_dB(C11,D11)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F11" s="25">
-        <f>_xll.StatGainWolfGain(B11,A11)</f>
+      <c r="F11" s="25" cm="1">
+        <f t="array" ref="F11">_xll.StatGainWolfGain(B11,A11)</f>
         <v>16.448500216800941</v>
       </c>
-      <c r="G11" s="25">
-        <f>_xll.StatGain(B11,A11)</f>
+      <c r="G11" s="25" cm="1">
+        <f t="array" ref="G11">_xll.StatGain(B11,A11)</f>
         <v>16.448500216800941</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>43</v>
       </c>
@@ -6816,20 +6791,20 @@
       <c r="D12" s="12">
         <v>0.75</v>
       </c>
-      <c r="E12" s="25">
-        <f>_xll.BmWToGain_dB(C12,D12)</f>
+      <c r="E12" s="25" cm="1">
+        <f t="array" ref="E12">_xll.BmWToGain_dB(C12,D12)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F12" s="25">
-        <f>_xll.StatGainWolfGain(B12,A12)</f>
+      <c r="F12" s="25" cm="1">
+        <f t="array" ref="F12">_xll.StatGainWolfGain(B12,A12)</f>
         <v>15.169687155616408</v>
       </c>
-      <c r="G12" s="25">
-        <f>_xll.StatGain(B12,A12)</f>
+      <c r="G12" s="25" cm="1">
+        <f t="array" ref="G12">_xll.StatGain(B12,A12)</f>
         <v>15.169687155616408</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>43</v>
       </c>
@@ -6842,20 +6817,20 @@
       <c r="D13" s="12">
         <v>0.75</v>
       </c>
-      <c r="E13" s="25">
-        <f>_xll.BmWToGain_dB(C13,D13)</f>
+      <c r="E13" s="25" cm="1">
+        <f t="array" ref="E13">_xll.BmWToGain_dB(C13,D13)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F13" s="25">
-        <f>_xll.StatGainWolfGain(B13,A13)</f>
+      <c r="F13" s="25" cm="1">
+        <f t="array" ref="F13">_xll.StatGainWolfGain(B13,A13)</f>
         <v>14.025749891599528</v>
       </c>
-      <c r="G13" s="25">
-        <f>_xll.StatGain(B13,A13)</f>
+      <c r="G13" s="25" cm="1">
+        <f t="array" ref="G13">_xll.StatGain(B13,A13)</f>
         <v>14.025749891599528</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>43</v>
       </c>
@@ -6868,20 +6843,20 @@
       <c r="D14" s="12">
         <v>0.75</v>
       </c>
-      <c r="E14" s="25">
-        <f>_xll.BmWToGain_dB(C14,D14)</f>
+      <c r="E14" s="25" cm="1">
+        <f t="array" ref="E14">_xll.BmWToGain_dB(C14,D14)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F14" s="25">
-        <f>_xll.StatGainWolfGain(B14,A14)</f>
+      <c r="F14" s="25" cm="1">
+        <f t="array" ref="F14">_xll.StatGainWolfGain(B14,A14)</f>
         <v>12.990932762643904</v>
       </c>
-      <c r="G14" s="25">
-        <f>_xll.StatGain(B14,A14)</f>
+      <c r="G14" s="25" cm="1">
+        <f t="array" ref="G14">_xll.StatGain(B14,A14)</f>
         <v>12.990932762643904</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>43</v>
       </c>
@@ -6894,20 +6869,20 @@
       <c r="D15" s="12">
         <v>0.75</v>
       </c>
-      <c r="E15" s="25">
-        <f>_xll.BmWToGain_dB(C15,D15)</f>
+      <c r="E15" s="25" cm="1">
+        <f t="array" ref="E15">_xll.BmWToGain_dB(C15,D15)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F15" s="25">
-        <f>_xll.StatGainWolfGain(B15,A15)</f>
+      <c r="F15" s="25" cm="1">
+        <f t="array" ref="F15">_xll.StatGainWolfGain(B15,A15)</f>
         <v>12.046218740408911</v>
       </c>
-      <c r="G15" s="25">
-        <f>_xll.StatGain(B15,A15)</f>
+      <c r="G15" s="25" cm="1">
+        <f t="array" ref="G15">_xll.StatGain(B15,A15)</f>
         <v>12.046218740408911</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>43</v>
       </c>
@@ -6920,20 +6895,20 @@
       <c r="D16" s="12">
         <v>0.75</v>
       </c>
-      <c r="E16" s="25">
-        <f>_xll.BmWToGain_dB(C16,D16)</f>
+      <c r="E16" s="25" cm="1">
+        <f t="array" ref="E16">_xll.BmWToGain_dB(C16,D16)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F16" s="25">
-        <f>_xll.StatGainWolfGain(B16,A16)</f>
+      <c r="F16" s="25" cm="1">
+        <f t="array" ref="F16">_xll.StatGainWolfGain(B16,A16)</f>
         <v>11.177166083928611</v>
       </c>
-      <c r="G16" s="25">
-        <f>_xll.StatGain(B16,A16)</f>
+      <c r="G16" s="25" cm="1">
+        <f t="array" ref="G16">_xll.StatGain(B16,A16)</f>
         <v>11.177166083928611</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>43</v>
       </c>
@@ -6946,20 +6921,20 @@
       <c r="D17" s="12">
         <v>0.75</v>
       </c>
-      <c r="E17" s="25">
-        <f>_xll.BmWToGain_dB(C17,D17)</f>
+      <c r="E17" s="25" cm="1">
+        <f t="array" ref="E17">_xll.BmWToGain_dB(C17,D17)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F17" s="25">
-        <f>_xll.StatGainWolfGain(B17,A17)</f>
+      <c r="F17" s="25" cm="1">
+        <f t="array" ref="F17">_xll.StatGainWolfGain(B17,A17)</f>
         <v>10.37254899964358</v>
       </c>
-      <c r="G17" s="25">
-        <f>_xll.StatGain(B17,A17)</f>
+      <c r="G17" s="25" cm="1">
+        <f t="array" ref="G17">_xll.StatGain(B17,A17)</f>
         <v>10.37254899964358</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>43</v>
       </c>
@@ -6972,20 +6947,20 @@
       <c r="D18" s="12">
         <v>0.75</v>
       </c>
-      <c r="E18" s="25">
-        <f>_xll.BmWToGain_dB(C18,D18)</f>
+      <c r="E18" s="25" cm="1">
+        <f t="array" ref="E18">_xll.BmWToGain_dB(C18,D18)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F18" s="25">
-        <f>_xll.StatGainWolfGain(B18,A18)</f>
+      <c r="F18" s="25" cm="1">
+        <f t="array" ref="F18">_xll.StatGainWolfGain(B18,A18)</f>
         <v>9.6234684152074976</v>
       </c>
-      <c r="G18" s="25">
-        <f>_xll.StatGain(B18,A18)</f>
+      <c r="G18" s="25" cm="1">
+        <f t="array" ref="G18">_xll.StatGain(B18,A18)</f>
         <v>9.6234684152074976</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>43</v>
       </c>
@@ -6998,20 +6973,20 @@
       <c r="D19" s="12">
         <v>0.75</v>
       </c>
-      <c r="E19" s="25">
-        <f>_xll.BmWToGain_dB(C19,D19)</f>
+      <c r="E19" s="25" cm="1">
+        <f t="array" ref="E19">_xll.BmWToGain_dB(C19,D19)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F19" s="25">
-        <f>_xll.StatGainWolfGain(B19,A19)</f>
+      <c r="F19" s="25" cm="1">
+        <f t="array" ref="F19">_xll.StatGainWolfGain(B19,A19)</f>
         <v>8.9227503252014131</v>
       </c>
-      <c r="G19" s="25">
-        <f>_xll.StatGain(B19,A19)</f>
+      <c r="G19" s="25" cm="1">
+        <f t="array" ref="G19">_xll.StatGain(B19,A19)</f>
         <v>8.9227503252014131</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>43</v>
       </c>
@@ -7024,20 +6999,20 @@
       <c r="D20" s="12">
         <v>0.75</v>
       </c>
-      <c r="E20" s="25">
-        <f>_xll.BmWToGain_dB(C20,D20)</f>
+      <c r="E20" s="25" cm="1">
+        <f t="array" ref="E20">_xll.BmWToGain_dB(C20,D20)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F20" s="25">
-        <f>_xll.StatGainWolfGain(B20,A20)</f>
+      <c r="F20" s="25" cm="1">
+        <f t="array" ref="F20">_xll.StatGainWolfGain(B20,A20)</f>
         <v>8.2645268571426804</v>
       </c>
-      <c r="G20" s="25">
-        <f>_xll.StatGain(B20,A20)</f>
+      <c r="G20" s="25" cm="1">
+        <f t="array" ref="G20">_xll.StatGain(B20,A20)</f>
         <v>8.2645268571426804</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>43</v>
       </c>
@@ -7050,20 +7025,20 @@
       <c r="D21" s="12">
         <v>0.75</v>
       </c>
-      <c r="E21" s="25">
-        <f>_xll.BmWToGain_dB(C21,D21)</f>
+      <c r="E21" s="25" cm="1">
+        <f t="array" ref="E21">_xll.BmWToGain_dB(C21,D21)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F21" s="25">
-        <f>_xll.StatGainWolfGain(B21,A21)</f>
+      <c r="F21" s="25" cm="1">
+        <f t="array" ref="F21">_xll.StatGainWolfGain(B21,A21)</f>
         <v>7.643937264016877</v>
       </c>
-      <c r="G21" s="25">
-        <f>_xll.StatGain(B21,A21)</f>
+      <c r="G21" s="25" cm="1">
+        <f t="array" ref="G21">_xll.StatGain(B21,A21)</f>
         <v>7.643937264016877</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>43</v>
       </c>
@@ -7076,20 +7051,20 @@
       <c r="D22" s="12">
         <v>0.75</v>
       </c>
-      <c r="E22" s="25">
-        <f>_xll.BmWToGain_dB(C22,D22)</f>
+      <c r="E22" s="25" cm="1">
+        <f t="array" ref="E22">_xll.BmWToGain_dB(C22,D22)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F22" s="25">
-        <f>_xll.StatGainWolfGain(B22,A22)</f>
+      <c r="F22" s="25" cm="1">
+        <f t="array" ref="F22">_xll.StatGainWolfGain(B22,A22)</f>
         <v>7.0569098677788062</v>
       </c>
-      <c r="G22" s="25">
-        <f>_xll.StatGain(B22,A22)</f>
+      <c r="G22" s="25" cm="1">
+        <f t="array" ref="G22">_xll.StatGain(B22,A22)</f>
         <v>7.0569098677788062</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>43</v>
       </c>
@@ -7102,16 +7077,16 @@
       <c r="D23" s="12">
         <v>0.75</v>
       </c>
-      <c r="E23" s="25">
-        <f>_xll.BmWToGain_dB(C23,D23)</f>
+      <c r="E23" s="25" cm="1">
+        <f t="array" ref="E23">_xll.BmWToGain_dB(C23,D23)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F23" s="25">
-        <f>_xll.StatGainWolfGain(B23,A23)</f>
+      <c r="F23" s="25" cm="1">
+        <f t="array" ref="F23">_xll.StatGainWolfGain(B23,A23)</f>
         <v>6.5</v>
       </c>
-      <c r="G23" s="25">
-        <f>_xll.StatGain(B23,A23)</f>
+      <c r="G23" s="25" cm="1">
+        <f t="array" ref="G23">_xll.StatGain(B23,A23)</f>
         <v>6.5</v>
       </c>
     </row>
@@ -7126,12 +7101,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>34</v>
       </c>
@@ -7145,8 +7120,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -7160,73 +7135,73 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="41"/>
       <c r="B3" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="23">
-        <f>_xll.Volts_to_dBuV(C3)</f>
+      <c r="D3" s="23" cm="1">
+        <f t="array" ref="D3">_xll.Volts_to_dBuV(C3)</f>
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="41"/>
       <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="23">
-        <f>_xll.Volts_to_dBV(C4)</f>
+      <c r="D4" s="23" cm="1">
+        <f t="array" ref="D4">_xll.Volts_to_dBV(C4)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="40"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="41"/>
       <c r="B5" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
       </c>
-      <c r="D5" s="23">
-        <f>_xll.dBV_to_Volts(C5)</f>
+      <c r="D5" s="23" cm="1">
+        <f t="array" ref="D5">_xll.dBV_to_Volts(C5)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="40"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="41"/>
       <c r="B6" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
       </c>
-      <c r="D6" s="23">
-        <f>_xll.dBV_to_dBuV(C6)</f>
+      <c r="D6" s="23" cm="1">
+        <f t="array" ref="D6">_xll.dBV_to_dBuV(C6)</f>
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="40"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="41"/>
       <c r="B7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2">
         <v>120</v>
       </c>
-      <c r="D7" s="23">
-        <f>_xll.dBuV_to_dBV(C7)</f>
+      <c r="D7" s="23" cm="1">
+        <f t="array" ref="D7">_xll.dBuV_to_dBV(C7)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="41" t="s">
         <v>41</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -7235,78 +7210,78 @@
       <c r="C8" s="2">
         <v>0</v>
       </c>
-      <c r="D8" s="23">
-        <f>_xll.dBm_to_Watts(C8)</f>
+      <c r="D8" s="23" cm="1">
+        <f t="array" ref="D8">_xll.dBm_to_Watts(C8)</f>
         <v>1E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="40"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="41"/>
       <c r="B9" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="2">
         <v>1E-3</v>
       </c>
-      <c r="D9" s="23">
-        <f>_xll.Watts_to_dBm(C9)</f>
+      <c r="D9" s="23" cm="1">
+        <f t="array" ref="D9">_xll.Watts_to_dBm(C9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="40"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="41"/>
       <c r="B10" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="2">
         <v>0</v>
       </c>
-      <c r="D10" s="23">
-        <f>_xll.dBW_to_Watts(C10)</f>
+      <c r="D10" s="23" cm="1">
+        <f t="array" ref="D10">_xll.dBW_to_Watts(C10)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="40"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="41"/>
       <c r="B11" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="2">
         <v>10</v>
       </c>
-      <c r="D11" s="23">
-        <f>_xll.Watts_to_dBW(C11)</f>
+      <c r="D11" s="23" cm="1">
+        <f t="array" ref="D11">_xll.Watts_to_dBW(C11)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="40"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="41"/>
       <c r="B12" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
       </c>
-      <c r="D12" s="23">
-        <f>_xll.dBW_to_dBm(C12)</f>
+      <c r="D12" s="23" cm="1">
+        <f t="array" ref="D12">_xll.dBW_to_dBm(C12)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="40"/>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="41"/>
       <c r="B13" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="2">
         <v>30</v>
       </c>
-      <c r="D13" s="23">
-        <f>_xll.dBm_to_dBW(C13)</f>
+      <c r="D13" s="23" cm="1">
+        <f t="array" ref="D13">_xll.dBm_to_dBW(C13)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="41" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -7315,78 +7290,78 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="23">
-        <f>_xll.dBuA_to_uA(C14)</f>
+      <c r="D14" s="23" cm="1">
+        <f t="array" ref="D14">_xll.dBuA_to_uA(C14)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="40"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="41"/>
       <c r="B15" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="23">
-        <f>_xll.uA_to_dBuA(C15)</f>
+      <c r="D15" s="23" cm="1">
+        <f t="array" ref="D15">_xll.uA_to_dBuA(C15)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="40"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="41"/>
       <c r="B16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
       </c>
-      <c r="D16" s="23">
-        <f>_xll.dBA_to_A(C16)</f>
+      <c r="D16" s="23" cm="1">
+        <f t="array" ref="D16">_xll.dBA_to_A(C16)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="40"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="41"/>
       <c r="B17" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
-      <c r="D17" s="23">
-        <f>_xll.A_to_dBA(C17)</f>
+      <c r="D17" s="23" cm="1">
+        <f t="array" ref="D17">_xll.A_to_dBA(C17)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="40"/>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="41"/>
       <c r="B18" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
-      <c r="D18" s="23">
-        <f>_xll.dBA_to_dBuA(C18)</f>
+      <c r="D18" s="23" cm="1">
+        <f t="array" ref="D18">_xll.dBA_to_dBuA(C18)</f>
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="40"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="41"/>
       <c r="B19" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="2">
         <v>120</v>
       </c>
-      <c r="D19" s="23">
-        <f>_xll.dBuA_to_dBA(C19)</f>
+      <c r="D19" s="23" cm="1">
+        <f t="array" ref="D19">_xll.dBuA_to_dBA(C19)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="38" t="s">
         <v>62</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -7395,156 +7370,156 @@
       <c r="C20" s="2">
         <v>0</v>
       </c>
-      <c r="D20" s="23">
-        <f>_xll.dBuVpm_to_Vpm(C20)</f>
+      <c r="D20" s="23" cm="1">
+        <f t="array" ref="D20">_xll.dBuVpm_to_Vpm(C20)</f>
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="38"/>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="39"/>
       <c r="B21" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="2">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="D21" s="23">
-        <f>_xll.Vpm_to_dBuVpm(C21)</f>
+      <c r="D21" s="23" cm="1">
+        <f t="array" ref="D21">_xll.Vpm_to_dBuVpm(C21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="38"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="39"/>
       <c r="B22" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
       </c>
-      <c r="D22" s="23">
-        <f>_xll.dBuVpm_to_dBmWpm2(C22)</f>
+      <c r="D22" s="23" cm="1">
+        <f t="array" ref="D22">_xll.dBuVpm_to_dBmWpm2(C22)</f>
         <v>-115.8</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="38"/>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="39"/>
       <c r="B23" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C23" s="2">
         <v>-115.8</v>
       </c>
-      <c r="D23" s="23">
-        <f>_xll.dBmWpm2_to_dBuVpm(C23)</f>
+      <c r="D23" s="23" cm="1">
+        <f t="array" ref="D23">_xll.dBmWpm2_to_dBuVpm(C23)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="38"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="39"/>
       <c r="B24" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
       </c>
-      <c r="D24" s="23">
-        <f>_xll.dBuVpm_to_dBuApm(C24)</f>
+      <c r="D24" s="23" cm="1">
+        <f t="array" ref="D24">_xll.dBuVpm_to_dBuApm(C24)</f>
         <v>-51.5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="38"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="39"/>
       <c r="B25" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C25" s="2">
         <v>-51.5</v>
       </c>
-      <c r="D25" s="23">
-        <f>_xll.dBuApm_to_dBuVpm(C25)</f>
+      <c r="D25" s="23" cm="1">
+        <f t="array" ref="D25">_xll.dBuApm_to_dBuVpm(C25)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="38"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="39"/>
       <c r="B26" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
       </c>
-      <c r="D26" s="23">
-        <f>_xll.dBuApm_to_dBpT(C26)</f>
+      <c r="D26" s="23" cm="1">
+        <f t="array" ref="D26">_xll.dBuApm_to_dBpT(C26)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="38"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="39"/>
       <c r="B27" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C27" s="2">
         <v>2</v>
       </c>
-      <c r="D27" s="23">
-        <f>_xll.dBpT_to_dBuApm(C27)</f>
+      <c r="D27" s="23" cm="1">
+        <f t="array" ref="D27">_xll.dBpT_to_dBuApm(C27)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="38"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="39"/>
       <c r="B28" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C28" s="2">
         <v>10</v>
       </c>
-      <c r="D28" s="23">
-        <f>_xll.Wpm2_to_Vpm(C28)</f>
+      <c r="D28" s="23" cm="1">
+        <f t="array" ref="D28">_xll.Wpm2_to_Vpm(C28)</f>
         <v>61.400325732035007</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="38"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="39"/>
       <c r="B29" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="2">
         <v>61.400325732035007</v>
       </c>
-      <c r="D29" s="23">
-        <f>_xll.Vpm_to_Wpm2(C29)</f>
+      <c r="D29" s="23" cm="1">
+        <f t="array" ref="D29">_xll.Vpm_to_Wpm2(C29)</f>
         <v>10.000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="38"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="39"/>
       <c r="B30" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C30" s="2">
         <v>10</v>
       </c>
-      <c r="D30" s="23">
-        <f>_xll.uT_to_Apm(C30)</f>
+      <c r="D30" s="23" cm="1">
+        <f t="array" ref="D30">_xll.uT_to_Apm(C30)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="40"/>
       <c r="B31" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C31" s="2">
         <v>8</v>
       </c>
-      <c r="D31" s="23">
-        <f>_xll.Apm_to_uT(C31)</f>
+      <c r="D31" s="23" cm="1">
+        <f t="array" ref="D31">_xll.Apm_to_uT(C31)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="37" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="38" t="s">
         <v>71</v>
       </c>
       <c r="B32" s="5" t="s">
@@ -7553,104 +7528,104 @@
       <c r="C32" s="2">
         <v>1</v>
       </c>
-      <c r="D32" s="23">
-        <f>_xll.Feet_to_Meters(C32)</f>
+      <c r="D32" s="23" cm="1">
+        <f t="array" ref="D32">_xll.Feet_to_Meters(C32)</f>
         <v>0.30480370641306997</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="38"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="39"/>
       <c r="B33" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C33" s="2">
         <v>0.30480370641306997</v>
       </c>
-      <c r="D33" s="23">
-        <f>_xll.Meters_to_Feet(C33)</f>
+      <c r="D33" s="23" cm="1">
+        <f t="array" ref="D33">_xll.Meters_to_Feet(C33)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="38"/>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="39"/>
       <c r="B34" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
       </c>
-      <c r="D34" s="23">
-        <f>_xll.Miles_to_Kilometers(C34)</f>
+      <c r="D34" s="23" cm="1">
+        <f t="array" ref="D34">_xll.Miles_to_Kilometers(C34)</f>
         <v>1.6093440000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="38"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="39"/>
       <c r="B35" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C35" s="2">
         <v>1.6093440000000001</v>
       </c>
-      <c r="D35" s="23">
-        <f>_xll.Kilometeres_to_Miles(C35)</f>
+      <c r="D35" s="23" cm="1">
+        <f t="array" ref="D35">_xll.Kilometeres_to_Miles(C35)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="38"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="39"/>
       <c r="B36" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
       </c>
-      <c r="D36" s="23">
-        <f>_xll.Feet_to_Miles(C36)</f>
+      <c r="D36" s="23" cm="1">
+        <f t="array" ref="D36">_xll.Feet_to_Miles(C36)</f>
         <v>1.8939393939393939E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="38"/>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="39"/>
       <c r="B37" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C37" s="2">
         <v>1.8939393939393939E-4</v>
       </c>
-      <c r="D37" s="23">
-        <f>_xll.Miles_to_Feet(C37)</f>
+      <c r="D37" s="23" cm="1">
+        <f t="array" ref="D37">_xll.Miles_to_Feet(C37)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="38"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="39"/>
       <c r="B38" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
       </c>
-      <c r="D38" s="23">
-        <f>_xll.Meters_to_Kilometers(C38)</f>
+      <c r="D38" s="23" cm="1">
+        <f t="array" ref="D38">_xll.Meters_to_Kilometers(C38)</f>
         <v>1E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="39"/>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="40"/>
       <c r="B39" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C39" s="2">
         <v>1E-3</v>
       </c>
-      <c r="D39" s="23">
-        <f>_xll.Kilometers_to_Meters(C39)</f>
+      <c r="D39" s="23" cm="1">
+        <f t="array" ref="D39">_xll.Kilometers_to_Meters(C39)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="40" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="41" t="s">
         <v>78</v>
       </c>
       <c r="B40" s="5" t="s">
@@ -7659,77 +7634,77 @@
       <c r="C40" s="2">
         <v>212</v>
       </c>
-      <c r="D40" s="23">
-        <f>_xll.Fahrenheit_to_Celsius(C40)</f>
+      <c r="D40" s="23" cm="1">
+        <f t="array" ref="D40">_xll.Fahrenheit_to_Celsius(C40)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="40"/>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="41"/>
       <c r="B41" s="5" t="s">
         <v>73</v>
       </c>
       <c r="C41" s="2">
         <v>100</v>
       </c>
-      <c r="D41" s="23">
-        <f>_xll.Celsius_to_Fahrenheit(C41)</f>
+      <c r="D41" s="23" cm="1">
+        <f t="array" ref="D41">_xll.Celsius_to_Fahrenheit(C41)</f>
         <v>212</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="40"/>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="41"/>
       <c r="B42" s="5" t="s">
         <v>74</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
       </c>
-      <c r="D42" s="23">
-        <f>_xll.Celsius_to_Kelvin(C42)</f>
+      <c r="D42" s="23" cm="1">
+        <f t="array" ref="D42">_xll.Celsius_to_Kelvin(C42)</f>
         <v>273.14999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="40"/>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="41"/>
       <c r="B43" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C43" s="2">
         <v>273.14999999999998</v>
       </c>
-      <c r="D43" s="23">
-        <f>_xll.Kelvin_to_Celsius(C43)</f>
+      <c r="D43" s="23" cm="1">
+        <f t="array" ref="D43">_xll.Kelvin_to_Celsius(C43)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="40"/>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="41"/>
       <c r="B44" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C44" s="2">
         <v>32</v>
       </c>
-      <c r="D44" s="23">
-        <f>_xll.Fahrenheit_to_Kelvin(C44)</f>
+      <c r="D44" s="23" cm="1">
+        <f t="array" ref="D44">_xll.Fahrenheit_to_Kelvin(C44)</f>
         <v>273.70555555555552</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="40"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="41"/>
       <c r="B45" s="5" t="s">
         <v>77</v>
       </c>
       <c r="C45" s="2">
         <v>273.70555555555552</v>
       </c>
-      <c r="D45" s="23">
-        <f>_xll.Kelvin_to_Fahrenheit(C45)</f>
+      <c r="D45" s="23" cm="1">
+        <f t="array" ref="D45">_xll.Kelvin_to_Fahrenheit(C45)</f>
         <v>32.999999999999979</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>80</v>
       </c>
@@ -7739,8 +7714,8 @@
       <c r="C46" s="2">
         <v>3.5</v>
       </c>
-      <c r="D46" s="23">
-        <f>_xll.gpm3_to_hPa(C46, 273.15)</f>
+      <c r="D46" s="23" cm="1">
+        <f t="array" ref="D46">_xll.gpm3_to_hPa(C46, 273.15)</f>
         <v>4.411744347023534</v>
       </c>
     </row>
@@ -7761,52 +7736,51 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="G1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="B2" s="2">
         <v>39.4</v>
@@ -7830,9 +7804,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B3" s="2">
         <v>39.130000000000003</v>
@@ -7856,9 +7830,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B4" s="2">
         <v>39.18</v>
@@ -7882,9 +7856,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B5" s="2">
         <v>39.369999999999997</v>
@@ -7908,7 +7882,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
         <v>83</v>
       </c>
@@ -7919,31 +7893,25 @@
         <v>89</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>123</v>
+        <v>195</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>197</v>
+        <v>85</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="L11" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>87</v>
       </c>
@@ -7956,37 +7924,29 @@
       <c r="D12" s="2">
         <v>10</v>
       </c>
-      <c r="E12" s="23">
-        <f>ROUND(_xll.TerrainHeight_m(B12,C12,TerHandler,TerDirectory),0)</f>
-        <v>215</v>
-      </c>
-      <c r="F12" s="23">
-        <f>ROUND(_xll.RadioHorizon_Km(D12),3)</f>
+      <c r="E12" s="23" cm="1">
+        <f t="array" ref="E12">ROUND(_xll.RadioHorizon_Km(D12),3)</f>
         <v>11.289</v>
       </c>
+      <c r="F12" s="2">
+        <v>39.634782999999999</v>
+      </c>
       <c r="G12" s="2">
-        <v>39.634782999999999</v>
+        <v>-78.231067999999993</v>
       </c>
       <c r="H12" s="2">
-        <v>-78.231067999999993</v>
-      </c>
-      <c r="I12" s="2">
         <v>20</v>
       </c>
-      <c r="J12" s="23">
-        <f>ROUND(_xll.TerrainHeight_m(G12,H12,TerHandler,TerDirectory),0)</f>
-        <v>230</v>
-      </c>
-      <c r="K12" s="23">
-        <f>ROUND(_xll.RadioHorizon_Km(I12),3)</f>
+      <c r="I12" s="23" cm="1">
+        <f t="array" ref="I12">ROUND(_xll.RadioHorizon_Km(H12),3)</f>
         <v>15.965999999999999</v>
       </c>
-      <c r="L12" s="23" t="str">
-        <f>"Distance: " &amp; ROUND(_xll.DistKm(B12,C12,G12,H12),3) &amp; " Km"</f>
+      <c r="J12" s="23" t="str" cm="1">
+        <f t="array" ref="J12">"Distance: " &amp; ROUND(_xll.DistKm(B12,C12,F12,G12),3) &amp; " Km"</f>
         <v>Distance: 104.891 Km</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>88</v>
       </c>
@@ -7999,37 +7959,29 @@
       <c r="D13" s="2">
         <v>10</v>
       </c>
-      <c r="E13" s="23">
-        <f>ROUND(_xll.TerrainHeight_m(B13,C13,TerHandler,TerDirectory),0)</f>
-        <v>215</v>
-      </c>
-      <c r="F13" s="23">
-        <f>ROUND(_xll.RadioHorizon_Km(D13),3)</f>
+      <c r="E13" s="23" cm="1">
+        <f t="array" ref="E13">ROUND(_xll.RadioHorizon_Km(D13),3)</f>
         <v>11.289</v>
       </c>
+      <c r="F13" s="2">
+        <v>39.634782999999999</v>
+      </c>
       <c r="G13" s="2">
-        <v>39.634782999999999</v>
+        <v>-78.231067999999993</v>
       </c>
       <c r="H13" s="2">
-        <v>-78.231067999999993</v>
-      </c>
-      <c r="I13" s="2">
         <v>20</v>
       </c>
-      <c r="J13" s="23">
-        <f>ROUND(_xll.TerrainHeight_m(G13,H13,TerHandler,TerDirectory),0)</f>
-        <v>230</v>
-      </c>
-      <c r="K13" s="23">
-        <f>ROUND(_xll.RadioHorizon_Km(I13),3)</f>
+      <c r="I13" s="23" cm="1">
+        <f t="array" ref="I13">ROUND(_xll.RadioHorizon_Km(H13),3)</f>
         <v>15.965999999999999</v>
       </c>
-      <c r="L13" s="23" t="str">
-        <f>"Bearing: " &amp; ROUND(_xll.Bearing(B13,C13,G13,H13),2) &amp; " Deg"</f>
-        <v>Bearing: 274.54 Deg</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J13" s="23" t="str" cm="1">
+        <f t="array" ref="J13">"Distance: " &amp; ROUND(_xll.DistKm(B13,C13,F13,G13),3) &amp; " Km"</f>
+        <v>Distance: 104.891 Km</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>88</v>
       </c>
@@ -8042,37 +7994,29 @@
       <c r="D14" s="2">
         <v>20</v>
       </c>
-      <c r="E14" s="23">
-        <f>ROUND(_xll.TerrainHeight_m(B14,C14,TerHandler,TerDirectory),0)</f>
-        <v>230</v>
-      </c>
-      <c r="F14" s="23">
-        <f>ROUND(_xll.RadioHorizon_Km(D14),3)</f>
+      <c r="E14" s="23" cm="1">
+        <f t="array" ref="E14">ROUND(_xll.RadioHorizon_Km(D14),3)</f>
         <v>15.965999999999999</v>
       </c>
+      <c r="F14" s="2">
+        <v>39.566355999999999</v>
+      </c>
       <c r="G14" s="2">
-        <v>39.566355999999999</v>
+        <v>-77.013035000000002</v>
       </c>
       <c r="H14" s="2">
-        <v>-77.013035000000002</v>
-      </c>
-      <c r="I14" s="2">
         <v>10</v>
       </c>
-      <c r="J14" s="23">
-        <f>ROUND(_xll.TerrainHeight_m(G14,H14,TerHandler,TerDirectory),0)</f>
-        <v>215</v>
-      </c>
-      <c r="K14" s="23">
-        <f>ROUND(_xll.RadioHorizon_Km(I14),3)</f>
+      <c r="I14" s="23" cm="1">
+        <f t="array" ref="I14">ROUND(_xll.RadioHorizon_Km(H14),3)</f>
         <v>11.289</v>
       </c>
-      <c r="L14" s="23" t="str">
-        <f>"Bearing: " &amp; ROUND(_xll.Bearing(B14,C14,G14,H14),2) &amp; " Deg"</f>
-        <v>Bearing: 93.77 Deg</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J14" s="23" t="str" cm="1">
+        <f t="array" ref="J14">"Distance: " &amp; ROUND(_xll.DistKm(B14,C14,F14,G14),3) &amp; " Km"</f>
+        <v>Distance: 104.891 Km</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>91</v>
       </c>
@@ -8085,39 +8029,31 @@
       <c r="D15" s="2">
         <v>10</v>
       </c>
-      <c r="E15" s="23">
-        <f>ROUND(_xll.TerrainHeight_m(B15,C15,TerHandler,TerDirectory),0)</f>
-        <v>215</v>
-      </c>
-      <c r="F15" s="23">
-        <f>ROUND(_xll.RadioHorizon_Km(D15),3)</f>
+      <c r="E15" s="23" cm="1">
+        <f t="array" ref="E15">ROUND(_xll.RadioHorizon_Km(D15),3)</f>
         <v>11.289</v>
       </c>
+      <c r="F15" s="2">
+        <v>39.634782999999999</v>
+      </c>
       <c r="G15" s="2">
-        <v>39.634782999999999</v>
+        <v>-78.231067999999993</v>
       </c>
       <c r="H15" s="2">
-        <v>-78.231067999999993</v>
-      </c>
-      <c r="I15" s="2">
         <v>20</v>
       </c>
-      <c r="J15" s="23">
-        <f>ROUND(_xll.TerrainHeight_m(G15,H15,TerHandler,TerDirectory),0)</f>
-        <v>230</v>
-      </c>
-      <c r="K15" s="23">
-        <f>ROUND(_xll.RadioHorizon_Km(I15),3)</f>
+      <c r="I15" s="23" cm="1">
+        <f t="array" ref="I15">ROUND(_xll.RadioHorizon_Km(H15),3)</f>
         <v>15.965999999999999</v>
       </c>
-      <c r="L15" s="23" t="str">
-        <f>"Is LOS: " &amp; _xll.IsLOS(B15,C15,G15,H15,D15,I15,0,TerDirectory)</f>
-        <v>Is LOS: FALSE</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J15" s="23" t="str" cm="1">
+        <f t="array" ref="J15">"Distance: " &amp; ROUND(_xll.DistKm(B15,C15,F15,G15),3) &amp; " Km"</f>
+        <v>Distance: 104.891 Km</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -8127,10 +8063,8 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="23" t="str">
-        <f>"Delta Bearing: " &amp;ROUND( _xll.Delta_Bearing(_xll.Bearing(B13,C13,G13,H13), _xll.Bearing(B14,C14,G14,H14)),2) &amp; " Deg"</f>
+      <c r="J16" s="23" t="str" cm="1">
+        <f t="array" ref="J16">"Delta Bearing: " &amp;ROUND(_xll.Delta_Bearing(_xll.Bearing(B13,C13,F13,G13), _xll.Bearing(B14,C14,F14,G14)),2) &amp; " Deg"</f>
         <v>Delta Bearing: 179.22 Deg</v>
       </c>
     </row>
@@ -8141,93 +8075,84 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr codeName="Sheet6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2226CAC0-AF79-44C0-AA2A-1A7BFBA387F4}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.85546875" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B2" s="2">
-        <v>456.07499999999999</v>
+        <v>146.94</v>
       </c>
       <c r="C2" s="2">
-        <v>456.57499999999999</v>
+        <v>147.06</v>
       </c>
       <c r="D2" s="2">
-        <v>456.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>147.18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B3" s="2">
-        <v>461.55</v>
+        <v>146.52000000000001</v>
       </c>
       <c r="C3" s="2">
-        <v>456.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>147.18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B4" s="2">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="C4" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B6" s="26" t="str">
-        <f>_xll.IntermodHarmonics(B2:D2,B3:C3,B4:C4)</f>
-        <v xml:space="preserve"> Harmonic Found---&gt;    1 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
- Harmonic Found---&gt;    1 (456.1) = 456.1 ± 0.1 MHz bandwidth</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="B6" s="26" t="str" cm="1">
+        <f t="array" ref="B6">_xll.IntermodHarmonics(B2:D2,B3:C3,B4:C4)</f>
+        <v xml:space="preserve"> Harmonic Found---&gt;    1 (147.18) = 147.18 ± 0.02 MHz bandwidth</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="26" t="str">
-        <f>_xll.IntermodTwoSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
-        <v xml:space="preserve"> INTERMOD---&gt;   2 (456.075) - 1 (456.1) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   3 (456.075) - 2 (456.1) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   2 (456.1) - 1 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   3 (456.1) - 2 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   4 (456.1) - 3 (456.075) = 456.1 ± 0.1 MHz bandwidth</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="B7" s="26" t="str" cm="1">
+        <f t="array" ref="B7">_xll.IntermodTwoSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
+        <v xml:space="preserve"> INTERMOD---&gt;   2 (147.06) - 1 (146.94) = 147.18 ± 0.02 MHz bandwidth</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="B8" s="26" t="str">
-        <f>_xll.IntermodThreeSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
-        <v xml:space="preserve"> INTERMOD---&gt;   2 (456.075) - 1 (456.1) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   3 (456.075) - 2 (456.1) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   2 (456.1) - 1 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   3 (456.1) - 2 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   4 (456.1) - 3 (456.075) = 456.1 ± 0.1 MHz bandwidth</v>
+        <v>199</v>
+      </c>
+      <c r="B8" s="31" t="str" cm="1">
+        <f t="array" ref="B8">_xll.IntermodThreeSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
+        <v xml:space="preserve"> INTERMOD---&gt;   4 (147.06) - 2 (146.94) - 1 (147.18) = 147.18 ± 0.02 MHz bandwidth_x000D_
+ INTERMOD---&gt;   2 (147.18) - 2 (147.06) + 1 (146.94) = 147.18 ± 0.02 MHz bandwidth</v>
       </c>
     </row>
   </sheetData>
@@ -8240,48 +8165,143 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="2">
+        <v>456.07499999999999</v>
+      </c>
+      <c r="C2" s="2">
+        <v>456.57499999999999</v>
+      </c>
+      <c r="D2" s="2">
+        <v>456.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="2">
+        <v>461.55</v>
+      </c>
+      <c r="C3" s="2">
+        <v>456.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" s="26" t="str" cm="1">
+        <f t="array" ref="B6">_xll.IntermodHarmonics(B2:D2,B3:C3,B4:C4)</f>
+        <v xml:space="preserve"> Harmonic Found---&gt;    1 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
+ Harmonic Found---&gt;    1 (456.1) = 456.1 ± 0.1 MHz bandwidth</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="26" t="str" cm="1">
+        <f t="array" ref="B7">_xll.IntermodTwoSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
+        <v xml:space="preserve"> INTERMOD---&gt;   2 (456.075) - 1 (456.1) = 456.1 ± 0.1 MHz bandwidth_x000D_
+ INTERMOD---&gt;   3 (456.075) - 2 (456.1) = 456.1 ± 0.1 MHz bandwidth_x000D_
+ INTERMOD---&gt;   2 (456.1) - 1 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
+ INTERMOD---&gt;   3 (456.1) - 2 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
+ INTERMOD---&gt;   4 (456.1) - 3 (456.075) = 456.1 ± 0.1 MHz bandwidth</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" s="31" t="str" cm="1">
+        <f t="array" ref="B8">_xll.IntermodThreeSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87334F41-6ACF-41B1-9BF9-AAB07931F740}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" t="s">
         <v>210</v>
-      </c>
-      <c r="B1" s="42" t="s">
-        <v>211</v>
-      </c>
-      <c r="C1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="42" t="s">
-        <v>211</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B2" t="s">
-        <v>213</v>
       </c>
       <c r="C2">
         <v>25.032406999999999</v>
@@ -8290,7 +8310,7 @@
         <v>-77.356269999999995</v>
       </c>
       <c r="E2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F2">
         <v>24.707910999999999</v>
@@ -8299,12 +8319,12 @@
         <v>-77.765840999999995</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>216</v>
+        <v>212</v>
+      </c>
+      <c r="B3" t="s">
+        <v>213</v>
       </c>
       <c r="C3">
         <v>11.552263999999999</v>
@@ -8313,7 +8333,7 @@
         <v>104.937893</v>
       </c>
       <c r="E3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F3">
         <v>10.991194999999999</v>
@@ -8322,12 +8342,12 @@
         <v>104.77869099999999</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C4">
         <v>30.040597000000002</v>
@@ -8336,7 +8356,7 @@
         <v>31.235703000000001</v>
       </c>
       <c r="E4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F4">
         <v>30.458936000000001</v>
@@ -8345,12 +8365,12 @@
         <v>31.181923999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C5">
         <v>5.5423049999999998</v>
@@ -8359,7 +8379,7 @@
         <v>-0.20711499999999999</v>
       </c>
       <c r="E5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F5">
         <v>6.1462409999999998</v>
@@ -8368,12 +8388,12 @@
         <v>1.5762999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C6">
         <v>14.078479</v>
@@ -8382,7 +8402,7 @@
         <v>-87.185700999999995</v>
       </c>
       <c r="E6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F6">
         <v>13.803167999999999</v>
@@ -8391,12 +8411,12 @@
         <v>-87.258123999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C7">
         <v>17.977149000000001</v>
@@ -8405,7 +8425,7 @@
         <v>-76.812903000000006</v>
       </c>
       <c r="E7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F7">
         <v>17.947472000000001</v>
@@ -8414,12 +8434,12 @@
         <v>-77.240453000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C8">
         <v>27.729265999999999</v>
@@ -8428,7 +8448,7 @@
         <v>85.302627999999999</v>
       </c>
       <c r="E8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F8">
         <v>27.615233</v>
@@ -8437,12 +8457,12 @@
         <v>85.559207999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C9">
         <v>9.0569520000000008</v>
@@ -8451,7 +8471,7 @@
         <v>7.4993379999999998</v>
       </c>
       <c r="E9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F9">
         <v>8.8449989999999996</v>
@@ -8460,12 +8480,12 @@
         <v>7.8724879999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C10">
         <v>13.154978</v>
@@ -8474,7 +8494,7 @@
         <v>-61.227837000000001</v>
       </c>
       <c r="E10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F10">
         <v>13.025244000000001</v>
@@ -8483,12 +8503,12 @@
         <v>-61.232104999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B11" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C11">
         <v>8.4868369999999995</v>
@@ -8497,7 +8517,7 @@
         <v>-13.231096000000001</v>
       </c>
       <c r="E11" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F11">
         <v>8.3802179999999993</v>
@@ -8506,12 +8526,12 @@
         <v>-13.134311</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C12">
         <v>17.293337999999999</v>
@@ -8520,7 +8540,7 @@
         <v>-62.722065999999998</v>
       </c>
       <c r="E12" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F12">
         <v>17.136043999999998</v>
@@ -8529,12 +8549,12 @@
         <v>-62.626285000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B13" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C13">
         <v>0.33255699999999999</v>
@@ -8543,7 +8563,7 @@
         <v>32.575284000000003</v>
       </c>
       <c r="E13" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F13">
         <v>6.0284999999999998E-2</v>

--- a/MSAMtoExcel_Sample.xlsx
+++ b/MSAMtoExcel_Sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/700f8b47762a8359/Documents/Fred/Temp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FNajmy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{82E1E936-CF85-4E33-BC44-2D54D544A112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2363B8C3-0311-475E-84F4-9313FE91B908}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04852578-51C7-4527-B6FC-B87B98968703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Propagation" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,7 @@
     <sheet name="Antenna" sheetId="4" r:id="rId3"/>
     <sheet name="Conversion Functions" sheetId="2" r:id="rId4"/>
     <sheet name="Geographic" sheetId="3" r:id="rId5"/>
-    <sheet name="Intermod (2)" sheetId="8" r:id="rId6"/>
-    <sheet name="Intermod" sheetId="6" r:id="rId7"/>
-    <sheet name="Sample Locations" sheetId="7" r:id="rId8"/>
+    <sheet name="Intermod" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="TerDirectory">Propagation!$Z$8</definedName>
@@ -69,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="208">
   <si>
     <t>TxLat</t>
   </si>
@@ -726,121 +724,7 @@
     <t>Rx Freq (MHz)</t>
   </si>
   <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Bahamas</t>
-  </si>
-  <si>
-    <t>Nassau</t>
-  </si>
-  <si>
-    <t>Andros Town</t>
-  </si>
-  <si>
-    <t>Cambodia</t>
-  </si>
-  <si>
-    <t>Phnom Penh</t>
-  </si>
-  <si>
-    <t>Krong Doun Kaev</t>
-  </si>
-  <si>
-    <t>Egypt</t>
-  </si>
-  <si>
-    <t>Cairo</t>
-  </si>
-  <si>
-    <t>Banha</t>
-  </si>
-  <si>
-    <t>Ghana</t>
-  </si>
-  <si>
-    <t>Accra</t>
-  </si>
-  <si>
-    <t>Krobo Odumasi</t>
-  </si>
-  <si>
-    <t>Honduras</t>
-  </si>
-  <si>
-    <t>Tegucigalpa</t>
-  </si>
-  <si>
-    <t>Sabana Grande</t>
-  </si>
-  <si>
-    <t>Jamaica</t>
-  </si>
-  <si>
-    <t>Kingston</t>
-  </si>
-  <si>
-    <t>Curatoe Hill</t>
-  </si>
-  <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>Kathmandu</t>
-  </si>
-  <si>
-    <t>Dhulikhel</t>
-  </si>
-  <si>
-    <t>Nigeria</t>
-  </si>
-  <si>
-    <t>Abuja</t>
-  </si>
-  <si>
-    <t>Keffi</t>
-  </si>
-  <si>
-    <t>Saint Vincent and the Grenadines</t>
-  </si>
-  <si>
-    <t>Kingstown</t>
-  </si>
-  <si>
-    <t>Spring Estate</t>
-  </si>
-  <si>
-    <t>Sierra Leone</t>
-  </si>
-  <si>
-    <t>Freetown</t>
-  </si>
-  <si>
-    <t>Hastings</t>
-  </si>
-  <si>
-    <t>St Kitts&amp; Nevis</t>
-  </si>
-  <si>
-    <t>Basseterre</t>
-  </si>
-  <si>
-    <t>Charlestown</t>
-  </si>
-  <si>
-    <t>Uganda</t>
-  </si>
-  <si>
-    <t>Kampala</t>
-  </si>
-  <si>
-    <t>Kitoro</t>
-  </si>
-  <si>
-    <t>F:\USGS</t>
+    <t>C:\USGS</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +915,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1082,7 +966,6 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1794,52 +1677,52 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>135.42766979138744</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>135.95371367721219</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>136.44968437376377</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>136.91883544733909</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>137.36391944334778</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>137.78728575442187</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>138.1909557003485</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>138.57668090486609</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>138.94598923918485</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>139.30022138052666</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>139.64056019618354</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>139.96805457904148</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>140.2836389462158</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>140.58814931456496</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>140.88233664983366</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>141.16687802613515</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4615,10 +4498,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4884,18 +4763,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A2:AI38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="9.109375" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.6640625" customWidth="1"/>
-    <col min="16" max="16" width="9.88671875" customWidth="1"/>
-    <col min="17" max="17" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:35" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -4981,7 +4860,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="29">
         <v>8000</v>
       </c>
@@ -5040,42 +4919,42 @@
         <v>0.5</v>
       </c>
       <c r="T3" s="23" cm="1">
-        <f t="array" ref="T3">_xll.MSAM.Celsius_to_Kelvin(15)</f>
+        <f t="array" ref="T3">_xll.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
       <c r="U3" s="23" cm="1">
-        <f t="array" ref="U3">_xll.MSAM.gpm3_to_hPa(7.5,T3)</f>
+        <f t="array" ref="U3">_xll.gpm3_to_hPa(7.5,T3)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V3" s="29">
         <v>1013.25</v>
       </c>
       <c r="W3" s="23" cm="1">
-        <f t="array" ref="W3">_xll.MSAM.DistKm(B3,C3,E3,F3)</f>
-        <v>17.76476411326168</v>
-      </c>
-      <c r="X3" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="X3" ca="1">_xll.MSAM.IsLOS(B3,C3,E3,F3,D3,G3,1,TerDirectory)</f>
-        <v>#NAME?</v>
+        <f t="array" ref="W3">_xll.DistKm(B3,C3,E3,F3)</f>
+        <v>17.76476411326108</v>
+      </c>
+      <c r="X3" s="23" t="b" cm="1">
+        <f t="array" ref="X3">_xll.IsLOS(B3,C3,E3,F3,D3,G3,1,TerDirectory)</f>
+        <v>1</v>
       </c>
       <c r="Y3" s="23" cm="1">
-        <f t="array" ref="Y3">_xll.MSAM.FreeSpace(W3,A3)</f>
-        <v>135.50298864283729</v>
-      </c>
-      <c r="Z3" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="Z3" ca="1">_xll.MSAM.ITMPointToPoint(D3,G3,B3,C3,E3,F3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
+        <f t="array" ref="Y3">_xll.FreeSpace(W3,A3)</f>
+        <v>135.50298864283701</v>
+      </c>
+      <c r="Z3" s="23" cm="1">
+        <f t="array" ref="Z3">_xll.ITMPointToPoint(D3,G3,B3,C3,E3,F3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100,TerHandler,TerDirectory)</f>
+        <v>135.42766979138744</v>
       </c>
       <c r="AA3" s="23" cm="1">
-        <f t="array" ref="AA3">_xll.MSAM.ITMArea(D3,G3,N3,O3,W3,L3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100)</f>
-        <v>137.74535973059869</v>
+        <f t="array" ref="AA3">_xll.ITMArea(D3,G3,N3,O3,W3,L3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100)</f>
+        <v>137.74535973059781</v>
       </c>
       <c r="AB3" s="23" cm="1">
-        <f t="array" ref="AB3">_xll.MSAM.P676_SpecificAttenuation_dB(A3/1000,T3,U3,V3,W3)</f>
-        <v>0.20280107795332591</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+        <f t="array" ref="AB3">_xll.P676_SpecificAttenuation_dB(A3/1000,T3,U3,V3,W3)</f>
+        <v>0.20280107795331906</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>7400</v>
       </c>
@@ -5134,42 +5013,42 @@
         <v>0.5</v>
       </c>
       <c r="T4" s="23" cm="1">
-        <f t="array" ref="T4">_xll.MSAM.Celsius_to_Kelvin(15)</f>
+        <f t="array" ref="T4">_xll.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
       <c r="U4" s="23" cm="1">
-        <f t="array" ref="U4">_xll.MSAM.gpm3_to_hPa(7.5,T4)</f>
+        <f t="array" ref="U4">_xll.gpm3_to_hPa(7.5,T4)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V4" s="2">
         <v>1013.25</v>
       </c>
       <c r="W4" s="23" cm="1">
-        <f t="array" ref="W4">_xll.MSAM.DistKm(B4,C4,E4,F4)</f>
-        <v>104.89071248171265</v>
-      </c>
-      <c r="X4" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="X4" ca="1">_xll.MSAM.IsLOS(B4,C4,E4,F4,D4,G4,1,TerDirectory)</f>
-        <v>#NAME?</v>
+        <f t="array" ref="W4">_xll.DistKm(B4,C4,E4,F4)</f>
+        <v>104.89071248171258</v>
+      </c>
+      <c r="X4" s="23" t="b" cm="1">
+        <f t="array" ref="X4">_xll.IsLOS(B4,C4,E4,F4,D4,G4,1,TerDirectory)</f>
+        <v>0</v>
       </c>
       <c r="Y4" s="23" cm="1">
-        <f t="array" ref="Y4">_xll.MSAM.FreeSpace(W4,A4)</f>
+        <f t="array" ref="Y4">_xll.FreeSpace(W4,A4)</f>
         <v>150.24937510291187</v>
       </c>
-      <c r="Z4" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="Z4" ca="1">_xll.MSAM.ITMPointToPoint(D4,G4,B4,C4,E4,F4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
+      <c r="Z4" s="23" cm="1">
+        <f t="array" ref="Z4">_xll.ITMPointToPoint(D4,G4,B4,C4,E4,F4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100,TerHandler,TerDirectory)</f>
+        <v>247.81390859953319</v>
       </c>
       <c r="AA4" s="23" cm="1">
-        <f t="array" ref="AA4">_xll.MSAM.ITMArea(D4,G4,N4,O4,W4,L4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100)</f>
+        <f t="array" ref="AA4">_xll.ITMArea(D4,G4,N4,O4,W4,L4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100)</f>
         <v>210.22674503575132</v>
       </c>
       <c r="AB4" s="23" cm="1">
-        <f t="array" ref="AB4">_xll.MSAM.P676_SpecificAttenuation_dB(A4/1000,T4,U4,V4,W4)</f>
-        <v>1.1280677803367012</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+        <f t="array" ref="AB4">_xll.P676_SpecificAttenuation_dB(A4/1000,T4,U4,V4,W4)</f>
+        <v>1.1280677803367003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>7600</v>
       </c>
@@ -5228,42 +5107,42 @@
         <v>0.5</v>
       </c>
       <c r="T5" s="23" cm="1">
-        <f t="array" ref="T5">_xll.MSAM.Celsius_to_Kelvin(15)</f>
+        <f t="array" ref="T5">_xll.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
       <c r="U5" s="23" cm="1">
-        <f t="array" ref="U5">_xll.MSAM.gpm3_to_hPa(7.5,T5)</f>
+        <f t="array" ref="U5">_xll.gpm3_to_hPa(7.5,T5)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V5" s="2">
         <v>1013.25</v>
       </c>
       <c r="W5" s="23" cm="1">
-        <f t="array" ref="W5">_xll.MSAM.DistKm(B5,C5,E5,F5)</f>
-        <v>104.89071248171265</v>
-      </c>
-      <c r="X5" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="X5" ca="1">_xll.MSAM.IsLOS(B5,C5,E5,F5,D5,G5,1,TerDirectory)</f>
-        <v>#NAME?</v>
+        <f t="array" ref="W5">_xll.DistKm(B5,C5,E5,F5)</f>
+        <v>104.89071248171258</v>
+      </c>
+      <c r="X5" s="23" t="b" cm="1">
+        <f t="array" ref="X5">_xll.IsLOS(B5,C5,E5,F5,D5,G5,1,TerDirectory)</f>
+        <v>0</v>
       </c>
       <c r="Y5" s="23" cm="1">
-        <f t="array" ref="Y5">_xll.MSAM.FreeSpace(W5,A5)</f>
+        <f t="array" ref="Y5">_xll.FreeSpace(W5,A5)</f>
         <v>150.48101255390816</v>
       </c>
-      <c r="Z5" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="Z5" ca="1">_xll.MSAM.ITMPointToPoint(D5,G5,B5,C5,E5,F5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
+      <c r="Z5" s="23" cm="1">
+        <f t="array" ref="Z5">_xll.ITMPointToPoint(D5,G5,B5,C5,E5,F5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100,TerHandler,TerDirectory)</f>
+        <v>248.46459419519601</v>
       </c>
       <c r="AA5" s="23" cm="1">
-        <f t="array" ref="AA5">_xll.MSAM.ITMArea(D5,G5,N5,O5,W5,L5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100)</f>
+        <f t="array" ref="AA5">_xll.ITMArea(D5,G5,N5,O5,W5,L5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100)</f>
         <v>210.56824850094489</v>
       </c>
       <c r="AB5" s="23" cm="1">
-        <f t="array" ref="AB5">_xll.MSAM.P676_SpecificAttenuation_dB(A5/1000,T5,U5,V5,W5)</f>
-        <v>1.1503823038844667</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+        <f t="array" ref="AB5">_xll.P676_SpecificAttenuation_dB(A5/1000,T5,U5,V5,W5)</f>
+        <v>1.1503823038844661</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6725</v>
       </c>
@@ -5322,42 +5201,42 @@
         <v>0.5</v>
       </c>
       <c r="T6" s="23" cm="1">
-        <f t="array" ref="T6">_xll.MSAM.Celsius_to_Kelvin(15)</f>
+        <f t="array" ref="T6">_xll.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
       <c r="U6" s="23" cm="1">
-        <f t="array" ref="U6">_xll.MSAM.gpm3_to_hPa(7.5,T6)</f>
+        <f t="array" ref="U6">_xll.gpm3_to_hPa(7.5,T6)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V6" s="2">
         <v>1013.25</v>
       </c>
       <c r="W6" s="23" cm="1">
-        <f t="array" ref="W6">_xll.MSAM.DistKm(B6,C6,E6,F6)</f>
+        <f t="array" ref="W6">_xll.DistKm(B6,C6,E6,F6)</f>
         <v>35.791078240559798</v>
       </c>
-      <c r="X6" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="X6" ca="1">_xll.MSAM.IsLOS(B6,C6,E6,F6,D6,G6,1,TerDirectory)</f>
-        <v>#NAME?</v>
+      <c r="X6" s="23" t="b" cm="1">
+        <f t="array" ref="X6">_xll.IsLOS(B6,C6,E6,F6,D6,G6,1,TerDirectory)</f>
+        <v>0</v>
       </c>
       <c r="Y6" s="23" cm="1">
-        <f t="array" ref="Y6">_xll.MSAM.FreeSpace(W6,A6)</f>
+        <f t="array" ref="Y6">_xll.FreeSpace(W6,A6)</f>
         <v>140.07934141598673</v>
       </c>
-      <c r="Z6" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="Z6" ca="1">_xll.MSAM.ITMPointToPoint(D6,G6,B6,C6,E6,F6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
+      <c r="Z6" s="23" cm="1">
+        <f t="array" ref="Z6">_xll.ITMPointToPoint(D6,G6,B6,C6,E6,F6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100,TerHandler,TerDirectory)</f>
+        <v>229.3596488564566</v>
       </c>
       <c r="AA6" s="23" cm="1">
-        <f t="array" ref="AA6">_xll.MSAM.ITMArea(D6,G6,N6,O6,W6,L6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100)</f>
+        <f t="array" ref="AA6">_xll.ITMArea(D6,G6,N6,O6,W6,L6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100)</f>
         <v>166.90495037329015</v>
       </c>
       <c r="AB6" s="23" cm="1">
-        <f t="array" ref="AB6">_xll.MSAM.P676_SpecificAttenuation_dB(A6/1000,T6,U6,V6,W6)</f>
+        <f t="array" ref="AB6">_xll.P676_SpecificAttenuation_dB(A6/1000,T6,U6,V6,W6)</f>
         <v>0.36111607479468177</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
@@ -5368,75 +5247,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
       <c r="S8" s="8"/>
       <c r="X8" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="Z8" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA8" s="32"/>
-      <c r="AB8" s="32"/>
-      <c r="AC8" s="32"/>
-      <c r="AD8" s="32"/>
-      <c r="AE8" s="32"/>
-      <c r="AF8" s="32"/>
-      <c r="AG8" s="32"/>
-      <c r="AH8" s="32"/>
-      <c r="AI8" s="32"/>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="Z8" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31"/>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="31"/>
+      <c r="AG8" s="31"/>
+      <c r="AH8" s="31"/>
+      <c r="AI8" s="31"/>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="8"/>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
       <c r="S10" s="8"/>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
       <c r="S11" s="8"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A12" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33" t="s">
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="M12" s="34" t="s">
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="M12" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34" t="s">
+      <c r="N12" s="33"/>
+      <c r="O12" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="35" t="s">
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="35"/>
-      <c r="W12" s="35"/>
-    </row>
-    <row r="13" spans="1:35" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="S12" s="34"/>
+      <c r="T12" s="34"/>
+      <c r="U12" s="34"/>
+      <c r="V12" s="34"/>
+      <c r="W12" s="34"/>
+    </row>
+    <row r="13" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
@@ -5504,7 +5383,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>7125</v>
       </c>
@@ -5536,7 +5415,7 @@
         <v>3</v>
       </c>
       <c r="K14" s="23" cm="1">
-        <f t="array" ref="K14">_xll.MSAM.FDR_Stairs_3_20_40_60_dB(B14,C14,D14,E14,G14,H14,I14,J14,A14,F14)</f>
+        <f t="array" ref="K14">_xll.FDR_Stairs_3_20_40_60_dB(B14,C14,D14,E14,G14,H14,I14,J14,A14,F14)</f>
         <v>6.6280214362000329</v>
       </c>
       <c r="M14" s="2">
@@ -5555,61 +5434,61 @@
         <v>35887</v>
       </c>
       <c r="R14" s="23" cm="1">
-        <f t="array" ref="R14">_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,0)</f>
+        <f t="array" ref="R14">_xll.SatAz(M14,N14,O14,P14,Q14,0)</f>
         <v>8.679000600046443</v>
       </c>
       <c r="S14" s="23" cm="1">
-        <f t="array" ref="S14">_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,1)</f>
+        <f t="array" ref="S14">_xll.SatAz(M14,N14,O14,P14,Q14,1)</f>
         <v>41689.597238153408</v>
       </c>
       <c r="T14" s="23" cm="1">
-        <f t="array" ref="T14">_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,2)</f>
-        <v>97.359615358931137</v>
+        <f t="array" ref="T14">_xll.SatAz(M14,N14,O14,P14,Q14,2)</f>
+        <v>97.359615358931151</v>
       </c>
       <c r="U14" s="23" cm="1">
-        <f t="array" ref="U14">_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,3)</f>
+        <f t="array" ref="U14">_xll.SatAz(M14,N14,O14,P14,Q14,3)</f>
         <v>0.82543716113656984</v>
       </c>
       <c r="V14" s="23" cm="1">
-        <f t="array" ref="V14">_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,4)</f>
+        <f t="array" ref="V14">_xll.SatAz(M14,N14,O14,P14,Q14,4)</f>
         <v>13.318849480844628</v>
       </c>
       <c r="W14" s="23" t="b" cm="1">
-        <f t="array" ref="W14">IF(_xll.MSAM.SatAz(M14,N14,O14,P14,Q14,5)=0,TRUE,FALSE)</f>
+        <f t="array" ref="W14">IF(_xll.SatAz(M14,N14,O14,P14,Q14,5)=0,TRUE,FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
       <c r="S17" s="8"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
       <c r="S18" s="8"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
       <c r="S19" s="8"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
       <c r="S20" s="8"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
@@ -5623,276 +5502,276 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>50</v>
       </c>
       <c r="B23" s="23" cm="1">
-        <f t="array" ref="B23">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A23,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B23">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A23,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>176.35416608939531</v>
       </c>
       <c r="M23" s="2">
         <f>A3</f>
         <v>8000</v>
       </c>
-      <c r="N23" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N23" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M23,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N23" s="23" cm="1">
+        <f t="array" ref="N23">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M23,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>135.42766979138744</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>60</v>
       </c>
       <c r="B24" s="23" cm="1">
-        <f t="array" ref="B24">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A24,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B24">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A24,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>186.87976908830476</v>
       </c>
       <c r="M24" s="2">
         <f>M23+500</f>
         <v>8500</v>
       </c>
-      <c r="N24" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N24" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M24,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N24" s="23" cm="1">
+        <f t="array" ref="N24">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M24,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>135.95371367721219</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>70</v>
       </c>
       <c r="B25" s="23" cm="1">
-        <f t="array" ref="B25">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A25,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B25">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A25,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>197.24551913339644</v>
       </c>
       <c r="M25" s="2">
         <f t="shared" ref="M25:M38" si="0">M24+500</f>
         <v>9000</v>
       </c>
-      <c r="N25" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N25" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M25,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N25" s="23" cm="1">
+        <f t="array" ref="N25">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M25,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>136.44968437376377</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>80</v>
       </c>
       <c r="B26" s="23" cm="1">
-        <f t="array" ref="B26">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A26,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B26">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A26,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>207.52789850239242</v>
       </c>
       <c r="M26" s="2">
         <f t="shared" si="0"/>
         <v>9500</v>
       </c>
-      <c r="N26" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N26" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M26,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N26" s="23" cm="1">
+        <f t="array" ref="N26">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M26,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>136.91883544733909</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>90</v>
       </c>
       <c r="B27" s="23" cm="1">
-        <f t="array" ref="B27">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A27,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B27">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A27,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>209.4443793957183</v>
       </c>
       <c r="M27" s="2">
         <f t="shared" si="0"/>
         <v>10000</v>
       </c>
-      <c r="N27" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N27" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M27,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N27" s="23" cm="1">
+        <f t="array" ref="N27">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M27,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>137.36391944334778</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>100</v>
       </c>
       <c r="B28" s="23" cm="1">
-        <f t="array" ref="B28">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A28,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B28">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A28,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>210.66103070828476</v>
       </c>
       <c r="M28" s="2">
         <f t="shared" si="0"/>
         <v>10500</v>
       </c>
-      <c r="N28" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N28" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M28,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N28" s="23" cm="1">
+        <f t="array" ref="N28">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M28,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>137.78728575442187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>110</v>
       </c>
       <c r="B29" s="23" cm="1">
-        <f t="array" ref="B29">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A29,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B29">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A29,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>211.79807317762641</v>
       </c>
       <c r="M29" s="2">
         <f t="shared" si="0"/>
         <v>11000</v>
       </c>
-      <c r="N29" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N29" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M29,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N29" s="23" cm="1">
+        <f t="array" ref="N29">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M29,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>138.1909557003485</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>120</v>
       </c>
       <c r="B30" s="23" cm="1">
-        <f t="array" ref="B30">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A30,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B30">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A30,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>212.88192518947073</v>
       </c>
       <c r="M30" s="2">
         <f t="shared" si="0"/>
         <v>11500</v>
       </c>
-      <c r="N30" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N30" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M30,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N30" s="23" cm="1">
+        <f t="array" ref="N30">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M30,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>138.57668090486609</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>130</v>
       </c>
       <c r="B31" s="23" cm="1">
-        <f t="array" ref="B31">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A31,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B31">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A31,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>213.93526701187233</v>
       </c>
       <c r="M31" s="2">
         <f t="shared" si="0"/>
         <v>12000</v>
       </c>
-      <c r="N31" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N31" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M31,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N31" s="23" cm="1">
+        <f t="array" ref="N31">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M31,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>138.94598923918485</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>140</v>
       </c>
       <c r="B32" s="23" cm="1">
-        <f t="array" ref="B32">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A32,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B32">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A32,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>214.9770617162292</v>
       </c>
       <c r="M32" s="2">
         <f t="shared" si="0"/>
         <v>12500</v>
       </c>
-      <c r="N32" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N32" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M32,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N32" s="23" cm="1">
+        <f t="array" ref="N32">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M32,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>139.30022138052666</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>150</v>
       </c>
       <c r="B33" s="23" cm="1">
-        <f t="array" ref="B33">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A33,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B33">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A33,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>216.02224872255118</v>
       </c>
       <c r="M33" s="2">
         <f t="shared" si="0"/>
         <v>13000</v>
       </c>
-      <c r="N33" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N33" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M33,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N33" s="23" cm="1">
+        <f t="array" ref="N33">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M33,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>139.64056019618354</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>160</v>
       </c>
       <c r="B34" s="23" cm="1">
-        <f t="array" ref="B34">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A34,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B34">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A34,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>217.08146223455873</v>
       </c>
       <c r="M34" s="2">
         <f t="shared" si="0"/>
         <v>13500</v>
       </c>
-      <c r="N34" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N34" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M34,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N34" s="23" cm="1">
+        <f t="array" ref="N34">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M34,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>139.96805457904148</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>170</v>
       </c>
       <c r="B35" s="23" cm="1">
-        <f t="array" ref="B35">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A35,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B35">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A35,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>218.16101303187853</v>
       </c>
       <c r="M35" s="2">
         <f t="shared" si="0"/>
         <v>14000</v>
       </c>
-      <c r="N35" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N35" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M35,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N35" s="23" cm="1">
+        <f t="array" ref="N35">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M35,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>140.2836389462158</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>180</v>
       </c>
       <c r="B36" s="23" cm="1">
-        <f t="array" ref="B36">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A36,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B36">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A36,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>219.26323500631244</v>
       </c>
       <c r="M36" s="2">
         <f t="shared" si="0"/>
         <v>14500</v>
       </c>
-      <c r="N36" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N36" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M36,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N36" s="23" cm="1">
+        <f t="array" ref="N36">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M36,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>140.58814931456496</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>190</v>
       </c>
       <c r="B37" s="23" cm="1">
-        <f t="array" ref="B37">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A37,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B37">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A37,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>220.3871640114109</v>
       </c>
       <c r="M37" s="2">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
-      <c r="N37" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N37" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M37,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N37" s="23" cm="1">
+        <f t="array" ref="N37">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M37,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>140.88233664983366</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>200</v>
       </c>
       <c r="B38" s="23" cm="1">
-        <f t="array" ref="B38">_xll.MSAM.ITMArea($D$3,$G$3,$N$3,$O$3,A38,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+        <f t="array" ref="B38">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A38,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>221.52942277502015</v>
       </c>
       <c r="M38" s="2">
         <f t="shared" si="0"/>
         <v>15500</v>
       </c>
-      <c r="N38" s="23" t="e" cm="1">
-        <f t="array" aca="1" ref="N38" ca="1">_xll.MSAM.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M38,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
-        <v>#NAME?</v>
+      <c r="N38" s="23" cm="1">
+        <f t="array" ref="N38">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M38,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+        <v>141.16687802613515</v>
       </c>
     </row>
   </sheetData>
@@ -5914,33 +5793,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:AC37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.109375" customWidth="1"/>
-    <col min="2" max="6" width="10.44140625" customWidth="1"/>
-    <col min="7" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" customWidth="1"/>
-    <col min="12" max="12" width="10.5546875" customWidth="1"/>
-    <col min="13" max="13" width="11.5546875" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="16.33203125" customWidth="1"/>
-    <col min="17" max="17" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.28515625" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B1" s="33" t="s">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B1" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="36" t="s">
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-    </row>
-    <row r="2" spans="1:29" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="B2" s="13" t="s">
         <v>81</v>
       </c>
@@ -6026,7 +5905,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>136</v>
       </c>
@@ -6118,7 +5997,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>137</v>
       </c>
@@ -6180,12 +6059,12 @@
         <v>165.00000000000693</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="L6" s="17" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>141</v>
       </c>
@@ -6207,7 +6086,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>131</v>
       </c>
@@ -6219,12 +6098,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="N9" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="K10" t="s">
         <v>194</v>
       </c>
@@ -6232,7 +6111,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="K11">
         <v>-29.5</v>
       </c>
@@ -6240,7 +6119,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="K12">
         <v>33.5</v>
       </c>
@@ -6248,7 +6127,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="K13">
         <v>16</v>
       </c>
@@ -6256,12 +6135,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="L14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="K15">
         <v>8</v>
       </c>
@@ -6269,17 +6148,17 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="L16" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="11:22" x14ac:dyDescent="0.25">
       <c r="L17" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K18">
         <v>0</v>
       </c>
@@ -6287,7 +6166,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K19">
         <v>3</v>
       </c>
@@ -6295,7 +6174,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K20">
         <v>4</v>
       </c>
@@ -6303,7 +6182,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="21" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="21" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K21">
         <v>0</v>
       </c>
@@ -6311,7 +6190,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="24" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K24" s="18" t="s">
         <v>175</v>
       </c>
@@ -6349,7 +6228,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="25" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="25" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K25" s="16" t="s">
         <v>165</v>
       </c>
@@ -6387,13 +6266,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K26" s="16" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="2">
         <f>N26-O26-P26-Q26+R26+S26+T26+U26+V26</f>
-        <v>114.26920385902991</v>
+        <v>114.26920385903014</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2">
@@ -6410,7 +6289,7 @@
       </c>
       <c r="R26" s="23" cm="1">
         <f t="array" ref="R26">_xll.ITMPointToPointCR(D4,G3,B4,C4,E3,F3,W3,S3,H3,IF(N3="V",1,0),U3,T3,Z3,AA3*100,AB3*100,0,TerDirectory)</f>
-        <v>194.26920385902991</v>
+        <v>194.26920385903014</v>
       </c>
       <c r="S26" s="2">
         <v>0</v>
@@ -6425,7 +6304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="28" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K28" s="17" t="s">
         <v>197</v>
       </c>
@@ -6441,7 +6320,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="29" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="11:22" x14ac:dyDescent="0.25">
       <c r="O29" t="s">
         <v>180</v>
       </c>
@@ -6453,7 +6332,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="11:22" x14ac:dyDescent="0.25">
       <c r="O30" t="s">
         <v>181</v>
       </c>
@@ -6465,38 +6344,38 @@
         <v>179</v>
       </c>
     </row>
-    <row r="31" spans="11:22" x14ac:dyDescent="0.3">
+    <row r="31" spans="11:22" x14ac:dyDescent="0.25">
       <c r="L31" s="17" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="32" spans="11:22" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="11:22" ht="17.25" x14ac:dyDescent="0.25">
       <c r="L32" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="33" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="12:13" x14ac:dyDescent="0.25">
       <c r="M33" t="str">
         <f>"- Telecommunications Industry Association Bulletin 10F specifies an I/N of -6 dB for digital systems"</f>
         <v>- Telecommunications Industry Association Bulletin 10F specifies an I/N of -6 dB for digital systems</v>
       </c>
     </row>
-    <row r="34" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L34" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="35" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="12:13" x14ac:dyDescent="0.25">
       <c r="M35" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="36" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L36" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="12:13" x14ac:dyDescent="0.25">
       <c r="M37" t="s">
         <v>174</v>
       </c>
@@ -6516,12 +6395,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:G23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="6" width="9.88671875" customWidth="1"/>
+    <col min="4" max="6" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>113</v>
       </c>
@@ -6544,7 +6423,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>43</v>
       </c>
@@ -6570,7 +6449,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>43</v>
       </c>
@@ -6596,7 +6475,7 @@
         <v>41.004737685031124</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>43</v>
       </c>
@@ -6622,7 +6501,7 @@
         <v>35.018950740124481</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>43</v>
       </c>
@@ -6648,7 +6527,7 @@
         <v>25.25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>43</v>
       </c>
@@ -6674,7 +6553,7 @@
         <v>23.974250108400469</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>43</v>
       </c>
@@ -6700,7 +6579,7 @@
         <v>21.551499783199059</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>43</v>
       </c>
@@ -6726,7 +6605,7 @@
         <v>19.571968632008439</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>43</v>
       </c>
@@ -6752,7 +6631,7 @@
         <v>17.898298891243108</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>43</v>
       </c>
@@ -6778,7 +6657,7 @@
         <v>16.448500216800941</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>43</v>
       </c>
@@ -6804,7 +6683,7 @@
         <v>15.169687155616408</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>43</v>
       </c>
@@ -6830,7 +6709,7 @@
         <v>14.025749891599528</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>43</v>
       </c>
@@ -6856,7 +6735,7 @@
         <v>12.990932762643904</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>43</v>
       </c>
@@ -6882,7 +6761,7 @@
         <v>12.046218740408911</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>43</v>
       </c>
@@ -6908,7 +6787,7 @@
         <v>11.177166083928611</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>43</v>
       </c>
@@ -6934,7 +6813,7 @@
         <v>10.37254899964358</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>43</v>
       </c>
@@ -6960,7 +6839,7 @@
         <v>9.6234684152074976</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>43</v>
       </c>
@@ -6986,7 +6865,7 @@
         <v>8.9227503252014131</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>43</v>
       </c>
@@ -7012,7 +6891,7 @@
         <v>8.2645268571426804</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>43</v>
       </c>
@@ -7038,7 +6917,7 @@
         <v>7.643937264016877</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>43</v>
       </c>
@@ -7064,7 +6943,7 @@
         <v>7.0569098677788062</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>43</v>
       </c>
@@ -7101,12 +6980,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>34</v>
       </c>
@@ -7120,8 +6999,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
         <v>42</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -7135,8 +7014,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="41"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="40"/>
       <c r="B3" s="5" t="s">
         <v>29</v>
       </c>
@@ -7148,8 +7027,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="41"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="40"/>
       <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
@@ -7161,8 +7040,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="41"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="40"/>
       <c r="B5" s="5" t="s">
         <v>33</v>
       </c>
@@ -7174,8 +7053,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="41"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="40"/>
       <c r="B6" s="5" t="s">
         <v>31</v>
       </c>
@@ -7187,8 +7066,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="41"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="40"/>
       <c r="B7" s="5" t="s">
         <v>32</v>
       </c>
@@ -7200,8 +7079,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="41" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="40" t="s">
         <v>41</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -7215,8 +7094,8 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="41"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="40"/>
       <c r="B9" s="5" t="s">
         <v>36</v>
       </c>
@@ -7228,8 +7107,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="40"/>
       <c r="B10" s="5" t="s">
         <v>37</v>
       </c>
@@ -7241,8 +7120,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="41"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="40"/>
       <c r="B11" s="5" t="s">
         <v>38</v>
       </c>
@@ -7254,8 +7133,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="41"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="40"/>
       <c r="B12" s="5" t="s">
         <v>39</v>
       </c>
@@ -7267,8 +7146,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="41"/>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="40"/>
       <c r="B13" s="5" t="s">
         <v>40</v>
       </c>
@@ -7280,8 +7159,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="41" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="40" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -7295,8 +7174,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="41"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="40"/>
       <c r="B15" s="5" t="s">
         <v>44</v>
       </c>
@@ -7308,8 +7187,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="41"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="40"/>
       <c r="B16" s="5" t="s">
         <v>45</v>
       </c>
@@ -7321,8 +7200,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="41"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="40"/>
       <c r="B17" s="5" t="s">
         <v>47</v>
       </c>
@@ -7334,8 +7213,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="41"/>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="40"/>
       <c r="B18" s="5" t="s">
         <v>46</v>
       </c>
@@ -7347,8 +7226,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="41"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="40"/>
       <c r="B19" s="5" t="s">
         <v>48</v>
       </c>
@@ -7360,8 +7239,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="38" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="37" t="s">
         <v>62</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -7375,8 +7254,8 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="39"/>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="38"/>
       <c r="B21" s="5" t="s">
         <v>51</v>
       </c>
@@ -7388,8 +7267,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="39"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="38"/>
       <c r="B22" s="5" t="s">
         <v>52</v>
       </c>
@@ -7401,8 +7280,8 @@
         <v>-115.8</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="39"/>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="38"/>
       <c r="B23" s="5" t="s">
         <v>53</v>
       </c>
@@ -7414,8 +7293,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="39"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="38"/>
       <c r="B24" s="5" t="s">
         <v>54</v>
       </c>
@@ -7427,8 +7306,8 @@
         <v>-51.5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="38"/>
       <c r="B25" s="5" t="s">
         <v>55</v>
       </c>
@@ -7440,8 +7319,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="38"/>
       <c r="B26" s="5" t="s">
         <v>56</v>
       </c>
@@ -7453,8 +7332,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="39"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="38"/>
       <c r="B27" s="5" t="s">
         <v>57</v>
       </c>
@@ -7466,8 +7345,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="39"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="38"/>
       <c r="B28" s="5" t="s">
         <v>58</v>
       </c>
@@ -7479,8 +7358,8 @@
         <v>61.400325732035007</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="39"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="38"/>
       <c r="B29" s="5" t="s">
         <v>59</v>
       </c>
@@ -7492,8 +7371,8 @@
         <v>10.000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="39"/>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="38"/>
       <c r="B30" s="5" t="s">
         <v>60</v>
       </c>
@@ -7505,8 +7384,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="40"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="39"/>
       <c r="B31" s="5" t="s">
         <v>61</v>
       </c>
@@ -7518,8 +7397,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="38" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="37" t="s">
         <v>71</v>
       </c>
       <c r="B32" s="5" t="s">
@@ -7533,8 +7412,8 @@
         <v>0.30480370641306997</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="39"/>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="38"/>
       <c r="B33" s="5" t="s">
         <v>64</v>
       </c>
@@ -7546,8 +7425,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="39"/>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="38"/>
       <c r="B34" s="5" t="s">
         <v>65</v>
       </c>
@@ -7559,8 +7438,8 @@
         <v>1.6093440000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="39"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="38"/>
       <c r="B35" s="5" t="s">
         <v>66</v>
       </c>
@@ -7572,8 +7451,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="39"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="38"/>
       <c r="B36" s="5" t="s">
         <v>67</v>
       </c>
@@ -7585,8 +7464,8 @@
         <v>1.8939393939393939E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="39"/>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="38"/>
       <c r="B37" s="5" t="s">
         <v>68</v>
       </c>
@@ -7598,8 +7477,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="39"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="38"/>
       <c r="B38" s="5" t="s">
         <v>69</v>
       </c>
@@ -7611,8 +7490,8 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="40"/>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="39"/>
       <c r="B39" s="5" t="s">
         <v>70</v>
       </c>
@@ -7624,8 +7503,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="41" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="40" t="s">
         <v>78</v>
       </c>
       <c r="B40" s="5" t="s">
@@ -7639,8 +7518,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="41"/>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="40"/>
       <c r="B41" s="5" t="s">
         <v>73</v>
       </c>
@@ -7652,8 +7531,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="41"/>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="40"/>
       <c r="B42" s="5" t="s">
         <v>74</v>
       </c>
@@ -7665,8 +7544,8 @@
         <v>273.14999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="41"/>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="40"/>
       <c r="B43" s="5" t="s">
         <v>75</v>
       </c>
@@ -7678,8 +7557,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="41"/>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="40"/>
       <c r="B44" s="5" t="s">
         <v>76</v>
       </c>
@@ -7691,8 +7570,8 @@
         <v>273.70555555555552</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="41"/>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="40"/>
       <c r="B45" s="5" t="s">
         <v>77</v>
       </c>
@@ -7704,7 +7583,7 @@
         <v>32.999999999999979</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>80</v>
       </c>
@@ -7737,22 +7616,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>182</v>
       </c>
@@ -7778,7 +7657,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>190</v>
       </c>
@@ -7804,7 +7683,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>191</v>
       </c>
@@ -7830,7 +7709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>192</v>
       </c>
@@ -7856,7 +7735,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>193</v>
       </c>
@@ -7882,7 +7761,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>83</v>
       </c>
@@ -7911,7 +7790,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>87</v>
       </c>
@@ -7946,7 +7825,7 @@
         <v>Distance: 104.891 Km</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>88</v>
       </c>
@@ -7981,7 +7860,7 @@
         <v>Distance: 104.891 Km</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>88</v>
       </c>
@@ -8016,7 +7895,7 @@
         <v>Distance: 104.891 Km</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>91</v>
       </c>
@@ -8051,7 +7930,7 @@
         <v>Distance: 104.891 Km</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>92</v>
       </c>
@@ -8077,21 +7956,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2226CAC0-AF79-44C0-AA2A-1A7BFBA387F4}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>205</v>
       </c>
@@ -8105,7 +7984,7 @@
         <v>147.18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>206</v>
       </c>
@@ -8116,7 +7995,7 @@
         <v>147.18</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>204</v>
       </c>
@@ -8127,7 +8006,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>200</v>
       </c>
@@ -8136,7 +8015,7 @@
         <v xml:space="preserve"> Harmonic Found---&gt;    1 (147.18) = 147.18 ± 0.02 MHz bandwidth</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>198</v>
       </c>
@@ -8145,11 +8024,11 @@
         <v xml:space="preserve"> INTERMOD---&gt;   2 (147.06) - 1 (146.94) = 147.18 ± 0.02 MHz bandwidth</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="B8" s="31" t="str" cm="1">
+      <c r="B8" s="30" t="str" cm="1">
         <f t="array" ref="B8">_xll.IntermodThreeSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
         <v xml:space="preserve"> INTERMOD---&gt;   4 (147.06) - 2 (146.94) - 1 (147.18) = 147.18 ± 0.02 MHz bandwidth_x000D_
  INTERMOD---&gt;   2 (147.18) - 2 (147.06) + 1 (146.94) = 147.18 ± 0.02 MHz bandwidth</v>
@@ -8164,422 +8043,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
-        <v>201</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="B2" s="2">
-        <v>456.07499999999999</v>
-      </c>
-      <c r="C2" s="2">
-        <v>456.57499999999999</v>
-      </c>
-      <c r="D2" s="2">
-        <v>456.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B3" s="2">
-        <v>461.55</v>
-      </c>
-      <c r="C3" s="2">
-        <v>456.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="B6" s="26" t="str" cm="1">
-        <f t="array" ref="B6">_xll.IntermodHarmonics(B2:D2,B3:C3,B4:C4)</f>
-        <v xml:space="preserve"> Harmonic Found---&gt;    1 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
- Harmonic Found---&gt;    1 (456.1) = 456.1 ± 0.1 MHz bandwidth</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="26" t="str" cm="1">
-        <f t="array" ref="B7">_xll.IntermodTwoSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
-        <v xml:space="preserve"> INTERMOD---&gt;   2 (456.075) - 1 (456.1) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   3 (456.075) - 2 (456.1) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   2 (456.1) - 1 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   3 (456.1) - 2 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
- INTERMOD---&gt;   4 (456.1) - 3 (456.075) = 456.1 ± 0.1 MHz bandwidth</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="B8" s="31" t="str" cm="1">
-        <f t="array" ref="B8">_xll.IntermodThreeSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87334F41-6ACF-41B1-9BF9-AAB07931F740}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C2">
-        <v>25.032406999999999</v>
-      </c>
-      <c r="D2">
-        <v>-77.356269999999995</v>
-      </c>
-      <c r="E2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F2">
-        <v>24.707910999999999</v>
-      </c>
-      <c r="G2">
-        <v>-77.765840999999995</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C3">
-        <v>11.552263999999999</v>
-      </c>
-      <c r="D3">
-        <v>104.937893</v>
-      </c>
-      <c r="E3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F3">
-        <v>10.991194999999999</v>
-      </c>
-      <c r="G3">
-        <v>104.77869099999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4">
-        <v>30.040597000000002</v>
-      </c>
-      <c r="D4">
-        <v>31.235703000000001</v>
-      </c>
-      <c r="E4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F4">
-        <v>30.458936000000001</v>
-      </c>
-      <c r="G4">
-        <v>31.181923999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" t="s">
-        <v>219</v>
-      </c>
-      <c r="C5">
-        <v>5.5423049999999998</v>
-      </c>
-      <c r="D5">
-        <v>-0.20711499999999999</v>
-      </c>
-      <c r="E5" t="s">
-        <v>220</v>
-      </c>
-      <c r="F5">
-        <v>6.1462409999999998</v>
-      </c>
-      <c r="G5">
-        <v>1.5762999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C6">
-        <v>14.078479</v>
-      </c>
-      <c r="D6">
-        <v>-87.185700999999995</v>
-      </c>
-      <c r="E6" t="s">
-        <v>223</v>
-      </c>
-      <c r="F6">
-        <v>13.803167999999999</v>
-      </c>
-      <c r="G6">
-        <v>-87.258123999999995</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B7" t="s">
-        <v>225</v>
-      </c>
-      <c r="C7">
-        <v>17.977149000000001</v>
-      </c>
-      <c r="D7">
-        <v>-76.812903000000006</v>
-      </c>
-      <c r="E7" t="s">
-        <v>226</v>
-      </c>
-      <c r="F7">
-        <v>17.947472000000001</v>
-      </c>
-      <c r="G7">
-        <v>-77.240453000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>227</v>
-      </c>
-      <c r="B8" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8">
-        <v>27.729265999999999</v>
-      </c>
-      <c r="D8">
-        <v>85.302627999999999</v>
-      </c>
-      <c r="E8" t="s">
-        <v>229</v>
-      </c>
-      <c r="F8">
-        <v>27.615233</v>
-      </c>
-      <c r="G8">
-        <v>85.559207999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>230</v>
-      </c>
-      <c r="B9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C9">
-        <v>9.0569520000000008</v>
-      </c>
-      <c r="D9">
-        <v>7.4993379999999998</v>
-      </c>
-      <c r="E9" t="s">
-        <v>232</v>
-      </c>
-      <c r="F9">
-        <v>8.8449989999999996</v>
-      </c>
-      <c r="G9">
-        <v>7.8724879999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>233</v>
-      </c>
-      <c r="B10" t="s">
-        <v>234</v>
-      </c>
-      <c r="C10">
-        <v>13.154978</v>
-      </c>
-      <c r="D10">
-        <v>-61.227837000000001</v>
-      </c>
-      <c r="E10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F10">
-        <v>13.025244000000001</v>
-      </c>
-      <c r="G10">
-        <v>-61.232104999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>236</v>
-      </c>
-      <c r="B11" t="s">
-        <v>237</v>
-      </c>
-      <c r="C11">
-        <v>8.4868369999999995</v>
-      </c>
-      <c r="D11">
-        <v>-13.231096000000001</v>
-      </c>
-      <c r="E11" t="s">
-        <v>238</v>
-      </c>
-      <c r="F11">
-        <v>8.3802179999999993</v>
-      </c>
-      <c r="G11">
-        <v>-13.134311</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B12" t="s">
-        <v>240</v>
-      </c>
-      <c r="C12">
-        <v>17.293337999999999</v>
-      </c>
-      <c r="D12">
-        <v>-62.722065999999998</v>
-      </c>
-      <c r="E12" t="s">
-        <v>241</v>
-      </c>
-      <c r="F12">
-        <v>17.136043999999998</v>
-      </c>
-      <c r="G12">
-        <v>-62.626285000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>242</v>
-      </c>
-      <c r="B13" t="s">
-        <v>243</v>
-      </c>
-      <c r="C13">
-        <v>0.33255699999999999</v>
-      </c>
-      <c r="D13">
-        <v>32.575284000000003</v>
-      </c>
-      <c r="E13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F13">
-        <v>6.0284999999999998E-2</v>
-      </c>
-      <c r="G13">
-        <v>32.468792000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G13">
-    <sortCondition ref="A2:A13"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{568178ef-2b90-40ee-86de-4595a529cba9}" enabled="1" method="Standard" siteId="{d6cff1bd-67dd-4ce8-945d-d07dc775672f}" contentBits="0" removed="0"/>

--- a/MSAMtoExcel_Sample.xlsx
+++ b/MSAMtoExcel_Sample.xlsx
@@ -5,20 +5,21 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FNajmy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntia-my.sharepoint.com/personal/fnajmy_ntia_gov/Documents/Documents/MSAMExcelAdd-In/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04852578-51C7-4527-B6FC-B87B98968703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="8_{AAB07B3B-41F7-4507-9E6C-7FA57B4F8D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFFF19C0-096B-4DAF-A249-38CDAC0F5016}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Propagation" sheetId="1" r:id="rId1"/>
-    <sheet name="MSAM Example" sheetId="5" r:id="rId2"/>
-    <sheet name="Antenna" sheetId="4" r:id="rId3"/>
-    <sheet name="Conversion Functions" sheetId="2" r:id="rId4"/>
-    <sheet name="Geographic" sheetId="3" r:id="rId5"/>
-    <sheet name="Intermod" sheetId="8" r:id="rId6"/>
+    <sheet name="LMS" sheetId="7" r:id="rId2"/>
+    <sheet name="MSAM Example" sheetId="5" r:id="rId3"/>
+    <sheet name="Antenna" sheetId="4" r:id="rId4"/>
+    <sheet name="Conversion Functions" sheetId="2" r:id="rId5"/>
+    <sheet name="Geographic" sheetId="3" r:id="rId6"/>
+    <sheet name="Intermod" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="TerDirectory">Propagation!$Z$8</definedName>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="270">
   <si>
     <t>TxLat</t>
   </si>
@@ -345,6 +346,9 @@
     <t>Line-Of-Sight</t>
   </si>
   <si>
+    <t>P.528</t>
+  </si>
+  <si>
     <t>Delta Bearing</t>
   </si>
   <si>
@@ -433,6 +437,9 @@
   </si>
   <si>
     <t>P.676</t>
+  </si>
+  <si>
+    <t>Terrain Ht(m)</t>
   </si>
   <si>
     <t>Tx</t>
@@ -697,6 +704,9 @@
     <t>Req'd C/I (dB)</t>
   </si>
   <si>
+    <t>RxBW</t>
+  </si>
+  <si>
     <t>Two Signal</t>
   </si>
   <si>
@@ -715,16 +725,213 @@
     <t>Terrain Directory:</t>
   </si>
   <si>
-    <t>RxBW (KHz)</t>
-  </si>
-  <si>
-    <t>Tx Freq (MHz)</t>
-  </si>
-  <si>
-    <t>Rx Freq (MHz)</t>
-  </si>
-  <si>
     <t>C:\USGS</t>
+  </si>
+  <si>
+    <t>Land Mobile Service Models</t>
+  </si>
+  <si>
+    <t>Input Fields</t>
+  </si>
+  <si>
+    <t>Loss</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>MHz</t>
+  </si>
+  <si>
+    <t>Okumura-Hata ITU 529</t>
+  </si>
+  <si>
+    <t>db</t>
+  </si>
+  <si>
+    <t>Base Station Antenna Height</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Okumura-Hata Davidson</t>
+  </si>
+  <si>
+    <t>Mobile Anntenna Height</t>
+  </si>
+  <si>
+    <t>Cost 231</t>
+  </si>
+  <si>
+    <t>Km</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Urban</t>
+  </si>
+  <si>
+    <t>Field Strength</t>
+  </si>
+  <si>
+    <t>City Size</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>dB mv / m</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>watts</t>
+  </si>
+  <si>
+    <t>Frequency Range 150 MHz to 1500 MHz</t>
+  </si>
+  <si>
+    <t>Base Station Antenna Height 30 m to 200 m</t>
+  </si>
+  <si>
+    <t>Mobiel Antenna Height 1 m to 10 m</t>
+  </si>
+  <si>
+    <t>Distance &lt;= 300 Km</t>
+  </si>
+  <si>
+    <t>Frequency Range 1500 MHz to 2000 MHz</t>
+  </si>
+  <si>
+    <t>Distance &lt;= 100 Km</t>
+  </si>
+  <si>
+    <t>Frequency Range 30 MHz to 2000 MHz</t>
+  </si>
+  <si>
+    <t>Base Station Antenna Height 20 m to 2500 m</t>
+  </si>
+  <si>
+    <t>Cost 231 (European Cooperative for Scientific and Technical Research)</t>
+  </si>
+  <si>
+    <t>Okumura-Hata Davidson (Often used in American Software)</t>
+  </si>
+  <si>
+    <t>Okumura-Hata ITU 529 (Recognized as the Original Hata Model)</t>
+  </si>
+  <si>
+    <t>Origin: Empirical formulas developed by Masaharu Hata in 1980, which were based on the original graphical propagation data collected by Yoshihisa Okumura in Japan in the 1960s.</t>
+  </si>
+  <si>
+    <t>Propagation Models</t>
+  </si>
+  <si>
+    <t>ITM</t>
+  </si>
+  <si>
+    <t>empirical models developed by Anita Longley and Phil Rice.</t>
+  </si>
+  <si>
+    <t>between 20 MHz and 20 GHz based on electromagnetic theory and</t>
+  </si>
+  <si>
+    <t>Predicts terrestrial radiowave propagation for frequencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommendation contains a method for predicting basic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">transmission loss in the frequency range 100-30 000 MHz for </t>
+  </si>
+  <si>
+    <t>aeronautical services. (air-to-ground paths)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimates the instantaneous slant path gaseous attenuation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">due to oxygen and water vapour for the frequency range from </t>
+  </si>
+  <si>
+    <t>1 to 350 GHz.</t>
+  </si>
+  <si>
+    <t>EASY Statistical Antenna Gain Model for Fixed-Azimuth Antennas, ECAC-TN-85-023, Joint Spectrum Center, Annapolis, MD (1985).</t>
+  </si>
+  <si>
+    <t>Used to calculate the Fixed Service antenna reference radiation pattern when Gmax ≥ 10 dBi.</t>
+  </si>
+  <si>
+    <t>Wolfgain</t>
+  </si>
+  <si>
+    <t>Wolfgain formula provides a simple and conservative method to calculate the Fixed Service and Land Mobile Service antenna reference radiation patterns when Gmax &lt; 10 dBi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H. Maddoxs, Antenna Gain Estimation, Joint Spectrum Center, Annapolis, MD (1974). </t>
+  </si>
+  <si>
+    <t>Antenna Models For Electromagnetic Compatibility Analyses.</t>
+  </si>
+  <si>
+    <t>NTIA TM-13-489</t>
+  </si>
+  <si>
+    <t>https://www.ntia.gov/files/ntia/publications/antenna_models_report_tm-13-489.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in a non-linear system (like amplifiers or receivers), producing unwanted, new frequencies. These new, spurious signals </t>
+  </si>
+  <si>
+    <t>can cause significant distortion in radio, wireless audio, and communication systems.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Intermodulation (intermod or IMD)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is a form of signal interference occurring when two or more frequencies combine </t>
+    </r>
+  </si>
+  <si>
+    <t>Intermodulation Products:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third-Order: Most severe in radio, as they fall closest to the original signals </t>
+  </si>
+  <si>
+    <t>Higher-Order: 5th, 7th, etc., which are usually weaker but still cause interference.</t>
+  </si>
+  <si>
+    <t>Second-Order: Sum and difference of the input frequencies.</t>
   </si>
 </sst>
 </file>
@@ -734,7 +941,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -772,8 +979,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -816,8 +1062,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -910,12 +1162,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -966,7 +1243,21 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1002,8 +1293,17 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -4833,13 +5133,13 @@
         <v>16</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="V2" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="U2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>18</v>
@@ -4848,7 +5148,7 @@
         <v>20</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>23</v>
@@ -4857,7 +5157,10 @@
         <v>22</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>121</v>
+        <v>92</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
@@ -4909,48 +5212,52 @@
       <c r="P3" s="29">
         <v>0</v>
       </c>
-      <c r="Q3" s="29">
+      <c r="Q3" s="30">
         <v>0.5</v>
       </c>
-      <c r="R3" s="29">
+      <c r="R3" s="30">
         <v>0.5</v>
       </c>
-      <c r="S3" s="29">
+      <c r="S3" s="30">
         <v>0.5</v>
       </c>
-      <c r="T3" s="23" cm="1">
-        <f t="array" ref="T3">_xll.Celsius_to_Kelvin(15)</f>
+      <c r="T3" s="23">
+        <f>_xll.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
-      <c r="U3" s="23" cm="1">
-        <f t="array" ref="U3">_xll.gpm3_to_hPa(7.5,T3)</f>
+      <c r="U3" s="23">
+        <f>_xll.gpm3_to_hPa(7.5,T3)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V3" s="29">
         <v>1013.25</v>
       </c>
-      <c r="W3" s="23" cm="1">
-        <f t="array" ref="W3">_xll.DistKm(B3,C3,E3,F3)</f>
+      <c r="W3" s="23">
+        <f>_xll.DistKm(B3,C3,E3,F3)</f>
         <v>17.76476411326108</v>
       </c>
-      <c r="X3" s="23" t="b" cm="1">
-        <f t="array" ref="X3">_xll.IsLOS(B3,C3,E3,F3,D3,G3,1,TerDirectory)</f>
+      <c r="X3" s="23" t="b">
+        <f>_xll.IsLOS(B3,C3,E3,F3,D3,G3,1,TerDirectory)</f>
         <v>1</v>
       </c>
-      <c r="Y3" s="23" cm="1">
-        <f t="array" ref="Y3">_xll.FreeSpace(W3,A3)</f>
+      <c r="Y3" s="23">
+        <f>_xll.FreeSpace(W3,A3)</f>
         <v>135.50298864283701</v>
       </c>
-      <c r="Z3" s="23" cm="1">
-        <f t="array" ref="Z3">_xll.ITMPointToPoint(D3,G3,B3,C3,E3,F3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100,TerHandler,TerDirectory)</f>
+      <c r="Z3" s="23">
+        <f>_xll.ITMPointToPoint(D3,G3,B3,C3,E3,F3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100,TerHandler,TerDirectory)</f>
         <v>135.42766979138744</v>
       </c>
-      <c r="AA3" s="23" cm="1">
-        <f t="array" ref="AA3">_xll.ITMArea(D3,G3,N3,O3,W3,L3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100)</f>
+      <c r="AA3" s="23">
+        <f>_xll.ITMArea(D3,G3,N3,O3,W3,L3,M3,I3,A3,H3,K3,J3,P3,Q3*100,R3*100,S3*100)</f>
         <v>137.74535973059781</v>
       </c>
-      <c r="AB3" s="23" cm="1">
-        <f t="array" ref="AB3">_xll.P676_SpecificAttenuation_dB(A3/1000,T3,U3,V3,W3)</f>
+      <c r="AB3" s="23">
+        <f>_xll.P528_5(W3,MIN(D3,G3),MAX(D3,G3),A3,H3,Q3*100)</f>
+        <v>135.61004247905726</v>
+      </c>
+      <c r="AC3" s="23">
+        <f>_xll.P676_SpecificAttenuation_dB(A3/1000,T3,U3,V3,W3)</f>
         <v>0.20280107795331906</v>
       </c>
     </row>
@@ -5003,48 +5310,52 @@
       <c r="P4" s="2">
         <v>0</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="3">
         <v>0.5</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="3">
         <v>0.5</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="3">
         <v>0.5</v>
       </c>
-      <c r="T4" s="23" cm="1">
-        <f t="array" ref="T4">_xll.Celsius_to_Kelvin(15)</f>
+      <c r="T4" s="23">
+        <f>_xll.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
-      <c r="U4" s="23" cm="1">
-        <f t="array" ref="U4">_xll.gpm3_to_hPa(7.5,T4)</f>
+      <c r="U4" s="23">
+        <f>_xll.gpm3_to_hPa(7.5,T4)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V4" s="2">
         <v>1013.25</v>
       </c>
-      <c r="W4" s="23" cm="1">
-        <f t="array" ref="W4">_xll.DistKm(B4,C4,E4,F4)</f>
+      <c r="W4" s="23">
+        <f>_xll.DistKm(B4,C4,E4,F4)</f>
         <v>104.89071248171258</v>
       </c>
-      <c r="X4" s="23" t="b" cm="1">
-        <f t="array" ref="X4">_xll.IsLOS(B4,C4,E4,F4,D4,G4,1,TerDirectory)</f>
+      <c r="X4" s="23" t="b">
+        <f>_xll.IsLOS(B4,C4,E4,F4,D4,G4,1,TerDirectory)</f>
         <v>0</v>
       </c>
-      <c r="Y4" s="23" cm="1">
-        <f t="array" ref="Y4">_xll.FreeSpace(W4,A4)</f>
+      <c r="Y4" s="23">
+        <f>_xll.FreeSpace(W4,A4)</f>
         <v>150.24937510291187</v>
       </c>
-      <c r="Z4" s="23" cm="1">
-        <f t="array" ref="Z4">_xll.ITMPointToPoint(D4,G4,B4,C4,E4,F4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100,TerHandler,TerDirectory)</f>
+      <c r="Z4" s="23">
+        <f>_xll.ITMPointToPoint(D4,G4,B4,C4,E4,F4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100,TerHandler,TerDirectory)</f>
         <v>247.81390859953319</v>
       </c>
-      <c r="AA4" s="23" cm="1">
-        <f t="array" ref="AA4">_xll.ITMArea(D4,G4,N4,O4,W4,L4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100)</f>
+      <c r="AA4" s="23">
+        <f>_xll.ITMArea(D4,G4,N4,O4,W4,L4,M4,I4,A4,H4,K4,J4,P4,Q4*100,R4*100,S4*100)</f>
         <v>210.22674503575132</v>
       </c>
-      <c r="AB4" s="23" cm="1">
-        <f t="array" ref="AB4">_xll.P676_SpecificAttenuation_dB(A4/1000,T4,U4,V4,W4)</f>
+      <c r="AB4" s="23">
+        <f>_xll.P528_5(W4,MIN(D4,G4),MAX(D4,G4),A4,H4,Q4*100)</f>
+        <v>201.74436882882611</v>
+      </c>
+      <c r="AC4" s="23">
+        <f>_xll.P676_SpecificAttenuation_dB(A4/1000,T4,U4,V4,W4)</f>
         <v>1.1280677803367003</v>
       </c>
     </row>
@@ -5097,72 +5408,76 @@
       <c r="P5" s="2">
         <v>0</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="3">
         <v>0.5</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="3">
         <v>0.5</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="3">
         <v>0.5</v>
       </c>
-      <c r="T5" s="23" cm="1">
-        <f t="array" ref="T5">_xll.Celsius_to_Kelvin(15)</f>
+      <c r="T5" s="23">
+        <f>_xll.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
-      <c r="U5" s="23" cm="1">
-        <f t="array" ref="U5">_xll.gpm3_to_hPa(7.5,T5)</f>
+      <c r="U5" s="23">
+        <f>_xll.gpm3_to_hPa(7.5,T5)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V5" s="2">
         <v>1013.25</v>
       </c>
-      <c r="W5" s="23" cm="1">
-        <f t="array" ref="W5">_xll.DistKm(B5,C5,E5,F5)</f>
+      <c r="W5" s="23">
+        <f>_xll.DistKm(B5,C5,E5,F5)</f>
         <v>104.89071248171258</v>
       </c>
-      <c r="X5" s="23" t="b" cm="1">
-        <f t="array" ref="X5">_xll.IsLOS(B5,C5,E5,F5,D5,G5,1,TerDirectory)</f>
+      <c r="X5" s="23" t="b">
+        <f>_xll.IsLOS(B5,C5,E5,F5,D5,G5,1,TerDirectory)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="23" cm="1">
-        <f t="array" ref="Y5">_xll.FreeSpace(W5,A5)</f>
+      <c r="Y5" s="23">
+        <f>_xll.FreeSpace(W5,A5)</f>
         <v>150.48101255390816</v>
       </c>
-      <c r="Z5" s="23" cm="1">
-        <f t="array" ref="Z5">_xll.ITMPointToPoint(D5,G5,B5,C5,E5,F5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100,TerHandler,TerDirectory)</f>
+      <c r="Z5" s="23">
+        <f>_xll.ITMPointToPoint(D5,G5,B5,C5,E5,F5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100,TerHandler,TerDirectory)</f>
         <v>248.46459419519601</v>
       </c>
-      <c r="AA5" s="23" cm="1">
-        <f t="array" ref="AA5">_xll.ITMArea(D5,G5,N5,O5,W5,L5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100)</f>
+      <c r="AA5" s="23">
+        <f>_xll.ITMArea(D5,G5,N5,O5,W5,L5,M5,I5,A5,H5,K5,J5,P5,Q5*100,R5*100,S5*100)</f>
         <v>210.56824850094489</v>
       </c>
-      <c r="AB5" s="23" cm="1">
-        <f t="array" ref="AB5">_xll.P676_SpecificAttenuation_dB(A5/1000,T5,U5,V5,W5)</f>
+      <c r="AB5" s="23">
+        <f>_xll.P528_5(W5,MIN(D5,G5),MAX(D5,G5),A5,H5,Q5*100)</f>
+        <v>202.09473080295425</v>
+      </c>
+      <c r="AC5" s="23">
+        <f>_xll.P676_SpecificAttenuation_dB(A5/1000,T5,U5,V5,W5)</f>
         <v>1.1503823038844661</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>6725</v>
+        <v>7800</v>
       </c>
       <c r="B6" s="2">
-        <v>36.5</v>
+        <v>39.566355999999999</v>
       </c>
       <c r="C6" s="2">
-        <v>-82.2</v>
+        <v>-77.013035000000002</v>
       </c>
       <c r="D6" s="2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2">
-        <v>36.82</v>
+        <v>39.634782999999999</v>
       </c>
       <c r="F6" s="2">
-        <v>-82.25</v>
+        <v>-78.231067999999993</v>
       </c>
       <c r="G6" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -5191,49 +5506,53 @@
       <c r="P6" s="2">
         <v>0</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="3">
         <v>0.5</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="3">
         <v>0.5</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="3">
         <v>0.5</v>
       </c>
-      <c r="T6" s="23" cm="1">
-        <f t="array" ref="T6">_xll.Celsius_to_Kelvin(15)</f>
+      <c r="T6" s="23">
+        <f>_xll.Celsius_to_Kelvin(15)</f>
         <v>288.14999999999998</v>
       </c>
-      <c r="U6" s="23" cm="1">
-        <f t="array" ref="U6">_xll.gpm3_to_hPa(7.5,T6)</f>
+      <c r="U6" s="23">
+        <f>_xll.gpm3_to_hPa(7.5,T6)</f>
         <v>9.9728887863405635</v>
       </c>
       <c r="V6" s="2">
         <v>1013.25</v>
       </c>
-      <c r="W6" s="23" cm="1">
-        <f t="array" ref="W6">_xll.DistKm(B6,C6,E6,F6)</f>
-        <v>35.791078240559798</v>
-      </c>
-      <c r="X6" s="23" t="b" cm="1">
-        <f t="array" ref="X6">_xll.IsLOS(B6,C6,E6,F6,D6,G6,1,TerDirectory)</f>
+      <c r="W6" s="23">
+        <f>_xll.DistKm(B6,C6,E6,F6)</f>
+        <v>104.89071248171258</v>
+      </c>
+      <c r="X6" s="23" t="b">
+        <f>_xll.IsLOS(B6,C6,E6,F6,D6,G6,1,TerDirectory)</f>
         <v>0</v>
       </c>
-      <c r="Y6" s="23" cm="1">
-        <f t="array" ref="Y6">_xll.FreeSpace(W6,A6)</f>
-        <v>140.07934141598673</v>
-      </c>
-      <c r="Z6" s="23" cm="1">
-        <f t="array" ref="Z6">_xll.ITMPointToPoint(D6,G6,B6,C6,E6,F6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100,TerHandler,TerDirectory)</f>
-        <v>229.3596488564566</v>
-      </c>
-      <c r="AA6" s="23" cm="1">
-        <f t="array" ref="AA6">_xll.ITMArea(D6,G6,N6,O6,W6,L6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100)</f>
-        <v>166.90495037329015</v>
-      </c>
-      <c r="AB6" s="23" cm="1">
-        <f t="array" ref="AB6">_xll.P676_SpecificAttenuation_dB(A6/1000,T6,U6,V6,W6)</f>
-        <v>0.36111607479468177</v>
+      <c r="Y6" s="23">
+        <f>_xll.FreeSpace(W6,A6)</f>
+        <v>150.70663276210195</v>
+      </c>
+      <c r="Z6" s="23">
+        <f>_xll.ITMPointToPoint(D6,G6,B6,C6,E6,F6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100,TerHandler,TerDirectory)</f>
+        <v>249.09955255980461</v>
+      </c>
+      <c r="AA6" s="23">
+        <f>_xll.ITMArea(D6,G6,N6,O6,W6,L6,M6,I6,A6,H6,K6,J6,P6,Q6*100,R6*100,S6*100)</f>
+        <v>210.90096703099209</v>
+      </c>
+      <c r="AB6" s="23">
+        <f>_xll.P528_5(W6,MIN(D6,G6),MAX(D6,G6),A6,H6,Q6*100)</f>
+        <v>202.43775009526331</v>
+      </c>
+      <c r="AC6" s="23">
+        <f>_xll.P676_SpecificAttenuation_dB(A6/1000,T6,U6,V6,W6)</f>
+        <v>1.1734919908906527</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
@@ -5241,7 +5560,7 @@
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="X7" s="17" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Z7" s="28">
         <v>0</v>
@@ -5252,20 +5571,20 @@
       <c r="R8" s="8"/>
       <c r="S8" s="8"/>
       <c r="X8" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z8" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z8" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="AA8" s="31"/>
-      <c r="AB8" s="31"/>
-      <c r="AC8" s="31"/>
-      <c r="AD8" s="31"/>
-      <c r="AE8" s="31"/>
-      <c r="AF8" s="31"/>
-      <c r="AG8" s="31"/>
-      <c r="AH8" s="31"/>
-      <c r="AI8" s="31"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="37"/>
+      <c r="AC8" s="37"/>
+      <c r="AD8" s="37"/>
+      <c r="AE8" s="37"/>
+      <c r="AF8" s="37"/>
+      <c r="AG8" s="37"/>
+      <c r="AH8" s="37"/>
+      <c r="AI8" s="37"/>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="Q9" s="8"/>
@@ -5283,71 +5602,71 @@
       <c r="S11" s="8"/>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32" t="s">
+      <c r="A12" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="M12" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33" t="s">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="M12" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
-      <c r="V12" s="34"/>
-      <c r="W12" s="34"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="S12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
+      <c r="V12" s="40"/>
+      <c r="W12" s="40"/>
     </row>
     <row r="13" spans="1:35" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>81</v>
@@ -5362,25 +5681,28 @@
         <v>82</v>
       </c>
       <c r="Q13" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R13" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T13" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="AA13" s="51" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
@@ -5414,8 +5736,8 @@
       <c r="J14" s="2">
         <v>3</v>
       </c>
-      <c r="K14" s="23" cm="1">
-        <f t="array" ref="K14">_xll.FDR_Stairs_3_20_40_60_dB(B14,C14,D14,E14,G14,H14,I14,J14,A14,F14)</f>
+      <c r="K14" s="23">
+        <f>_xll.FDR_Stairs_3_20_40_60_dB(B14,C14,D14,E14,G14,H14,I14,J14,A14,F14)</f>
         <v>6.6280214362000329</v>
       </c>
       <c r="M14" s="2">
@@ -5433,62 +5755,85 @@
       <c r="Q14" s="2">
         <v>35887</v>
       </c>
-      <c r="R14" s="23" cm="1">
-        <f t="array" ref="R14">_xll.SatAz(M14,N14,O14,P14,Q14,0)</f>
+      <c r="R14" s="23">
+        <f>_xll.SatAz(M14,N14,O14,P14,Q14,0)</f>
         <v>8.679000600046443</v>
       </c>
-      <c r="S14" s="23" cm="1">
-        <f t="array" ref="S14">_xll.SatAz(M14,N14,O14,P14,Q14,1)</f>
+      <c r="S14" s="23">
+        <f>_xll.SatAz(M14,N14,O14,P14,Q14,1)</f>
         <v>41689.597238153408</v>
       </c>
-      <c r="T14" s="23" cm="1">
-        <f t="array" ref="T14">_xll.SatAz(M14,N14,O14,P14,Q14,2)</f>
+      <c r="T14" s="23">
+        <f>_xll.SatAz(M14,N14,O14,P14,Q14,2)</f>
         <v>97.359615358931151</v>
       </c>
-      <c r="U14" s="23" cm="1">
-        <f t="array" ref="U14">_xll.SatAz(M14,N14,O14,P14,Q14,3)</f>
+      <c r="U14" s="23">
+        <f>_xll.SatAz(M14,N14,O14,P14,Q14,3)</f>
         <v>0.82543716113656984</v>
       </c>
-      <c r="V14" s="23" cm="1">
-        <f t="array" ref="V14">_xll.SatAz(M14,N14,O14,P14,Q14,4)</f>
+      <c r="V14" s="23">
+        <f>_xll.SatAz(M14,N14,O14,P14,Q14,4)</f>
         <v>13.318849480844628</v>
       </c>
-      <c r="W14" s="23" t="b" cm="1">
-        <f t="array" ref="W14">IF(_xll.SatAz(M14,N14,O14,P14,Q14,5)=0,TRUE,FALSE)</f>
+      <c r="W14" s="23" t="b">
+        <f>IF(_xll.SatAz(M14,N14,O14,P14,Q14,5)=0,TRUE,FALSE)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AA14" s="17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" ht="16.5" x14ac:dyDescent="0.3">
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
+      <c r="AA15" s="50" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="AA16" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
       <c r="S17" s="8"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="AA17" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
       <c r="S18" s="8"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
       <c r="S19" s="8"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="AA19" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
       <c r="S20" s="8"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="AA20" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AA21" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
@@ -5501,174 +5846,189 @@
       <c r="N22" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="AA22" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>50</v>
       </c>
-      <c r="B23" s="23" cm="1">
-        <f t="array" ref="B23">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A23,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B23" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A23,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>176.35416608939531</v>
       </c>
       <c r="M23" s="2">
         <f>A3</f>
         <v>8000</v>
       </c>
-      <c r="N23" s="23" cm="1">
-        <f t="array" ref="N23">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M23,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N23" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M23,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>135.42766979138744</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>60</v>
       </c>
-      <c r="B24" s="23" cm="1">
-        <f t="array" ref="B24">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A24,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B24" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A24,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>186.87976908830476</v>
       </c>
       <c r="M24" s="2">
         <f>M23+500</f>
         <v>8500</v>
       </c>
-      <c r="N24" s="23" cm="1">
-        <f t="array" ref="N24">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M24,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N24" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M24,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>135.95371367721219</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="AA24" s="17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>70</v>
       </c>
-      <c r="B25" s="23" cm="1">
-        <f t="array" ref="B25">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A25,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B25" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A25,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>197.24551913339644</v>
       </c>
       <c r="M25" s="2">
         <f t="shared" ref="M25:M38" si="0">M24+500</f>
         <v>9000</v>
       </c>
-      <c r="N25" s="23" cm="1">
-        <f t="array" ref="N25">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M25,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N25" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M25,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>136.44968437376377</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="AA25" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>80</v>
       </c>
-      <c r="B26" s="23" cm="1">
-        <f t="array" ref="B26">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A26,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B26" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A26,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>207.52789850239242</v>
       </c>
       <c r="M26" s="2">
         <f t="shared" si="0"/>
         <v>9500</v>
       </c>
-      <c r="N26" s="23" cm="1">
-        <f t="array" ref="N26">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M26,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N26" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M26,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>136.91883544733909</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="AA26" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>90</v>
       </c>
-      <c r="B27" s="23" cm="1">
-        <f t="array" ref="B27">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A27,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B27" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A27,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>209.4443793957183</v>
       </c>
       <c r="M27" s="2">
         <f t="shared" si="0"/>
         <v>10000</v>
       </c>
-      <c r="N27" s="23" cm="1">
-        <f t="array" ref="N27">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M27,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N27" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M27,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>137.36391944334778</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="AA27" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>100</v>
       </c>
-      <c r="B28" s="23" cm="1">
-        <f t="array" ref="B28">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A28,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B28" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A28,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>210.66103070828476</v>
       </c>
       <c r="M28" s="2">
         <f t="shared" si="0"/>
         <v>10500</v>
       </c>
-      <c r="N28" s="23" cm="1">
-        <f t="array" ref="N28">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M28,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N28" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M28,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>137.78728575442187</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>110</v>
       </c>
-      <c r="B29" s="23" cm="1">
-        <f t="array" ref="B29">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A29,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B29" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A29,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>211.79807317762641</v>
       </c>
       <c r="M29" s="2">
         <f t="shared" si="0"/>
         <v>11000</v>
       </c>
-      <c r="N29" s="23" cm="1">
-        <f t="array" ref="N29">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M29,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N29" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M29,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>138.1909557003485</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>120</v>
       </c>
-      <c r="B30" s="23" cm="1">
-        <f t="array" ref="B30">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A30,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B30" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A30,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>212.88192518947073</v>
       </c>
       <c r="M30" s="2">
         <f t="shared" si="0"/>
         <v>11500</v>
       </c>
-      <c r="N30" s="23" cm="1">
-        <f t="array" ref="N30">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M30,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N30" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M30,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>138.57668090486609</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>130</v>
       </c>
-      <c r="B31" s="23" cm="1">
-        <f t="array" ref="B31">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A31,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B31" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A31,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>213.93526701187233</v>
       </c>
       <c r="M31" s="2">
         <f t="shared" si="0"/>
         <v>12000</v>
       </c>
-      <c r="N31" s="23" cm="1">
-        <f t="array" ref="N31">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M31,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N31" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M31,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>138.94598923918485</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>140</v>
       </c>
-      <c r="B32" s="23" cm="1">
-        <f t="array" ref="B32">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A32,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B32" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A32,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>214.9770617162292</v>
       </c>
       <c r="M32" s="2">
         <f t="shared" si="0"/>
         <v>12500</v>
       </c>
-      <c r="N32" s="23" cm="1">
-        <f t="array" ref="N32">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M32,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N32" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M32,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>139.30022138052666</v>
       </c>
     </row>
@@ -5676,16 +6036,16 @@
       <c r="A33" s="2">
         <v>150</v>
       </c>
-      <c r="B33" s="23" cm="1">
-        <f t="array" ref="B33">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A33,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B33" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A33,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>216.02224872255118</v>
       </c>
       <c r="M33" s="2">
         <f t="shared" si="0"/>
         <v>13000</v>
       </c>
-      <c r="N33" s="23" cm="1">
-        <f t="array" ref="N33">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M33,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N33" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M33,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>139.64056019618354</v>
       </c>
     </row>
@@ -5693,16 +6053,16 @@
       <c r="A34" s="2">
         <v>160</v>
       </c>
-      <c r="B34" s="23" cm="1">
-        <f t="array" ref="B34">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A34,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B34" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A34,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>217.08146223455873</v>
       </c>
       <c r="M34" s="2">
         <f t="shared" si="0"/>
         <v>13500</v>
       </c>
-      <c r="N34" s="23" cm="1">
-        <f t="array" ref="N34">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M34,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N34" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M34,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>139.96805457904148</v>
       </c>
     </row>
@@ -5710,16 +6070,16 @@
       <c r="A35" s="2">
         <v>170</v>
       </c>
-      <c r="B35" s="23" cm="1">
-        <f t="array" ref="B35">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A35,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B35" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A35,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>218.16101303187853</v>
       </c>
       <c r="M35" s="2">
         <f t="shared" si="0"/>
         <v>14000</v>
       </c>
-      <c r="N35" s="23" cm="1">
-        <f t="array" ref="N35">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M35,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N35" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M35,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>140.2836389462158</v>
       </c>
     </row>
@@ -5727,16 +6087,16 @@
       <c r="A36" s="2">
         <v>180</v>
       </c>
-      <c r="B36" s="23" cm="1">
-        <f t="array" ref="B36">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A36,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B36" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A36,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>219.26323500631244</v>
       </c>
       <c r="M36" s="2">
         <f t="shared" si="0"/>
         <v>14500</v>
       </c>
-      <c r="N36" s="23" cm="1">
-        <f t="array" ref="N36">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M36,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N36" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M36,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>140.58814931456496</v>
       </c>
     </row>
@@ -5744,16 +6104,16 @@
       <c r="A37" s="2">
         <v>190</v>
       </c>
-      <c r="B37" s="23" cm="1">
-        <f t="array" ref="B37">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A37,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B37" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A37,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>220.3871640114109</v>
       </c>
       <c r="M37" s="2">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
-      <c r="N37" s="23" cm="1">
-        <f t="array" ref="N37">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M37,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N37" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M37,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>140.88233664983366</v>
       </c>
     </row>
@@ -5761,16 +6121,16 @@
       <c r="A38" s="2">
         <v>200</v>
       </c>
-      <c r="B38" s="23" cm="1">
-        <f t="array" ref="B38">_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A38,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
+      <c r="B38" s="23">
+        <f>_xll.ITMArea($D$3,$G$3,$N$3,$O$3,A38,$L$3,$M$3,$I$3,$A$3,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100)</f>
         <v>221.52942277502015</v>
       </c>
       <c r="M38" s="2">
         <f t="shared" si="0"/>
         <v>15500</v>
       </c>
-      <c r="N38" s="23" cm="1">
-        <f t="array" ref="N38">_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M38,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
+      <c r="N38" s="23">
+        <f>_xll.ITMPointToPoint($D$3,$G$3,$B$3,$C$3,$E$3,$F$3,$M$3,$I$3,M38,$H$3,$K$3,$J$3,$P$3,$Q$3*100,$R$3*100,$S$3*100,TerHandler,TerDirectory)</f>
         <v>141.16687802613515</v>
       </c>
     </row>
@@ -5790,6 +6150,305 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A0CF99E-3E17-49E1-9C91-44E97FB772F4}">
+  <dimension ref="B1:I32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B1" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="G3" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="48" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="23">
+        <v>800</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>212</v>
+      </c>
+      <c r="G4" s="48" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="49" cm="1">
+        <f t="array" ref="H4">_xll.OkumHataITU529(C4,C5,C6,C7,IF(C8="Urban",0,IF(C8="Suburban",1,2)),IF(C9="Small/Medium",0,1),C10,C11)</f>
+        <v>149.65575310666375</v>
+      </c>
+      <c r="I4" s="48" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="23">
+        <v>100</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="H5" s="49" cm="1">
+        <f t="array" ref="H5">_xll.OkumHataDavidson(C4,C5,C6,C7,IF(C8="Urban",0,IF(C8="Suburban",1,2)),IF(C9="Small/Medium",0,1),C10,C11)</f>
+        <v>149.65575310666375</v>
+      </c>
+      <c r="I5" s="48" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="H6" s="49" cm="1">
+        <f t="array" ref="H6">_xll.Cost231(C4,C5,C6,C7,IF(C8="Urban",0,IF(C8="Suburban",1,2)),IF(C9="Small/Medium",0,1),C10,C11)</f>
+        <v>151.86347246019758</v>
+      </c>
+      <c r="I6" s="48" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="23">
+        <v>10</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="48" t="s">
+        <v>221</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="48"/>
+      <c r="G8" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="48" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="48"/>
+      <c r="G9" s="48" t="s">
+        <v>213</v>
+      </c>
+      <c r="H9" s="49" cm="1">
+        <f t="array" ref="H9">_xll.OkumHata529FieldStrength(C4,C5,C6,C7,IF(C9="Small/Medium",0,1),IF(C8="Urban",0,IF(C8="Suburban",1,2)),C10,C11,C12)</f>
+        <v>47.776046633175127</v>
+      </c>
+      <c r="I9" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="48" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="23">
+        <v>50</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>228</v>
+      </c>
+      <c r="G10" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="H10" s="49" cm="1">
+        <f t="array" ref="H10">_xll.OkumHataDavidsonFieldStrength(C4,C5,C6,C7,IF(C9="Small/Medium",0,1),IF(C8="Urban",0,IF(C8="Suburban",1,2)),C10,C11,C12)</f>
+        <v>47.766046633175137</v>
+      </c>
+      <c r="I10" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="48" t="s">
+        <v>229</v>
+      </c>
+      <c r="C11" s="23">
+        <v>50</v>
+      </c>
+      <c r="D11" s="48" t="s">
+        <v>228</v>
+      </c>
+      <c r="G11" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="H11" s="49" cm="1">
+        <f t="array" ref="H11">_xll.Cost231FieldStrength(C4,C5,C6,C7,IF(C9="Small/Medium",0,1),IF(C8="Urban",0,IF(C8="Suburban",1,2)),C10,C11,C12)</f>
+        <v>45.558327279641254</v>
+      </c>
+      <c r="I11" s="48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" s="23">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="31" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="17" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="17" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="17" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="31" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="17" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="17" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="17" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="17" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="31" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="17" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="17" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="17" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="17" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B32:F32"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9" xr:uid="{B8706703-3002-4F7F-8B7D-6B9FC3EF3728}">
+      <formula1>"Small/Medium,Large"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8" xr:uid="{17CC1B1C-72F1-442B-A739-F2B19E228B28}">
+      <formula1>"Urban,Suburban,Open"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:AC37"/>
@@ -5808,16 +6467,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="B1" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
+      <c r="B1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
     </row>
     <row r="2" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="B2" s="13" t="s">
@@ -5827,7 +6486,7 @@
         <v>82</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>81</v>
@@ -5836,40 +6495,40 @@
         <v>82</v>
       </c>
       <c r="G2" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="J2" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="H2" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>138</v>
-      </c>
       <c r="K2" s="13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O2" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R2" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>6</v>
@@ -5907,25 +6566,25 @@
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B3" s="24" cm="1">
-        <f t="array" ref="B3">_xll.GetLatitude(E3,F3,20,80)</f>
+        <v>138</v>
+      </c>
+      <c r="B3" s="24">
+        <f>_xll.GetLatitude(E3,F3,20,80)</f>
         <v>39.430778738197418</v>
       </c>
-      <c r="C3" s="24" cm="1">
-        <f t="array" ref="C3">_xll.GetLongitude(E3,F3,20,80)</f>
+      <c r="C3" s="24">
+        <f>_xll.GetLongitude(E3,F3,20,80)</f>
         <v>-77.408737187096492</v>
       </c>
       <c r="D3" s="14">
         <v>45.72</v>
       </c>
-      <c r="E3" s="2" cm="1">
-        <f t="array" ref="E3">_xll.DMS2DecDeg("392359N")</f>
+      <c r="E3" s="2">
+        <f>_xll.DMS2DecDeg("392359N")</f>
         <v>39.399722222222223</v>
       </c>
-      <c r="F3" s="2" cm="1">
-        <f t="array" ref="F3">_xll.DMS2DecDeg("0773815W")</f>
+      <c r="F3" s="2">
+        <f>_xll.DMS2DecDeg("0773815W")</f>
         <v>-77.637500000000003</v>
       </c>
       <c r="G3" s="2">
@@ -5950,17 +6609,17 @@
         <v>3.5</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O3" s="2">
         <v>4</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q3" s="23" cm="1">
-        <f t="array" ref="Q3">_xll.Bearing(E3,F3,B3,C3)</f>
-        <v>80.000000000000057</v>
+        <v>144</v>
+      </c>
+      <c r="Q3" s="23">
+        <f>_xll.Bearing(E3,F3,B3,C3)</f>
+        <v>79.999999999996078</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="20">
@@ -5999,25 +6658,25 @@
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="B4" s="23" cm="1">
-        <f t="array" ref="B4">_xll.DMS2DecDeg("392400N")</f>
+        <v>139</v>
+      </c>
+      <c r="B4" s="23">
+        <f>_xll.DMS2DecDeg("392400N")</f>
         <v>39.4</v>
       </c>
-      <c r="C4" s="23" cm="1">
-        <f t="array" ref="C4">_xll.DMS2DecDeg("0772400W")</f>
+      <c r="C4" s="23">
+        <f>_xll.DMS2DecDeg("0772400W")</f>
         <v>-77.400000000000006</v>
       </c>
       <c r="D4" s="2">
         <v>45.72</v>
       </c>
-      <c r="E4" s="24" cm="1">
-        <f t="array" ref="E4">_xll.GetLatitude(B4,C4,20,275)</f>
+      <c r="E4" s="24">
+        <f>_xll.GetLatitude(B4,C4,20,275)</f>
         <v>39.415470445255202</v>
       </c>
-      <c r="F4" s="24" cm="1">
-        <f t="array" ref="F4">_xll.GetLongitude(B4,C4,20,275)</f>
+      <c r="F4" s="24">
+        <f>_xll.GetLongitude(B4,C4,20,275)</f>
         <v>-77.631357303040929</v>
       </c>
       <c r="G4" s="14">
@@ -6042,73 +6701,73 @@
         <v>3.5</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O4" s="2">
         <v>3</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q4" s="23" cm="1">
-        <f t="array" ref="Q4">_xll.Bearing(B4,C4,E4,F4)</f>
-        <v>274.99999999999312</v>
-      </c>
-      <c r="R4" s="23" cm="1">
-        <f t="array" ref="R4">_xll.Delta_Bearing(Q4,Q3)</f>
-        <v>165.00000000000693</v>
+        <v>137</v>
+      </c>
+      <c r="Q4" s="23">
+        <f>_xll.Bearing(B4,C4,E4,F4)</f>
+        <v>274.9999999999921</v>
+      </c>
+      <c r="R4" s="23">
+        <f>_xll.Delta_Bearing(Q4,Q3)</f>
+        <v>165.00000000000398</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="L6" s="17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E7">
         <f>_xll.Bearing(B4,C4,E3,F3)</f>
-        <v>269.98900055432966</v>
+        <v>269.98900055432671</v>
       </c>
       <c r="F7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G7">
         <f>_xll.DistKm(E3,F3,B4,C4)</f>
         <v>20.457487034523673</v>
       </c>
       <c r="L7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E8">
         <f>_xll.Bearing(E3,F3,B4,C4)</f>
-        <v>89.838252372911114</v>
+        <v>89.838252372907164</v>
       </c>
       <c r="L8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="N9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="K10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
@@ -6116,7 +6775,7 @@
         <v>-29.5</v>
       </c>
       <c r="L11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
@@ -6124,7 +6783,7 @@
         <v>33.5</v>
       </c>
       <c r="L12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
@@ -6132,12 +6791,12 @@
         <v>16</v>
       </c>
       <c r="L13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="L14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
@@ -6145,17 +6804,17 @@
         <v>8</v>
       </c>
       <c r="L15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="L16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="11:22" x14ac:dyDescent="0.25">
       <c r="L17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="11:22" x14ac:dyDescent="0.25">
@@ -6163,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="11:22" x14ac:dyDescent="0.25">
@@ -6171,7 +6830,7 @@
         <v>3</v>
       </c>
       <c r="L19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="11:22" x14ac:dyDescent="0.25">
@@ -6179,7 +6838,7 @@
         <v>4</v>
       </c>
       <c r="L20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="11:22" x14ac:dyDescent="0.25">
@@ -6187,50 +6846,50 @@
         <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K24" s="18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L24" s="18" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M24" s="18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N24" s="18" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O24" s="18" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P24" s="18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q24" s="18" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="R24" s="18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="S24" s="18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T24" s="18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="U24" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="V24" s="18" t="s">
         <v>166</v>
-      </c>
-      <c r="V24" s="18" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="25" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K25" s="16" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L25" s="2">
         <f>N25-O25-P25-Q25+R25+S25+T25+U25+V25</f>
@@ -6249,8 +6908,8 @@
       <c r="Q25" s="2">
         <v>8</v>
       </c>
-      <c r="R25" s="23" cm="1">
-        <f t="array" ref="R25">_xll.ITMArea(D4,G3,X3,Y3,_xll.DistKm(B4,C4,E3,F3),V3,W3,S3,H3,IF(N3="V",1,0),U3,T3,Z3,AA3*100,AB3*100,AC3*100)</f>
+      <c r="R25" s="23">
+        <f>_xll.ITMArea(D4,G3,X3,Y3,_xll.DistKm(B4,C4,E3,F3),V3,W3,S3,H3,IF(N3="V",1,0),U3,T3,Z3,AA3*100,AB3*100,AC3*100)</f>
         <v>136.65456853650161</v>
       </c>
       <c r="S25" s="2">
@@ -6287,8 +6946,8 @@
       <c r="Q26" s="2">
         <v>8</v>
       </c>
-      <c r="R26" s="23" cm="1">
-        <f t="array" ref="R26">_xll.ITMPointToPointCR(D4,G3,B4,C4,E3,F3,W3,S3,H3,IF(N3="V",1,0),U3,T3,Z3,AA3*100,AB3*100,0,TerDirectory)</f>
+      <c r="R26" s="23">
+        <f>_xll.ITMPointToPointCR(D4,G3,B4,C4,E3,F3,W3,S3,H3,IF(N3="V",1,0),U3,T3,Z3,AA3*100,AB3*100,0,TerDirectory)</f>
         <v>194.26920385903014</v>
       </c>
       <c r="S26" s="2">
@@ -6306,7 +6965,7 @@
     </row>
     <row r="28" spans="11:22" x14ac:dyDescent="0.25">
       <c r="K28" s="17" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L28">
         <f>-29.5-(-102.5)</f>
@@ -6317,41 +6976,41 @@
         <v>=</v>
       </c>
       <c r="N28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="11:22" x14ac:dyDescent="0.25">
       <c r="O29" t="s">
-        <v>180</v>
-      </c>
-      <c r="P29" s="27" cm="1">
-        <f t="array" ref="P29">_xll.Delta_Bearing(_xll.Bearing(B4,C4,E4,F4),_xll.Bearing(B4,C4,E3,F3))</f>
-        <v>5.0109994456634581</v>
+        <v>182</v>
+      </c>
+      <c r="P29" s="27">
+        <f xml:space="preserve"> _xll.Delta_Bearing(_xll.Bearing(B4,C4,E4,F4),_xll.Bearing(B4,C4,E3,F3))</f>
+        <v>5.0109994456653908</v>
       </c>
       <c r="Q29" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="11:22" x14ac:dyDescent="0.25">
       <c r="O30" t="s">
+        <v>183</v>
+      </c>
+      <c r="P30" s="27">
+        <f xml:space="preserve"> _xll.Delta_Bearing(_xll.Bearing(E4,F4,B4,C4),_xll.Bearing(E4,F4,B3,C3))</f>
+        <v>9.9904702043319702</v>
+      </c>
+      <c r="Q30" t="s">
         <v>181</v>
-      </c>
-      <c r="P30" s="27" cm="1">
-        <f t="array" ref="P30">_xll.Delta_Bearing(_xll.Bearing(E4,F4,B4,C4),_xll.Bearing(E4,F4,B3,C3))</f>
-        <v>9.9904702043319702</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="31" spans="11:22" x14ac:dyDescent="0.25">
       <c r="L31" s="17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="11:22" ht="17.25" x14ac:dyDescent="0.25">
       <c r="L32" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="12:13" x14ac:dyDescent="0.25">
@@ -6362,22 +7021,22 @@
     </row>
     <row r="34" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="12:13" x14ac:dyDescent="0.25">
       <c r="M35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="12:13" x14ac:dyDescent="0.25">
       <c r="M37" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -6391,10 +7050,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:G23"/>
+  <dimension ref="A2:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="6" width="9.85546875" customWidth="1"/>
@@ -6402,25 +7061,25 @@
   <sheetData>
     <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>112</v>
-      </c>
       <c r="G2" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6436,16 +7095,16 @@
       <c r="D3" s="12">
         <v>0.75</v>
       </c>
-      <c r="E3" s="25" cm="1">
-        <f t="array" ref="E3">_xll.BmWToGain_dB(C3,D3)</f>
+      <c r="E3" s="25">
+        <f>_xll.BmWToGain_dB(C3,D3)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F3" s="25" cm="1">
-        <f t="array" ref="F3">_xll.StatGainWolfGain(B3,A3)</f>
+      <c r="F3" s="25">
+        <f>_xll.StatGainWolfGain(B3,A3)</f>
         <v>43</v>
       </c>
-      <c r="G3" s="25" cm="1">
-        <f t="array" ref="G3">_xll.StatGain(B3,A3)</f>
+      <c r="G3" s="25">
+        <f>_xll.StatGain(B3,A3)</f>
         <v>43</v>
       </c>
     </row>
@@ -6462,16 +7121,16 @@
       <c r="D4" s="12">
         <v>0.75</v>
       </c>
-      <c r="E4" s="25" cm="1">
-        <f t="array" ref="E4">_xll.BmWToGain_dB(C4,D4)</f>
+      <c r="E4" s="25">
+        <f>_xll.BmWToGain_dB(C4,D4)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F4" s="25" cm="1">
-        <f t="array" ref="F4">_xll.StatGainWolfGain(B4,A4)</f>
+      <c r="F4" s="25">
+        <f>_xll.StatGainWolfGain(B4,A4)</f>
         <v>41.004737685031124</v>
       </c>
-      <c r="G4" s="25" cm="1">
-        <f t="array" ref="G4">_xll.StatGain(B4,A4)</f>
+      <c r="G4" s="25">
+        <f>_xll.StatGain(B4,A4)</f>
         <v>41.004737685031124</v>
       </c>
     </row>
@@ -6488,16 +7147,16 @@
       <c r="D5" s="12">
         <v>0.75</v>
       </c>
-      <c r="E5" s="25" cm="1">
-        <f t="array" ref="E5">_xll.BmWToGain_dB(C5,D5)</f>
+      <c r="E5" s="25">
+        <f>_xll.BmWToGain_dB(C5,D5)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F5" s="25" cm="1">
-        <f t="array" ref="F5">_xll.StatGainWolfGain(B5,A5)</f>
+      <c r="F5" s="25">
+        <f>_xll.StatGainWolfGain(B5,A5)</f>
         <v>35.018950740124481</v>
       </c>
-      <c r="G5" s="25" cm="1">
-        <f t="array" ref="G5">_xll.StatGain(B5,A5)</f>
+      <c r="G5" s="25">
+        <f>_xll.StatGain(B5,A5)</f>
         <v>35.018950740124481</v>
       </c>
     </row>
@@ -6514,16 +7173,16 @@
       <c r="D6" s="12">
         <v>0.75</v>
       </c>
-      <c r="E6" s="25" cm="1">
-        <f t="array" ref="E6">_xll.BmWToGain_dB(C6,D6)</f>
+      <c r="E6" s="25">
+        <f>_xll.BmWToGain_dB(C6,D6)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F6" s="25" cm="1">
-        <f t="array" ref="F6">_xll.StatGainWolfGain(B6,A6)</f>
+      <c r="F6" s="25">
+        <f>_xll.StatGainWolfGain(B6,A6)</f>
         <v>25.25</v>
       </c>
-      <c r="G6" s="25" cm="1">
-        <f t="array" ref="G6">_xll.StatGain(B6,A6)</f>
+      <c r="G6" s="25">
+        <f>_xll.StatGain(B6,A6)</f>
         <v>25.25</v>
       </c>
     </row>
@@ -6540,16 +7199,16 @@
       <c r="D7" s="12">
         <v>0.75</v>
       </c>
-      <c r="E7" s="25" cm="1">
-        <f t="array" ref="E7">_xll.BmWToGain_dB(C7,D7)</f>
+      <c r="E7" s="25">
+        <f>_xll.BmWToGain_dB(C7,D7)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F7" s="25" cm="1">
-        <f t="array" ref="F7">_xll.StatGainWolfGain(B7,A7)</f>
+      <c r="F7" s="25">
+        <f>_xll.StatGainWolfGain(B7,A7)</f>
         <v>23.974250108400469</v>
       </c>
-      <c r="G7" s="25" cm="1">
-        <f t="array" ref="G7">_xll.StatGain(B7,A7)</f>
+      <c r="G7" s="25">
+        <f>_xll.StatGain(B7,A7)</f>
         <v>23.974250108400469</v>
       </c>
     </row>
@@ -6566,16 +7225,16 @@
       <c r="D8" s="12">
         <v>0.75</v>
       </c>
-      <c r="E8" s="25" cm="1">
-        <f t="array" ref="E8">_xll.BmWToGain_dB(C8,D8)</f>
+      <c r="E8" s="25">
+        <f>_xll.BmWToGain_dB(C8,D8)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F8" s="25" cm="1">
-        <f t="array" ref="F8">_xll.StatGainWolfGain(B8,A8)</f>
+      <c r="F8" s="25">
+        <f>_xll.StatGainWolfGain(B8,A8)</f>
         <v>21.551499783199059</v>
       </c>
-      <c r="G8" s="25" cm="1">
-        <f t="array" ref="G8">_xll.StatGain(B8,A8)</f>
+      <c r="G8" s="25">
+        <f>_xll.StatGain(B8,A8)</f>
         <v>21.551499783199059</v>
       </c>
     </row>
@@ -6592,16 +7251,16 @@
       <c r="D9" s="12">
         <v>0.75</v>
       </c>
-      <c r="E9" s="25" cm="1">
-        <f t="array" ref="E9">_xll.BmWToGain_dB(C9,D9)</f>
+      <c r="E9" s="25">
+        <f>_xll.BmWToGain_dB(C9,D9)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F9" s="25" cm="1">
-        <f t="array" ref="F9">_xll.StatGainWolfGain(B9,A9)</f>
+      <c r="F9" s="25">
+        <f>_xll.StatGainWolfGain(B9,A9)</f>
         <v>19.571968632008439</v>
       </c>
-      <c r="G9" s="25" cm="1">
-        <f t="array" ref="G9">_xll.StatGain(B9,A9)</f>
+      <c r="G9" s="25">
+        <f>_xll.StatGain(B9,A9)</f>
         <v>19.571968632008439</v>
       </c>
     </row>
@@ -6618,16 +7277,16 @@
       <c r="D10" s="12">
         <v>0.75</v>
       </c>
-      <c r="E10" s="25" cm="1">
-        <f t="array" ref="E10">_xll.BmWToGain_dB(C10,D10)</f>
+      <c r="E10" s="25">
+        <f>_xll.BmWToGain_dB(C10,D10)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F10" s="25" cm="1">
-        <f t="array" ref="F10">_xll.StatGainWolfGain(B10,A10)</f>
+      <c r="F10" s="25">
+        <f>_xll.StatGainWolfGain(B10,A10)</f>
         <v>17.898298891243108</v>
       </c>
-      <c r="G10" s="25" cm="1">
-        <f t="array" ref="G10">_xll.StatGain(B10,A10)</f>
+      <c r="G10" s="25">
+        <f>_xll.StatGain(B10,A10)</f>
         <v>17.898298891243108</v>
       </c>
     </row>
@@ -6644,16 +7303,16 @@
       <c r="D11" s="12">
         <v>0.75</v>
       </c>
-      <c r="E11" s="25" cm="1">
-        <f t="array" ref="E11">_xll.BmWToGain_dB(C11,D11)</f>
+      <c r="E11" s="25">
+        <f>_xll.BmWToGain_dB(C11,D11)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F11" s="25" cm="1">
-        <f t="array" ref="F11">_xll.StatGainWolfGain(B11,A11)</f>
+      <c r="F11" s="25">
+        <f>_xll.StatGainWolfGain(B11,A11)</f>
         <v>16.448500216800941</v>
       </c>
-      <c r="G11" s="25" cm="1">
-        <f t="array" ref="G11">_xll.StatGain(B11,A11)</f>
+      <c r="G11" s="25">
+        <f>_xll.StatGain(B11,A11)</f>
         <v>16.448500216800941</v>
       </c>
     </row>
@@ -6670,16 +7329,16 @@
       <c r="D12" s="12">
         <v>0.75</v>
       </c>
-      <c r="E12" s="25" cm="1">
-        <f t="array" ref="E12">_xll.BmWToGain_dB(C12,D12)</f>
+      <c r="E12" s="25">
+        <f>_xll.BmWToGain_dB(C12,D12)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F12" s="25" cm="1">
-        <f t="array" ref="F12">_xll.StatGainWolfGain(B12,A12)</f>
+      <c r="F12" s="25">
+        <f>_xll.StatGainWolfGain(B12,A12)</f>
         <v>15.169687155616408</v>
       </c>
-      <c r="G12" s="25" cm="1">
-        <f t="array" ref="G12">_xll.StatGain(B12,A12)</f>
+      <c r="G12" s="25">
+        <f>_xll.StatGain(B12,A12)</f>
         <v>15.169687155616408</v>
       </c>
     </row>
@@ -6696,16 +7355,16 @@
       <c r="D13" s="12">
         <v>0.75</v>
       </c>
-      <c r="E13" s="25" cm="1">
-        <f t="array" ref="E13">_xll.BmWToGain_dB(C13,D13)</f>
+      <c r="E13" s="25">
+        <f>_xll.BmWToGain_dB(C13,D13)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F13" s="25" cm="1">
-        <f t="array" ref="F13">_xll.StatGainWolfGain(B13,A13)</f>
+      <c r="F13" s="25">
+        <f>_xll.StatGainWolfGain(B13,A13)</f>
         <v>14.025749891599528</v>
       </c>
-      <c r="G13" s="25" cm="1">
-        <f t="array" ref="G13">_xll.StatGain(B13,A13)</f>
+      <c r="G13" s="25">
+        <f>_xll.StatGain(B13,A13)</f>
         <v>14.025749891599528</v>
       </c>
     </row>
@@ -6722,16 +7381,16 @@
       <c r="D14" s="12">
         <v>0.75</v>
       </c>
-      <c r="E14" s="25" cm="1">
-        <f t="array" ref="E14">_xll.BmWToGain_dB(C14,D14)</f>
+      <c r="E14" s="25">
+        <f>_xll.BmWToGain_dB(C14,D14)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F14" s="25" cm="1">
-        <f t="array" ref="F14">_xll.StatGainWolfGain(B14,A14)</f>
+      <c r="F14" s="25">
+        <f>_xll.StatGainWolfGain(B14,A14)</f>
         <v>12.990932762643904</v>
       </c>
-      <c r="G14" s="25" cm="1">
-        <f t="array" ref="G14">_xll.StatGain(B14,A14)</f>
+      <c r="G14" s="25">
+        <f>_xll.StatGain(B14,A14)</f>
         <v>12.990932762643904</v>
       </c>
     </row>
@@ -6748,16 +7407,16 @@
       <c r="D15" s="12">
         <v>0.75</v>
       </c>
-      <c r="E15" s="25" cm="1">
-        <f t="array" ref="E15">_xll.BmWToGain_dB(C15,D15)</f>
+      <c r="E15" s="25">
+        <f>_xll.BmWToGain_dB(C15,D15)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F15" s="25" cm="1">
-        <f t="array" ref="F15">_xll.StatGainWolfGain(B15,A15)</f>
+      <c r="F15" s="25">
+        <f>_xll.StatGainWolfGain(B15,A15)</f>
         <v>12.046218740408911</v>
       </c>
-      <c r="G15" s="25" cm="1">
-        <f t="array" ref="G15">_xll.StatGain(B15,A15)</f>
+      <c r="G15" s="25">
+        <f>_xll.StatGain(B15,A15)</f>
         <v>12.046218740408911</v>
       </c>
     </row>
@@ -6774,16 +7433,16 @@
       <c r="D16" s="12">
         <v>0.75</v>
       </c>
-      <c r="E16" s="25" cm="1">
-        <f t="array" ref="E16">_xll.BmWToGain_dB(C16,D16)</f>
+      <c r="E16" s="25">
+        <f>_xll.BmWToGain_dB(C16,D16)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F16" s="25" cm="1">
-        <f t="array" ref="F16">_xll.StatGainWolfGain(B16,A16)</f>
+      <c r="F16" s="25">
+        <f>_xll.StatGainWolfGain(B16,A16)</f>
         <v>11.177166083928611</v>
       </c>
-      <c r="G16" s="25" cm="1">
-        <f t="array" ref="G16">_xll.StatGain(B16,A16)</f>
+      <c r="G16" s="25">
+        <f>_xll.StatGain(B16,A16)</f>
         <v>11.177166083928611</v>
       </c>
     </row>
@@ -6800,16 +7459,16 @@
       <c r="D17" s="12">
         <v>0.75</v>
       </c>
-      <c r="E17" s="25" cm="1">
-        <f t="array" ref="E17">_xll.BmWToGain_dB(C17,D17)</f>
+      <c r="E17" s="25">
+        <f>_xll.BmWToGain_dB(C17,D17)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F17" s="25" cm="1">
-        <f t="array" ref="F17">_xll.StatGainWolfGain(B17,A17)</f>
+      <c r="F17" s="25">
+        <f>_xll.StatGainWolfGain(B17,A17)</f>
         <v>10.37254899964358</v>
       </c>
-      <c r="G17" s="25" cm="1">
-        <f t="array" ref="G17">_xll.StatGain(B17,A17)</f>
+      <c r="G17" s="25">
+        <f>_xll.StatGain(B17,A17)</f>
         <v>10.37254899964358</v>
       </c>
     </row>
@@ -6826,16 +7485,16 @@
       <c r="D18" s="12">
         <v>0.75</v>
       </c>
-      <c r="E18" s="25" cm="1">
-        <f t="array" ref="E18">_xll.BmWToGain_dB(C18,D18)</f>
+      <c r="E18" s="25">
+        <f>_xll.BmWToGain_dB(C18,D18)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F18" s="25" cm="1">
-        <f t="array" ref="F18">_xll.StatGainWolfGain(B18,A18)</f>
+      <c r="F18" s="25">
+        <f>_xll.StatGainWolfGain(B18,A18)</f>
         <v>9.6234684152074976</v>
       </c>
-      <c r="G18" s="25" cm="1">
-        <f t="array" ref="G18">_xll.StatGain(B18,A18)</f>
+      <c r="G18" s="25">
+        <f>_xll.StatGain(B18,A18)</f>
         <v>9.6234684152074976</v>
       </c>
     </row>
@@ -6852,16 +7511,16 @@
       <c r="D19" s="12">
         <v>0.75</v>
       </c>
-      <c r="E19" s="25" cm="1">
-        <f t="array" ref="E19">_xll.BmWToGain_dB(C19,D19)</f>
+      <c r="E19" s="25">
+        <f>_xll.BmWToGain_dB(C19,D19)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F19" s="25" cm="1">
-        <f t="array" ref="F19">_xll.StatGainWolfGain(B19,A19)</f>
+      <c r="F19" s="25">
+        <f>_xll.StatGainWolfGain(B19,A19)</f>
         <v>8.9227503252014131</v>
       </c>
-      <c r="G19" s="25" cm="1">
-        <f t="array" ref="G19">_xll.StatGain(B19,A19)</f>
+      <c r="G19" s="25">
+        <f>_xll.StatGain(B19,A19)</f>
         <v>8.9227503252014131</v>
       </c>
     </row>
@@ -6878,16 +7537,16 @@
       <c r="D20" s="12">
         <v>0.75</v>
       </c>
-      <c r="E20" s="25" cm="1">
-        <f t="array" ref="E20">_xll.BmWToGain_dB(C20,D20)</f>
+      <c r="E20" s="25">
+        <f>_xll.BmWToGain_dB(C20,D20)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F20" s="25" cm="1">
-        <f t="array" ref="F20">_xll.StatGainWolfGain(B20,A20)</f>
+      <c r="F20" s="25">
+        <f>_xll.StatGainWolfGain(B20,A20)</f>
         <v>8.2645268571426804</v>
       </c>
-      <c r="G20" s="25" cm="1">
-        <f t="array" ref="G20">_xll.StatGain(B20,A20)</f>
+      <c r="G20" s="25">
+        <f>_xll.StatGain(B20,A20)</f>
         <v>8.2645268571426804</v>
       </c>
     </row>
@@ -6904,16 +7563,16 @@
       <c r="D21" s="12">
         <v>0.75</v>
       </c>
-      <c r="E21" s="25" cm="1">
-        <f t="array" ref="E21">_xll.BmWToGain_dB(C21,D21)</f>
+      <c r="E21" s="25">
+        <f>_xll.BmWToGain_dB(C21,D21)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F21" s="25" cm="1">
-        <f t="array" ref="F21">_xll.StatGainWolfGain(B21,A21)</f>
+      <c r="F21" s="25">
+        <f>_xll.StatGainWolfGain(B21,A21)</f>
         <v>7.643937264016877</v>
       </c>
-      <c r="G21" s="25" cm="1">
-        <f t="array" ref="G21">_xll.StatGain(B21,A21)</f>
+      <c r="G21" s="25">
+        <f>_xll.StatGain(B21,A21)</f>
         <v>7.643937264016877</v>
       </c>
     </row>
@@ -6930,16 +7589,16 @@
       <c r="D22" s="12">
         <v>0.75</v>
       </c>
-      <c r="E22" s="25" cm="1">
-        <f t="array" ref="E22">_xll.BmWToGain_dB(C22,D22)</f>
+      <c r="E22" s="25">
+        <f>_xll.BmWToGain_dB(C22,D22)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F22" s="25" cm="1">
-        <f t="array" ref="F22">_xll.StatGainWolfGain(B22,A22)</f>
+      <c r="F22" s="25">
+        <f>_xll.StatGainWolfGain(B22,A22)</f>
         <v>7.0569098677788062</v>
       </c>
-      <c r="G22" s="25" cm="1">
-        <f t="array" ref="G22">_xll.StatGain(B22,A22)</f>
+      <c r="G22" s="25">
+        <f>_xll.StatGain(B22,A22)</f>
         <v>7.0569098677788062</v>
       </c>
     </row>
@@ -6956,27 +7615,75 @@
       <c r="D23" s="12">
         <v>0.75</v>
       </c>
-      <c r="E23" s="25" cm="1">
-        <f t="array" ref="E23">_xll.BmWToGain_dB(C23,D23)</f>
+      <c r="E23" s="25">
+        <f>_xll.BmWToGain_dB(C23,D23)</f>
         <v>49.503599999999999</v>
       </c>
-      <c r="F23" s="25" cm="1">
-        <f t="array" ref="F23">_xll.StatGainWolfGain(B23,A23)</f>
+      <c r="F23" s="25">
+        <f>_xll.StatGainWolfGain(B23,A23)</f>
         <v>6.5</v>
       </c>
-      <c r="G23" s="25" cm="1">
-        <f t="array" ref="G23">_xll.StatGain(B23,A23)</f>
+      <c r="G23" s="25">
+        <f>_xll.StatGain(B23,A23)</f>
         <v>6.5</v>
       </c>
     </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="52" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>259</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A27" r:id="rId1" xr:uid="{90B367F7-D5CA-4512-A232-0A140940FDBE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D46"/>
@@ -7000,7 +7707,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="46" t="s">
         <v>42</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -7015,72 +7722,72 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
+      <c r="A3" s="46"/>
       <c r="B3" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="23" cm="1">
-        <f t="array" ref="D3">_xll.Volts_to_dBuV(C3)</f>
+      <c r="D3" s="23">
+        <f>_xll.Volts_to_dBuV(C3)</f>
         <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
+      <c r="A4" s="46"/>
       <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="23" cm="1">
-        <f t="array" ref="D4">_xll.Volts_to_dBV(C4)</f>
+      <c r="D4" s="23">
+        <f>_xll.Volts_to_dBV(C4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="40"/>
+      <c r="A5" s="46"/>
       <c r="B5" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
       </c>
-      <c r="D5" s="23" cm="1">
-        <f t="array" ref="D5">_xll.dBV_to_Volts(C5)</f>
+      <c r="D5" s="23">
+        <f>_xll.dBV_to_Volts(C5)</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="40"/>
+      <c r="A6" s="46"/>
       <c r="B6" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
       </c>
-      <c r="D6" s="23" cm="1">
-        <f t="array" ref="D6">_xll.dBV_to_dBuV(C6)</f>
+      <c r="D6" s="23">
+        <f>_xll.dBV_to_dBuV(C6)</f>
         <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="40"/>
+      <c r="A7" s="46"/>
       <c r="B7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2">
         <v>120</v>
       </c>
-      <c r="D7" s="23" cm="1">
-        <f t="array" ref="D7">_xll.dBuV_to_dBV(C7)</f>
+      <c r="D7" s="23">
+        <f>_xll.dBuV_to_dBV(C7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="46" t="s">
         <v>41</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -7089,78 +7796,78 @@
       <c r="C8" s="2">
         <v>0</v>
       </c>
-      <c r="D8" s="23" cm="1">
-        <f t="array" ref="D8">_xll.dBm_to_Watts(C8)</f>
+      <c r="D8" s="23">
+        <f>_xll.dBm_to_Watts(C8)</f>
         <v>1E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="40"/>
+      <c r="A9" s="46"/>
       <c r="B9" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="2">
         <v>1E-3</v>
       </c>
-      <c r="D9" s="23" cm="1">
-        <f t="array" ref="D9">_xll.Watts_to_dBm(C9)</f>
+      <c r="D9" s="23">
+        <f>_xll.Watts_to_dBm(C9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="40"/>
+      <c r="A10" s="46"/>
       <c r="B10" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="2">
         <v>0</v>
       </c>
-      <c r="D10" s="23" cm="1">
-        <f t="array" ref="D10">_xll.dBW_to_Watts(C10)</f>
+      <c r="D10" s="23">
+        <f>_xll.dBW_to_Watts(C10)</f>
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="40"/>
+      <c r="A11" s="46"/>
       <c r="B11" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="2">
         <v>10</v>
       </c>
-      <c r="D11" s="23" cm="1">
-        <f t="array" ref="D11">_xll.Watts_to_dBW(C11)</f>
+      <c r="D11" s="23">
+        <f>_xll.Watts_to_dBW(C11)</f>
         <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="40"/>
+      <c r="A12" s="46"/>
       <c r="B12" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
       </c>
-      <c r="D12" s="23" cm="1">
-        <f t="array" ref="D12">_xll.dBW_to_dBm(C12)</f>
+      <c r="D12" s="23">
+        <f>_xll.dBW_to_dBm(C12)</f>
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="40"/>
+      <c r="A13" s="46"/>
       <c r="B13" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="2">
         <v>30</v>
       </c>
-      <c r="D13" s="23" cm="1">
-        <f t="array" ref="D13">_xll.dBm_to_dBW(C13)</f>
+      <c r="D13" s="23">
+        <f>_xll.dBm_to_dBW(C13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="46" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -7169,78 +7876,78 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="23" cm="1">
-        <f t="array" ref="D14">_xll.dBuA_to_uA(C14)</f>
+      <c r="D14" s="23">
+        <f>_xll.dBuA_to_uA(C14)</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="40"/>
+      <c r="A15" s="46"/>
       <c r="B15" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="23" cm="1">
-        <f t="array" ref="D15">_xll.uA_to_dBuA(C15)</f>
+      <c r="D15" s="23">
+        <f>_xll.uA_to_dBuA(C15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="40"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
       </c>
-      <c r="D16" s="23" cm="1">
-        <f t="array" ref="D16">_xll.dBA_to_A(C16)</f>
+      <c r="D16" s="23">
+        <f>_xll.dBA_to_A(C16)</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="40"/>
+      <c r="A17" s="46"/>
       <c r="B17" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
-      <c r="D17" s="23" cm="1">
-        <f t="array" ref="D17">_xll.A_to_dBA(C17)</f>
+      <c r="D17" s="23">
+        <f>_xll.A_to_dBA(C17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="40"/>
+      <c r="A18" s="46"/>
       <c r="B18" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
-      <c r="D18" s="23" cm="1">
-        <f t="array" ref="D18">_xll.dBA_to_dBuA(C18)</f>
+      <c r="D18" s="23">
+        <f>_xll.dBA_to_dBuA(C18)</f>
         <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="40"/>
+      <c r="A19" s="46"/>
       <c r="B19" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="2">
         <v>120</v>
       </c>
-      <c r="D19" s="23" cm="1">
-        <f t="array" ref="D19">_xll.dBuA_to_dBA(C19)</f>
+      <c r="D19" s="23">
+        <f>_xll.dBuA_to_dBA(C19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="43" t="s">
         <v>62</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -7249,156 +7956,156 @@
       <c r="C20" s="2">
         <v>0</v>
       </c>
-      <c r="D20" s="23" cm="1">
-        <f t="array" ref="D20">_xll.dBuVpm_to_Vpm(C20)</f>
+      <c r="D20" s="23">
+        <f>_xll.dBuVpm_to_Vpm(C20)</f>
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="38"/>
+      <c r="A21" s="44"/>
       <c r="B21" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="2">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="D21" s="23" cm="1">
-        <f t="array" ref="D21">_xll.Vpm_to_dBuVpm(C21)</f>
+      <c r="D21" s="23">
+        <f>_xll.Vpm_to_dBuVpm(C21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="38"/>
+      <c r="A22" s="44"/>
       <c r="B22" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
       </c>
-      <c r="D22" s="23" cm="1">
-        <f t="array" ref="D22">_xll.dBuVpm_to_dBmWpm2(C22)</f>
+      <c r="D22" s="23">
+        <f>_xll.dBuVpm_to_dBmWpm2(C22)</f>
         <v>-115.8</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="38"/>
+      <c r="A23" s="44"/>
       <c r="B23" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C23" s="2">
         <v>-115.8</v>
       </c>
-      <c r="D23" s="23" cm="1">
-        <f t="array" ref="D23">_xll.dBmWpm2_to_dBuVpm(C23)</f>
+      <c r="D23" s="23">
+        <f>_xll.dBmWpm2_to_dBuVpm(C23)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="38"/>
+      <c r="A24" s="44"/>
       <c r="B24" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
       </c>
-      <c r="D24" s="23" cm="1">
-        <f t="array" ref="D24">_xll.dBuVpm_to_dBuApm(C24)</f>
+      <c r="D24" s="23">
+        <f>_xll.dBuVpm_to_dBuApm(C24)</f>
         <v>-51.5</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="38"/>
+      <c r="A25" s="44"/>
       <c r="B25" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C25" s="2">
         <v>-51.5</v>
       </c>
-      <c r="D25" s="23" cm="1">
-        <f t="array" ref="D25">_xll.dBuApm_to_dBuVpm(C25)</f>
+      <c r="D25" s="23">
+        <f>_xll.dBuApm_to_dBuVpm(C25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="38"/>
+      <c r="A26" s="44"/>
       <c r="B26" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
       </c>
-      <c r="D26" s="23" cm="1">
-        <f t="array" ref="D26">_xll.dBuApm_to_dBpT(C26)</f>
+      <c r="D26" s="23">
+        <f>_xll.dBuApm_to_dBpT(C26)</f>
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="38"/>
+      <c r="A27" s="44"/>
       <c r="B27" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C27" s="2">
         <v>2</v>
       </c>
-      <c r="D27" s="23" cm="1">
-        <f t="array" ref="D27">_xll.dBpT_to_dBuApm(C27)</f>
+      <c r="D27" s="23">
+        <f>_xll.dBpT_to_dBuApm(C27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="38"/>
+      <c r="A28" s="44"/>
       <c r="B28" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C28" s="2">
         <v>10</v>
       </c>
-      <c r="D28" s="23" cm="1">
-        <f t="array" ref="D28">_xll.Wpm2_to_Vpm(C28)</f>
+      <c r="D28" s="23">
+        <f>_xll.Wpm2_to_Vpm(C28)</f>
         <v>61.400325732035007</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="38"/>
+      <c r="A29" s="44"/>
       <c r="B29" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="2">
         <v>61.400325732035007</v>
       </c>
-      <c r="D29" s="23" cm="1">
-        <f t="array" ref="D29">_xll.Vpm_to_Wpm2(C29)</f>
+      <c r="D29" s="23">
+        <f>_xll.Vpm_to_Wpm2(C29)</f>
         <v>10.000000000000002</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="38"/>
+      <c r="A30" s="44"/>
       <c r="B30" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C30" s="2">
         <v>10</v>
       </c>
-      <c r="D30" s="23" cm="1">
-        <f t="array" ref="D30">_xll.uT_to_Apm(C30)</f>
+      <c r="D30" s="23">
+        <f>_xll.uT_to_Apm(C30)</f>
         <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
+      <c r="A31" s="45"/>
       <c r="B31" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C31" s="2">
         <v>8</v>
       </c>
-      <c r="D31" s="23" cm="1">
-        <f t="array" ref="D31">_xll.Apm_to_uT(C31)</f>
+      <c r="D31" s="23">
+        <f>_xll.Apm_to_uT(C31)</f>
         <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="37" t="s">
+      <c r="A32" s="43" t="s">
         <v>71</v>
       </c>
       <c r="B32" s="5" t="s">
@@ -7407,104 +8114,104 @@
       <c r="C32" s="2">
         <v>1</v>
       </c>
-      <c r="D32" s="23" cm="1">
-        <f t="array" ref="D32">_xll.Feet_to_Meters(C32)</f>
+      <c r="D32" s="23">
+        <f>_xll.Feet_to_Meters(C32)</f>
         <v>0.30480370641306997</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="38"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C33" s="2">
         <v>0.30480370641306997</v>
       </c>
-      <c r="D33" s="23" cm="1">
-        <f t="array" ref="D33">_xll.Meters_to_Feet(C33)</f>
+      <c r="D33" s="23">
+        <f>_xll.Meters_to_Feet(C33)</f>
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="38"/>
+      <c r="A34" s="44"/>
       <c r="B34" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="2">
         <v>1</v>
       </c>
-      <c r="D34" s="23" cm="1">
-        <f t="array" ref="D34">_xll.Miles_to_Kilometers(C34)</f>
+      <c r="D34" s="23">
+        <f>_xll.Miles_to_Kilometers(C34)</f>
         <v>1.6093440000000001</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="38"/>
+      <c r="A35" s="44"/>
       <c r="B35" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C35" s="2">
         <v>1.6093440000000001</v>
       </c>
-      <c r="D35" s="23" cm="1">
-        <f t="array" ref="D35">_xll.Kilometeres_to_Miles(C35)</f>
+      <c r="D35" s="23">
+        <f>_xll.Kilometeres_to_Miles(C35)</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="38"/>
+      <c r="A36" s="44"/>
       <c r="B36" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C36" s="2">
         <v>1</v>
       </c>
-      <c r="D36" s="23" cm="1">
-        <f t="array" ref="D36">_xll.Feet_to_Miles(C36)</f>
+      <c r="D36" s="23">
+        <f>_xll.Feet_to_Miles(C36)</f>
         <v>1.8939393939393939E-4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="38"/>
+      <c r="A37" s="44"/>
       <c r="B37" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C37" s="2">
         <v>1.8939393939393939E-4</v>
       </c>
-      <c r="D37" s="23" cm="1">
-        <f t="array" ref="D37">_xll.Miles_to_Feet(C37)</f>
+      <c r="D37" s="23">
+        <f>_xll.Miles_to_Feet(C37)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="38"/>
+      <c r="A38" s="44"/>
       <c r="B38" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
       </c>
-      <c r="D38" s="23" cm="1">
-        <f t="array" ref="D38">_xll.Meters_to_Kilometers(C38)</f>
+      <c r="D38" s="23">
+        <f>_xll.Meters_to_Kilometers(C38)</f>
         <v>1E-3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="39"/>
+      <c r="A39" s="45"/>
       <c r="B39" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C39" s="2">
         <v>1E-3</v>
       </c>
-      <c r="D39" s="23" cm="1">
-        <f t="array" ref="D39">_xll.Kilometers_to_Meters(C39)</f>
+      <c r="D39" s="23">
+        <f>_xll.Kilometers_to_Meters(C39)</f>
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="40" t="s">
+      <c r="A40" s="46" t="s">
         <v>78</v>
       </c>
       <c r="B40" s="5" t="s">
@@ -7513,73 +8220,73 @@
       <c r="C40" s="2">
         <v>212</v>
       </c>
-      <c r="D40" s="23" cm="1">
-        <f t="array" ref="D40">_xll.Fahrenheit_to_Celsius(C40)</f>
+      <c r="D40" s="23">
+        <f>_xll.Fahrenheit_to_Celsius(C40)</f>
         <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="40"/>
+      <c r="A41" s="46"/>
       <c r="B41" s="5" t="s">
         <v>73</v>
       </c>
       <c r="C41" s="2">
         <v>100</v>
       </c>
-      <c r="D41" s="23" cm="1">
-        <f t="array" ref="D41">_xll.Celsius_to_Fahrenheit(C41)</f>
+      <c r="D41" s="23">
+        <f>_xll.Celsius_to_Fahrenheit(C41)</f>
         <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="40"/>
+      <c r="A42" s="46"/>
       <c r="B42" s="5" t="s">
         <v>74</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
       </c>
-      <c r="D42" s="23" cm="1">
-        <f t="array" ref="D42">_xll.Celsius_to_Kelvin(C42)</f>
+      <c r="D42" s="23">
+        <f>_xll.Celsius_to_Kelvin(C42)</f>
         <v>273.14999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="40"/>
+      <c r="A43" s="46"/>
       <c r="B43" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C43" s="2">
         <v>273.14999999999998</v>
       </c>
-      <c r="D43" s="23" cm="1">
-        <f t="array" ref="D43">_xll.Kelvin_to_Celsius(C43)</f>
+      <c r="D43" s="23">
+        <f>_xll.Kelvin_to_Celsius(C43)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="40"/>
+      <c r="A44" s="46"/>
       <c r="B44" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C44" s="2">
         <v>32</v>
       </c>
-      <c r="D44" s="23" cm="1">
-        <f t="array" ref="D44">_xll.Fahrenheit_to_Kelvin(C44)</f>
+      <c r="D44" s="23">
+        <f>_xll.Fahrenheit_to_Kelvin(C44)</f>
         <v>273.70555555555552</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="40"/>
+      <c r="A45" s="46"/>
       <c r="B45" s="5" t="s">
         <v>77</v>
       </c>
       <c r="C45" s="2">
         <v>273.70555555555552</v>
       </c>
-      <c r="D45" s="23" cm="1">
-        <f t="array" ref="D45">_xll.Kelvin_to_Fahrenheit(C45)</f>
+      <c r="D45" s="23">
+        <f>_xll.Kelvin_to_Fahrenheit(C45)</f>
         <v>32.999999999999979</v>
       </c>
     </row>
@@ -7593,8 +8300,8 @@
       <c r="C46" s="2">
         <v>3.5</v>
       </c>
-      <c r="D46" s="23" cm="1">
-        <f t="array" ref="D46">_xll.gpm3_to_hPa(C46, 273.15)</f>
+      <c r="D46" s="23">
+        <f>_xll.gpm3_to_hPa(C46, 273.15)</f>
         <v>4.411744347023534</v>
       </c>
     </row>
@@ -7612,10 +8319,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -7627,39 +8334,40 @@
     <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B2" s="2">
         <v>39.4</v>
@@ -7683,9 +8391,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B3" s="2">
         <v>39.130000000000003</v>
@@ -7709,9 +8417,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B4" s="2">
         <v>39.18</v>
@@ -7735,9 +8443,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B5" s="2">
         <v>39.369999999999997</v>
@@ -7761,7 +8469,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>83</v>
       </c>
@@ -7772,25 +8480,31 @@
         <v>89</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>195</v>
+        <v>123</v>
       </c>
       <c r="F11" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>195</v>
-      </c>
       <c r="J11" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="L11" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>87</v>
       </c>
@@ -7803,29 +8517,37 @@
       <c r="D12" s="2">
         <v>10</v>
       </c>
-      <c r="E12" s="23" cm="1">
-        <f t="array" ref="E12">ROUND(_xll.RadioHorizon_Km(D12),3)</f>
+      <c r="E12" s="23">
+        <f>ROUND(_xll.TerrainHeight_m(B12,C12,TerHandler,TerDirectory),0)</f>
+        <v>215</v>
+      </c>
+      <c r="F12" s="23">
+        <f>ROUND(_xll.RadioHorizon_Km(D12),3)</f>
         <v>11.289</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="2">
         <v>39.634782999999999</v>
       </c>
-      <c r="G12" s="2">
+      <c r="H12" s="2">
         <v>-78.231067999999993</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <v>20</v>
       </c>
-      <c r="I12" s="23" cm="1">
-        <f t="array" ref="I12">ROUND(_xll.RadioHorizon_Km(H12),3)</f>
+      <c r="J12" s="23">
+        <f>ROUND(_xll.TerrainHeight_m(G12,H12,TerHandler,TerDirectory),0)</f>
+        <v>230</v>
+      </c>
+      <c r="K12" s="23">
+        <f>ROUND(_xll.RadioHorizon_Km(I12),3)</f>
         <v>15.965999999999999</v>
       </c>
-      <c r="J12" s="23" t="str" cm="1">
-        <f t="array" ref="J12">"Distance: " &amp; ROUND(_xll.DistKm(B12,C12,F12,G12),3) &amp; " Km"</f>
+      <c r="L12" s="23" t="str">
+        <f>"Distance: " &amp; ROUND(_xll.DistKm(B12,C12,G12,H12),3) &amp; " Km"</f>
         <v>Distance: 104.891 Km</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>88</v>
       </c>
@@ -7838,29 +8560,37 @@
       <c r="D13" s="2">
         <v>10</v>
       </c>
-      <c r="E13" s="23" cm="1">
-        <f t="array" ref="E13">ROUND(_xll.RadioHorizon_Km(D13),3)</f>
+      <c r="E13" s="23">
+        <f>ROUND(_xll.TerrainHeight_m(B13,C13,TerHandler,TerDirectory),0)</f>
+        <v>215</v>
+      </c>
+      <c r="F13" s="23">
+        <f>ROUND(_xll.RadioHorizon_Km(D13),3)</f>
         <v>11.289</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="2">
         <v>39.634782999999999</v>
       </c>
-      <c r="G13" s="2">
+      <c r="H13" s="2">
         <v>-78.231067999999993</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <v>20</v>
       </c>
-      <c r="I13" s="23" cm="1">
-        <f t="array" ref="I13">ROUND(_xll.RadioHorizon_Km(H13),3)</f>
+      <c r="J13" s="23">
+        <f>ROUND(_xll.TerrainHeight_m(G13,H13,TerHandler,TerDirectory),0)</f>
+        <v>230</v>
+      </c>
+      <c r="K13" s="23">
+        <f>ROUND(_xll.RadioHorizon_Km(I13),3)</f>
         <v>15.965999999999999</v>
       </c>
-      <c r="J13" s="23" t="str" cm="1">
-        <f t="array" ref="J13">"Distance: " &amp; ROUND(_xll.DistKm(B13,C13,F13,G13),3) &amp; " Km"</f>
-        <v>Distance: 104.891 Km</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L13" s="23" t="str">
+        <f>"Bearing: " &amp; ROUND(_xll.Bearing(B13,C13,G13,H13),2) &amp; " Deg"</f>
+        <v>Bearing: 274.54 Deg</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>88</v>
       </c>
@@ -7873,29 +8603,37 @@
       <c r="D14" s="2">
         <v>20</v>
       </c>
-      <c r="E14" s="23" cm="1">
-        <f t="array" ref="E14">ROUND(_xll.RadioHorizon_Km(D14),3)</f>
+      <c r="E14" s="23">
+        <f>ROUND(_xll.TerrainHeight_m(B14,C14,TerHandler,TerDirectory),0)</f>
+        <v>230</v>
+      </c>
+      <c r="F14" s="23">
+        <f>ROUND(_xll.RadioHorizon_Km(D14),3)</f>
         <v>15.965999999999999</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
         <v>39.566355999999999</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H14" s="2">
         <v>-77.013035000000002</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <v>10</v>
       </c>
-      <c r="I14" s="23" cm="1">
-        <f t="array" ref="I14">ROUND(_xll.RadioHorizon_Km(H14),3)</f>
+      <c r="J14" s="23">
+        <f>ROUND(_xll.TerrainHeight_m(G14,H14,TerHandler,TerDirectory),0)</f>
+        <v>215</v>
+      </c>
+      <c r="K14" s="23">
+        <f>ROUND(_xll.RadioHorizon_Km(I14),3)</f>
         <v>11.289</v>
       </c>
-      <c r="J14" s="23" t="str" cm="1">
-        <f t="array" ref="J14">"Distance: " &amp; ROUND(_xll.DistKm(B14,C14,F14,G14),3) &amp; " Km"</f>
-        <v>Distance: 104.891 Km</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L14" s="23" t="str">
+        <f>"Bearing: " &amp; ROUND(_xll.Bearing(B14,C14,G14,H14),2) &amp; " Deg"</f>
+        <v>Bearing: 93.77 Deg</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>91</v>
       </c>
@@ -7908,31 +8646,39 @@
       <c r="D15" s="2">
         <v>10</v>
       </c>
-      <c r="E15" s="23" cm="1">
-        <f t="array" ref="E15">ROUND(_xll.RadioHorizon_Km(D15),3)</f>
+      <c r="E15" s="23">
+        <f>ROUND(_xll.TerrainHeight_m(B15,C15,TerHandler,TerDirectory),0)</f>
+        <v>215</v>
+      </c>
+      <c r="F15" s="23">
+        <f>ROUND(_xll.RadioHorizon_Km(D15),3)</f>
         <v>11.289</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="2">
         <v>39.634782999999999</v>
       </c>
-      <c r="G15" s="2">
+      <c r="H15" s="2">
         <v>-78.231067999999993</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="2">
         <v>20</v>
       </c>
-      <c r="I15" s="23" cm="1">
-        <f t="array" ref="I15">ROUND(_xll.RadioHorizon_Km(H15),3)</f>
+      <c r="J15" s="23">
+        <f>ROUND(_xll.TerrainHeight_m(G15,H15,TerHandler,TerDirectory),0)</f>
+        <v>230</v>
+      </c>
+      <c r="K15" s="23">
+        <f>ROUND(_xll.RadioHorizon_Km(I15),3)</f>
         <v>15.965999999999999</v>
       </c>
-      <c r="J15" s="23" t="str" cm="1">
-        <f t="array" ref="J15">"Distance: " &amp; ROUND(_xll.DistKm(B15,C15,F15,G15),3) &amp; " Km"</f>
-        <v>Distance: 104.891 Km</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L15" s="23" t="str">
+        <f>"Is LOS: " &amp; _xll.IsLOS(B15,C15,G15,H15,D15,I15,0,TerDirectory)</f>
+        <v>Is LOS: FALSE</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -7942,8 +8688,10 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="23" t="str" cm="1">
-        <f t="array" ref="J16">"Delta Bearing: " &amp;ROUND(_xll.Delta_Bearing(_xll.Bearing(B13,C13,F13,G13), _xll.Bearing(B14,C14,F14,G14)),2) &amp; " Deg"</f>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="23" t="str">
+        <f>"Delta Bearing: " &amp;ROUND( _xll.Delta_Bearing(_xll.Bearing(B13,C13,G13,H13), _xll.Bearing(B14,C14,G14,H14)),2) &amp; " Deg"</f>
         <v>Delta Bearing: 179.22 Deg</v>
       </c>
     </row>
@@ -7953,85 +8701,128 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2226CAC0-AF79-44C0-AA2A-1A7BFBA387F4}">
-  <dimension ref="A1:D8"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="75" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="61.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
+      <c r="A1" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="B2" s="2">
-        <v>146.94</v>
+        <v>456.07499999999999</v>
       </c>
       <c r="C2" s="2">
-        <v>147.06</v>
+        <v>456.57499999999999</v>
       </c>
       <c r="D2" s="2">
-        <v>147.18</v>
+        <v>456.1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>206</v>
+        <v>125</v>
       </c>
       <c r="B3" s="2">
-        <v>146.52000000000001</v>
+        <v>461.55</v>
       </c>
       <c r="C3" s="2">
-        <v>147.18</v>
+        <v>456.1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B4" s="2">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="C4" s="2">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="B6" s="26" t="str" cm="1">
-        <f t="array" ref="B6">_xll.IntermodHarmonics(B2:D2,B3:C3,B4:C4)</f>
-        <v xml:space="preserve"> Harmonic Found---&gt;    1 (147.18) = 147.18 ± 0.02 MHz bandwidth</v>
+        <v>203</v>
+      </c>
+      <c r="B6" s="26" t="str">
+        <f>_xll.IntermodHarmonics(B2:D2,B3:C3,B4:C4)</f>
+        <v xml:space="preserve"> Harmonic Found---&gt;    1 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
+ Harmonic Found---&gt;    1 (456.1) = 456.1 ± 0.1 MHz bandwidth</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="26" t="str" cm="1">
-        <f t="array" ref="B7">_xll.IntermodTwoSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
-        <v xml:space="preserve"> INTERMOD---&gt;   2 (147.06) - 1 (146.94) = 147.18 ± 0.02 MHz bandwidth</v>
+        <v>201</v>
+      </c>
+      <c r="B7" s="26" t="str">
+        <f>_xll.IntermodTwoSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
+        <v xml:space="preserve"> INTERMOD---&gt;   2 (456.075) - 1 (456.1) = 456.1 ± 0.1 MHz bandwidth_x000D_
+ INTERMOD---&gt;   3 (456.075) - 2 (456.1) = 456.1 ± 0.1 MHz bandwidth_x000D_
+ INTERMOD---&gt;   2 (456.1) - 1 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
+ INTERMOD---&gt;   3 (456.1) - 2 (456.075) = 456.1 ± 0.1 MHz bandwidth_x000D_
+ INTERMOD---&gt;   4 (456.1) - 3 (456.075) = 456.1 ± 0.1 MHz bandwidth</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="B8" s="30" t="str" cm="1">
-        <f t="array" ref="B8">_xll.IntermodThreeSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
-        <v xml:space="preserve"> INTERMOD---&gt;   4 (147.06) - 2 (146.94) - 1 (147.18) = 147.18 ± 0.02 MHz bandwidth_x000D_
- INTERMOD---&gt;   2 (147.18) - 2 (147.06) + 1 (146.94) = 147.18 ± 0.02 MHz bandwidth</v>
+        <v>202</v>
+      </c>
+      <c r="B8" s="26" t="str">
+        <f>_xll.IntermodThreeSignalMix(B2:D2,B3:C3,B4:C4,3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="53" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="53" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="54" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="54"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="55" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -8045,6 +8836,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{568178ef-2b90-40ee-86de-4595a529cba9}" enabled="1" method="Standard" siteId="{d6cff1bd-67dd-4ce8-945d-d07dc775672f}" contentBits="0" removed="0"/>
+  <clbl:label id="{568178ef-2b90-40ee-86de-4595a529cba9}" enabled="1" method="Standard" siteId="{d6cff1bd-67dd-4ce8-945d-d07dc775672f}" removed="0"/>
 </clbl:labelList>
 </file>